--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chứng khoán Rồng Việt sắp phát hành 300 tỷ đồng trái phiếu ‘ba không’</t>
+          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chứng khoán Rồng Việt dự kiến phát hành 3.000 trái phiếu mã VDS12602 vào ngày 12/5/2026 tới đây nhằm huy động 300 tỷ đồng dùng để cơ cấu nợ.</t>
+          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-rong-viet-sap-phat-hanh-300-ty-dong-trai-phieu-ba-khong-188260511215752335.chn</t>
+          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
+          <t>Tue, 12 May 26 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
+          <t>Tue, 12 May 26 07:36:00 +0700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
+          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
+          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
+          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
+          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
+          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:45:00 +0700</t>
+          <t>Mon, 11 May 26 22:10:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
+          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
+          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:34:00 +0700</t>
+          <t>Mon, 11 May 26 22:04:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
+          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thanh toán QR xuyên biên giới tái định hình dòng chảy thương mại khu vực</t>
+          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sự trỗi dậy của thanh toán QR xuyên biên giới không chỉ giải quyết triệt để bài toán ngoại tệ và tỷ giá cho hàng triệu du khách Việt mỗi năm, mà còn tạo đòn bẩy vĩ mô giúp các doanh nghiệp trong nước đón đầu dòng khách quốc tế, hội nhập sâu rộng vào nền kinh tế số khu vực.</t>
+          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:20:00 +0700</t>
+          <t>Mon, 11 May 26 22:00:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thanh-toan-qr-xuyen-bien-gioi-tai-dinh-hinh-dong-chay-thuong-mai-khu-vuc-188260511152039861.chn</t>
+          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Đầu tư Sài Gòn VRG sắp chi hơn 968 tỷ đồng trả cổ tức đợt 2/2025</t>
+          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ngày 15/5/2026 tới đây, Đầu tư Sài Gòn VRG sẽ chốt danh sách cổ đông để thực hiện chi chi trả cổ tức đợt 2 năm 2025 bằng tiền mặt với tỷ lệ 40%. Thời gian thực hiện thanh toán 5/6/2026.</t>
+          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 14:09:00 +0700</t>
+          <t>Mon, 11 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-sai-gon-vrg-sap-chi-hon-968-ty-dong-tra-co-tuc-dot-2-2025-188260511140113381.chn</t>
+          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F88 chào bán thành công 300 tỷ đồng trái phiếu</t>
+          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kết thúc đợt chào bán ngày 7/5/2026, F88 đã chào bán thành công 3 triệu trái phiếu tên F88BOND.PO.02, mã trái phiếu dự kiến là F88126015, qua đó huy động 300 tỷ đồng.</t>
+          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 14:06:00 +0700</t>
+          <t>Mon, 11 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/f88-chao-ban-thanh-cong-300-ty-dong-trai-phieu-188260511140148051.chn</t>
+          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Một cổ phiếu trên HOSE bất ngờ "trần cứng" 3 phiên liên tiếp, chuyện gì đang xảy ra?</t>
+          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Không phải cái tên nổi bật trên thị trường, nhưng cổ phiếu này cũng từng gây chú ý hồi đầu năm với chuỗi tăng trần kéo dài hàng chục phiên liên tiếp.</t>
+          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 11:31:00 +0700</t>
+          <t>Mon, 11 May 26 15:34:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-tren-hose-bat-ngo-tran-cung-3-phien-lien-tiep-chuyen-gi-dang-xay-ra-188260511112953843.chn</t>
+          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>“Gà đẻ trứng vàng” đồng loạt báo tin vui, CTCK dự báo MWG vượt kế hoạch lợi nhuận 2026</t>
+          <t>Thanh toán QR xuyên biên giới tái định hình dòng chảy thương mại khu vực</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Những chuỗi chủ lực của MWG là Điện Máy Xanh, Bách Hóa Xanh,… đều ghi nhận tín hiệu tích cực từ hoạt động kinh doanh.</t>
+          <t>Sự trỗi dậy của thanh toán QR xuyên biên giới không chỉ giải quyết triệt để bài toán ngoại tệ và tỷ giá cho hàng triệu du khách Việt mỗi năm, mà còn tạo đòn bẩy vĩ mô giúp các doanh nghiệp trong nước đón đầu dòng khách quốc tế, hội nhập sâu rộng vào nền kinh tế số khu vực.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 11:04:00 +0700</t>
+          <t>Mon, 11 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ga-de-trung-vang-dong-loat-bao-tin-vui-ctck-du-bao-mwg-vuot-ke-hoach-loi-nhuan-2026-188260511110426822.chn</t>
+          <t>https://cafef.vn/thanh-toan-qr-xuyen-bien-gioi-tai-dinh-hinh-dong-chay-thuong-mai-khu-vuc-188260511152039861.chn</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chứng khoán UP trở thành cổ đông lớn tại một công ty thực phẩm</t>
+          <t>Đầu tư Sài Gòn VRG sắp chi hơn 968 tỷ đồng trả cổ tức đợt 2/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sau hai lần mua vào cổ phiếu FCC, Chứng khoán UP đã mua vào 830.000 cổ phiếu FCC, chiếm 13,83% Công ty cổ phần Liên hợp Thực phẩm.</t>
+          <t>Ngày 15/5/2026 tới đây, Đầu tư Sài Gòn VRG sẽ chốt danh sách cổ đông để thực hiện chi chi trả cổ tức đợt 2 năm 2025 bằng tiền mặt với tỷ lệ 40%. Thời gian thực hiện thanh toán 5/6/2026.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:54:00 +0700</t>
+          <t>Mon, 11 May 26 14:09:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-up-tro-thanh-co-dong-lon-tai-mot-cong-ty-thuc-pham-188260511101355489.chn</t>
+          <t>https://cafef.vn/dau-tu-sai-gon-vrg-sap-chi-hon-968-ty-dong-tra-co-tuc-dot-2-2025-188260511140113381.chn</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>295 người sắp được mua cổ phiếu công ty chứng khoán của ông Nguyễn Duy Hưng với giá cực hời</t>
+          <t>F88 chào bán thành công 300 tỷ đồng trái phiếu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cổ phiếu SSI hiện giao dịch quanh vùng 28.500 đồng/cổ phiếu, tương đương vốn hóa hơn 71.000 tỷ đồng.</t>
+          <t>Kết thúc đợt chào bán ngày 7/5/2026, F88 đã chào bán thành công 3 triệu trái phiếu tên F88BOND.PO.02, mã trái phiếu dự kiến là F88126015, qua đó huy động 300 tỷ đồng.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:53:00 +0700</t>
+          <t>Mon, 11 May 26 14:06:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/295-nguoi-sap-duoc-mua-co-phieu-cong-ty-chung-khoan-cua-ong-nguyen-duy-hung-voi-gia-cuc-hoi-188260511105332872.chn</t>
+          <t>https://cafef.vn/f88-chao-ban-thanh-cong-300-ty-dong-trai-phieu-188260511140148051.chn</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loạt doanh nghiệp chốt quyền trả cổ tức trong tuần từ ngày 11/5-15/5</t>
+          <t>Một cổ phiếu trên HOSE bất ngờ "trần cứng" 3 phiên liên tiếp, chuyện gì đang xảy ra?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Từ ngày 11/5-15/5, trên các sàn chứng khoán, có 37 doanh nghiệp chốt quyền trả cổ tức cho cổ đông bằng tiền mặt hoặc cổ phiếu.</t>
+          <t>Không phải cái tên nổi bật trên thị trường, nhưng cổ phiếu này cũng từng gây chú ý hồi đầu năm với chuỗi tăng trần kéo dài hàng chục phiên liên tiếp.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:32:00 +0700</t>
+          <t>Mon, 11 May 26 11:31:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loat-doanh-nghiep-chot-quyen-tra-co-tuc-trong-tuan-tu-ngay-11-5-15-5-188260511103244806.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-tren-hose-bat-ngo-tran-cung-3-phien-lien-tiep-chuyen-gi-dang-xay-ra-188260511112953843.chn</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Giá vàng, bạc hồi phục mạnh, đã đến thời điểm giải ngân mạnh tay?</t>
+          <t>“Gà đẻ trứng vàng” đồng loạt báo tin vui, CTCK dự báo MWG vượt kế hoạch lợi nhuận 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dòng tiền sẽ sớm trở lại với vàng, một trong những tài sản dự trữ hàng đầu trong khi triển vọng thị trường bạc về cơ bản vẫn tích cực, nhu cầu cho kinh tế xanh hay trí tuệ nhân tạo là khá lớn.</t>
+          <t>Những chuỗi chủ lực của MWG là Điện Máy Xanh, Bách Hóa Xanh,… đều ghi nhận tín hiệu tích cực từ hoạt động kinh doanh.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:20:00 +0700</t>
+          <t>Mon, 11 May 26 11:04:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gia-vang-bac-hoi-phuc-manh-da-den-thoi-diem-giai-ngan-manh-tay-188260511102011136.chn</t>
+          <t>https://cafef.vn/ga-de-trung-vang-dong-loat-bao-tin-vui-ctck-du-bao-mwg-vuot-ke-hoach-loi-nhuan-2026-188260511110426822.chn</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HDBank dự kiến phát hành 15.000 tỷ đồng trái phiếu</t>
+          <t>Chứng khoán UP trở thành cổ đông lớn tại một công ty thực phẩm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HĐQT HDBank đã chấp thuận chủ trương phát hành riêng lẻ trái phiếu lần 1 năm 2026 với tổng mệnh giá phát hành tối đa 15.000 tỷ đồng.</t>
+          <t>Sau hai lần mua vào cổ phiếu FCC, Chứng khoán UP đã mua vào 830.000 cổ phiếu FCC, chiếm 13,83% Công ty cổ phần Liên hợp Thực phẩm.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:13:00 +0700</t>
+          <t>Mon, 11 May 26 10:54:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hdbank-du-kien-phat-hanh-15000-ty-dong-trai-phieu-188260511101352153.chn</t>
+          <t>https://cafef.vn/chung-khoan-up-tro-thanh-co-dong-lon-tai-mot-cong-ty-thuc-pham-188260511101355489.chn</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VN-Index vượt đỉnh lịch sử, nhưng ba nhóm cổ phiếu này vẫn “ở dưới mặt đất” với mức giảm sâu trên 30%</t>
+          <t>295 người sắp được mua cổ phiếu công ty chứng khoán của ông Nguyễn Duy Hưng với giá cực hời</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Theo Chứng khoán MB (MBS), dù VN-Index chính thức vượt mốc 1.900 điểm, thị trường vẫn cho thấy sự thiếu đồng thuận rõ rệt.</t>
+          <t>Cổ phiếu SSI hiện giao dịch quanh vùng 28.500 đồng/cổ phiếu, tương đương vốn hóa hơn 71.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 08:56:00 +0700</t>
+          <t>Mon, 11 May 26 10:53:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-nhung-ba-nhom-co-phieu-nay-van-o-duoi-mat-dat-voi-muc-giam-sau-tren-30-188260511085600698.chn</t>
+          <t>https://cafef.vn/295-nguoi-sap-duoc-mua-co-phieu-cong-ty-chung-khoan-cua-ong-nguyen-duy-hung-voi-gia-cuc-hoi-188260511105332872.chn</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Loạt thông tin tích cực xuất hiện, VN-Index sẽ sớm chinh phục mốc 2.000 điểm?</t>
+          <t>Loạt doanh nghiệp chốt quyền trả cổ tức trong tuần từ ngày 11/5-15/5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chứng khoán ABS kỳ vọng VN-Index có thể sớm vượt vùng đỉnh cũ 1.920 điểm, sau đó tích lũy trên vùng đỉnh với sự lan tỏa của dòng tiền và thanh khoản gia tăng.</t>
+          <t>Từ ngày 11/5-15/5, trên các sàn chứng khoán, có 37 doanh nghiệp chốt quyền trả cổ tức cho cổ đông bằng tiền mặt hoặc cổ phiếu.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:05:00 +0700</t>
+          <t>Mon, 11 May 26 10:32:00 +0700</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loat-thong-tin-tich-cuc-xuat-hien-vn-index-se-som-chinh-phuc-moc-2000-diem-188260510213551528.chn</t>
+          <t>https://cafef.vn/loat-doanh-nghiep-chot-quyen-tra-co-tuc-trong-tuan-tu-ngay-11-5-15-5-188260511103244806.chn</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chứng khoán VIX triệu tập ĐHĐCĐ thường niên năm 2026</t>
+          <t>Giá vàng, bạc hồi phục mạnh, đã đến thời điểm giải ngân mạnh tay?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ngày 27/5/2026 là ngày đăng ký cuối cùng để thực hiện quyền tham dự ĐHĐCĐ thường niên năm 2026 Chứng khoán VIX.</t>
+          <t>Dòng tiền sẽ sớm trở lại với vàng, một trong những tài sản dự trữ hàng đầu trong khi triển vọng thị trường bạc về cơ bản vẫn tích cực, nhu cầu cho kinh tế xanh hay trí tuệ nhân tạo là khá lớn.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:03:00 +0700</t>
+          <t>Mon, 11 May 26 10:20:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vix-trieu-tap-dhdcd-thuong-nien-nam-2026-188260510214351235.chn</t>
+          <t>https://cafef.vn/gia-vang-bac-hoi-phuc-manh-da-den-thoi-diem-giai-ngan-manh-tay-188260511102011136.chn</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dòng vốn tỷ USD "chực chờ" đổ bộ Việt Nam, công ty chứng khoán bước vào cuộc đua mới</t>
+          <t>HDBank dự kiến phát hành 15.000 tỷ đồng trái phiếu</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sau nâng hạng, ngành chứng khoán được kỳ vọng hưởng lợi từ dòng vốn ngoại, thanh khoản cải thiện và làn sóng huy động vốn mới. Tuy nhiên, áp lực lãi suất, chi phí vốn và cạnh tranh công nghệ cũng sẽ khiến cuộc chơi phân hóa mạnh hơn giữa các CTCK.</t>
+          <t>HĐQT HDBank đã chấp thuận chủ trương phát hành riêng lẻ trái phiếu lần 1 năm 2026 với tổng mệnh giá phát hành tối đa 15.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:01:00 +0700</t>
+          <t>Mon, 11 May 26 10:13:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dong-von-ty-usd-chuc-cho-do-bo-viet-nam-cong-ty-chung-khoan-buoc-vao-cuoc-dua-moi-188260510213652315.chn</t>
+          <t>https://cafef.vn/hdbank-du-kien-phat-hanh-15000-ty-dong-trai-phieu-188260511101352153.chn</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VN-Index vượt đỉnh lịch sử, tưởng ai cũng thắng lớn nhưng thực tế lại rất khác!</t>
+          <t>VN-Index vượt đỉnh lịch sử, nhưng ba nhóm cổ phiếu này vẫn “ở dưới mặt đất” với mức giảm sâu trên 30%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VN-Index trở lại vùng đỉnh lịch sử trên 1.900 điểm nhưng tài khoản của nhiều nhà đầu tư vẫn thua lỗ.</t>
+          <t>Theo Chứng khoán MB (MBS), dù VN-Index chính thức vượt mốc 1.900 điểm, thị trường vẫn cho thấy sự thiếu đồng thuận rõ rệt.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 18:19:00 +0700</t>
+          <t>Mon, 11 May 26 08:56:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-tuong-ai-cung-thang-lon-nhung-thuc-te-lai-rat-khac-188260510182010552.chn</t>
+          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-nhung-ba-nhom-co-phieu-nay-van-o-duoi-mat-dat-voi-muc-giam-sau-tren-30-188260511085600698.chn</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Đua nhau bán cổ phiếu Thế giới Di động</t>
+          <t>Loạt thông tin tích cực xuất hiện, VN-Index sẽ sớm chinh phục mốc 2.000 điểm?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nhóm quỹ liên quan Dragon Capital đã bán ra 541.366 cổ phiếu MWG của Công ty CP Đầu tư Thế giới Di động, giảm sở hữu về 4,96% vốn điều lệ và không còn là cổ đông lớn. Tương tự, ông Đoàn Văn Hiểu Em - thành viên Hội đồng quản trị MWG - đăng ký bán ra 2 triệu cổ phiếu MWG để giảm sở hữu xuống 1,55 triệu cổ phiếu.</t>
+          <t>Chứng khoán ABS kỳ vọng VN-Index có thể sớm vượt vùng đỉnh cũ 1.920 điểm, sau đó tích lũy trên vùng đỉnh với sự lan tỏa của dòng tiền và thanh khoản gia tăng.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 18:16:00 +0700</t>
+          <t>Mon, 11 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dua-nhau-ban-co-phieu-the-gioi-di-dong-188260510181703105.chn</t>
+          <t>https://cafef.vn/loat-thong-tin-tich-cuc-xuat-hien-vn-index-se-som-chinh-phuc-moc-2000-diem-188260510213551528.chn</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Góc nhìn chuyên gia: VN-Index khó tăng bền vững nếu không có một nhịp chỉnh lành mạnh trước</t>
+          <t>Chứng khoán VIX triệu tập ĐHĐCĐ thường niên năm 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, chiến lược hợp lý lúc này là kiên nhẫn chờ nhịp điều chỉnh, phân bổ một phần vào cổ phiếu trụ để đi theo đà thị trường, phần còn lại tập trung vào cổ phiếu có câu chuyện riêng và nền tảng cơ bản rõ ràng.</t>
+          <t>Ngày 27/5/2026 là ngày đăng ký cuối cùng để thực hiện quyền tham dự ĐHĐCĐ thường niên năm 2026 Chứng khoán VIX.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 16:10:00 +0700</t>
+          <t>Mon, 11 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/goc-nhin-chuyen-gia-vn-index-kho-tang-ben-vung-neu-khong-co-mot-nhip-chinh-lanh-manh-truoc-188260510161025213.chn</t>
+          <t>https://cafef.vn/chung-khoan-vix-trieu-tap-dhdcd-thuong-nien-nam-2026-188260510214351235.chn</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nhóm cổ đông Âu Lạc tăng sở lên 6% vốn tại ACB</t>
+          <t>Dòng vốn tỷ USD "chực chờ" đổ bộ Việt Nam, công ty chứng khoán bước vào cuộc đua mới</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sau khi ái nữ của Chủ tịch Ngô Thu Thúy mua vào gần 8,4 cổ phiếu ACB trong phiên 4/5/2026, nhóm cổ đông Âu Lạc đã nâng tổng sở hữu lên 6% vốn tại ACB.</t>
+          <t>Sau nâng hạng, ngành chứng khoán được kỳ vọng hưởng lợi từ dòng vốn ngoại, thanh khoản cải thiện và làn sóng huy động vốn mới. Tuy nhiên, áp lực lãi suất, chi phí vốn và cạnh tranh công nghệ cũng sẽ khiến cuộc chơi phân hóa mạnh hơn giữa các CTCK.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 10:59:00 +0700</t>
+          <t>Mon, 11 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-co-dong-au-lac-tang-so-len-6-von-tai-acb-188260510100859932.chn</t>
+          <t>https://cafef.vn/dong-von-ty-usd-chuc-cho-do-bo-viet-nam-cong-ty-chung-khoan-buoc-vao-cuoc-dua-moi-188260510213652315.chn</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Về Bộ Công an, Chủ tịch và Tổng Giám đốc FPT Telecom được phong cấp thượng tá</t>
+          <t>VN-Index vượt đỉnh lịch sử, tưởng ai cũng thắng lớn nhưng thực tế lại rất khác!</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tháng 7/2025, Bộ Công an đã tiếp nhận quyền đại diện chủ sở hữu phần vốn nhà nước tại Công ty FPT Telecom từ Tổng công ty Đầu tư và Kinh doanh vốn Nhà nước (SCIC).</t>
+          <t>VN-Index trở lại vùng đỉnh lịch sử trên 1.900 điểm nhưng tài khoản của nhiều nhà đầu tư vẫn thua lỗ.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:26:00 +0700</t>
+          <t>Sun, 10 May 26 18:19:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ve-bo-cong-an-chu-tich-va-tong-giam-doc-fpt-telecom-duoc-phong-cap-thuong-ta-188260510002659875.chn</t>
+          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-tuong-ai-cung-thang-lon-nhung-thuc-te-lai-rat-khac-188260510182010552.chn</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lịch chốt quyền cổ tức 11-15/5: 50 doanh nghiệp đồng loạt “lăn chốt”, Hòa Phát góp mặt, một ngân hàng chi gần 9.000 tỷ trả cổ tức</t>
+          <t>Đua nhau bán cổ phiếu Thế giới Di động</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Loạt doanh nghiệp hot lăn chốt trong tuần này là Hoà Phát, Digiworld, LPB, Dược Hậu Giang,...</t>
+          <t>Nhóm quỹ liên quan Dragon Capital đã bán ra 541.366 cổ phiếu MWG của Công ty CP Đầu tư Thế giới Di động, giảm sở hữu về 4,96% vốn điều lệ và không còn là cổ đông lớn. Tương tự, ông Đoàn Văn Hiểu Em - thành viên Hội đồng quản trị MWG - đăng ký bán ra 2 triệu cổ phiếu MWG để giảm sở hữu xuống 1,55 triệu cổ phiếu.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:06:00 +0700</t>
+          <t>Sun, 10 May 26 18:16:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lich-chot-quyen-co-tuc-11-15-5-50-doanh-nghiep-dong-loat-lan-chot-hoa-phat-gop-mat-mot-ngan-hang-chi-gan-9000-ty-tra-co-tuc-188260509215718878.chn</t>
+          <t>https://cafef.vn/dua-nhau-ban-co-phieu-the-gioi-di-dong-188260510181703105.chn</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dấu hiệu tạo đỉnh ngắn hạn của VN-Index</t>
+          <t>Góc nhìn chuyên gia: VN-Index khó tăng bền vững nếu không có một nhịp chỉnh lành mạnh trước</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Theo SHS, với việc chỉ số VN-Index, sau 5 tuần tăng liên tiếp từ vùng 1.600 điểm lên sát 1.900 điểm, thị trường đang đối mặt nguy cơ hình thành đỉnh ngắn hạn.</t>
+          <t>Theo chuyên gia, chiến lược hợp lý lúc này là kiên nhẫn chờ nhịp điều chỉnh, phân bổ một phần vào cổ phiếu trụ để đi theo đà thị trường, phần còn lại tập trung vào cổ phiếu có câu chuyện riêng và nền tảng cơ bản rõ ràng.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:05:00 +0700</t>
+          <t>Sun, 10 May 26 16:10:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-hieu-tao-dinh-ngan-han-cua-vn-index-188260509215903787.chn</t>
+          <t>https://cafef.vn/goc-nhin-chuyen-gia-vn-index-kho-tang-ben-vung-neu-khong-co-mot-nhip-chinh-lanh-manh-truoc-188260510161025213.chn</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chuyên gia: VN-Index còn dư địa tăng, nhà đầu tư vẫn nên thận trọng</t>
+          <t>Nhóm cổ đông Âu Lạc tăng sở lên 6% vốn tại ACB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VN-Index đang lấy lại tín hiệu tích cực sau nhịp điều chỉnh, với kỳ vọng chỉ số có thể hướng tới vùng cao hơn nếu vượt 1.920 điểm.</t>
+          <t>Sau khi ái nữ của Chủ tịch Ngô Thu Thúy mua vào gần 8,4 cổ phiếu ACB trong phiên 4/5/2026, nhóm cổ đông Âu Lạc đã nâng tổng sở hữu lên 6% vốn tại ACB.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 17:30:00 +0700</t>
+          <t>Sun, 10 May 26 10:59:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chuyen-gia-vn-index-con-du-dia-tang-nha-dau-tu-van-nen-than-trong-188260509172638364.chn</t>
+          <t>https://cafef.vn/nhom-co-dong-au-lac-tang-so-len-6-von-tai-acb-188260510100859932.chn</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"Cá mập" ôm gần 30.000 tỷ vừa tới thăm nhà máy thép lớn nhất của Hoà Phát</t>
+          <t>Về Bộ Công an, Chủ tịch và Tổng Giám đốc FPT Telecom được phong cấp thượng tá</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tính đến cuối tháng 4/2026, tỷ trọng cổ phiếu thép HPG trong danh mục cá mập này.</t>
+          <t>Tháng 7/2025, Bộ Công an đã tiếp nhận quyền đại diện chủ sở hữu phần vốn nhà nước tại Công ty FPT Telecom từ Tổng công ty Đầu tư và Kinh doanh vốn Nhà nước (SCIC).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 17:15:00 +0700</t>
+          <t>Sun, 10 May 26 00:26:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ca-map-om-gan-30000-ty-vua-toi-tham-nha-may-thep-lon-nhat-cua-hoa-phat-188260509171521614.chn</t>
+          <t>https://cafef.vn/ve-bo-cong-an-chu-tich-va-tong-giam-doc-fpt-telecom-duoc-phong-cap-thuong-ta-188260510002659875.chn</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều doanh nghiệp lớn trước thềm đại hội cổ đông</t>
+          <t>Lịch chốt quyền cổ tức 11-15/5: 50 doanh nghiệp đồng loạt “lăn chốt”, Hòa Phát góp mặt, một ngân hàng chi gần 9.000 tỷ trả cổ tức</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Địa ốc Hoàng Quân nhận được đơn từ nhiệm thành viên Hội đồng quản trị của ông Trần Anh Tuấn và đơn xin từ nhiệm thành viên Ban kiểm soát của bà Nguyễn Thị Bích Thủy. Trong khi đó, Đức Long Gia Lai nhận được đơn xin từ nhiệm thành viên Hội đồng quản trị của ông Võ Mộng Hùng và đề cử ông Phạm Văn Binh vào vị trí thành viên Hội đồng quản trị nhiệm kỳ 2022 - 2027.</t>
+          <t>Loạt doanh nghiệp hot lăn chốt trong tuần này là Hoà Phát, Digiworld, LPB, Dược Hậu Giang,...</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 15:11:00 +0700</t>
+          <t>Sun, 10 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-doanh-nghiep-lon-truoc-them-dai-hoi-co-dong-188260509142249403.chn</t>
+          <t>https://cafef.vn/lich-chot-quyen-co-tuc-11-15-5-50-doanh-nghiep-dong-loat-lan-chot-hoa-phat-gop-mat-mot-ngan-hang-chi-gan-9000-ty-tra-co-tuc-188260509215718878.chn</t>
         </is>
       </c>
     </row>
@@ -1381,76 +1381,76 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>“Bốc hơi” 57% lợi nhuận quý I, vì sao cổ phiếu Điện Gia Lai (GEG) vẫn được kỳ vọng tăng hơn 27%?</t>
+          <t>Dấu hiệu tạo đỉnh ngắn hạn của VN-Index</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dù lợi nhuận quý I/2026 “lao dốc” tới 57%, cổ phiếu GEG của CTCP Điện Gia Lai vẫn được công ty chứng khoán ACBS duy trì khuyến nghị “MUA” với kỳ vọng tăng giá hơn 27%.</t>
+          <t>Theo SHS, với việc chỉ số VN-Index, sau 5 tuần tăng liên tiếp từ vùng 1.600 điểm lên sát 1.900 điểm, thị trường đang đối mặt nguy cơ hình thành đỉnh ngắn hạn.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 13:55:00 +0700</t>
+          <t>Sun, 10 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/boc-hoi-57-loi-nhuan-quy-i-vi-sao-co-phieu-dien-gia-lai-geg-van-duoc-ky-vong-tang-hon-27-188260509135223314.chn</t>
+          <t>https://cafef.vn/dau-hieu-tao-dinh-ngan-han-cua-vn-index-188260509215903787.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chứng khoán tuần qua: VN-Index lập đỉnh lịch sử, một cổ phiếu bluechips bị khối ngoại “xả” đột biến</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VN-Index lập đỉnh lịch sử; Một cổ phiếu bluechips bị khối ngoại “xả” đột biến; Dòng tiền “bắt đáy” nhập cuộc, cổ phiếu Novaland (NVL) tăng bứt phá sau chuỗi 4 phiên “lao dốc”; VN-Index có thể vượt 2.300 điểm?, …</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung vẫn ở mức hấp dẫn, một số nhà băng như HDBank, NCB trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 13:51:00 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-tuan-qua-vn-index-lap-dinh-lich-su-mot-co-phieu-bluechips-bi-khoi-ngoai-xa-dot-bien-188260509133501609.chn</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vì sao Chứng khoán Beta bị phạt hơn 360 triệu đồng?</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chứng khoán Beta bị phạt do vi phạm về hạn chế cho vay và Báo cáo có nội dung sai lệch.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sat, 09 May 26 09:48:00 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vi-sao-chung-khoan-beta-bi-phat-hon-360-trieu-dong-188260509094817397.chn</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung vẫn ở mức hấp dẫn, một số nhà băng như HDBank, NCB trả 8-9% một năm.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 tỷ USD thức giấc</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 tỷ USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-ty-usd-thuc-giac-5072749.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Fri, 08 May 2026 11:57:38 +0700</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+          <t>Fri, 08 May 2026 07:36:44 +0700</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+          <t>Fri, 08 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+          <t>Fri, 08 May 2026 02:00:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+          <t>Fri, 08 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+          <t>Thu, 07 May 2026 20:26:38 +0700</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+          <t>Thu, 07 May 2026 19:05:00 +0700</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+          <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+          <t>'Ấn Độ sẵn sàng hỗ trợ Việt Nam phát triển thị trường vốn'</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+          <t>Lãnh đạo Sàn giao dịch Chứng khoán Quốc gia Ấn Độ cho biết cơ quan này sẵn sàng hỗ trợ quá trình phát triển thị trường vốn của Việt Nam.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 20:26:38 +0700</t>
+          <t>Thu, 07 May 2026 18:37:56 +0700</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+          <t>https://vnexpress.net/an-do-san-sang-ho-tro-viet-nam-phat-trien-thi-truong-von-5071229.html</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
+          <t>Giá xăng tăng, dầu giảm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
+          <t>Từ 15h ngày 7/5, giá xăng tăng, còn dầu diesel giảm theo đà biến động của thị trường năng lượng thế giới.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 19:05:00 +0700</t>
+          <t>Thu, 07 May 2026 14:34:36 +0700</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-7-5-5068301.html</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'Ấn Độ sẵn sàng hỗ trợ Việt Nam phát triển thị trường vốn'</t>
+          <t>Chứng khoán vượt đỉnh</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lãnh đạo Sàn giao dịch Chứng khoán Quốc gia Ấn Độ cho biết cơ quan này sẵn sàng hỗ trợ quá trình phát triển thị trường vốn của Việt Nam.</t>
+          <t>Chứng khoán lập kỷ lục mới khi VN-Index đóng cửa trên 1.909 điểm với sự dẫn dắt của cổ phiếu Vingroup và Vinhomes.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 18:37:56 +0700</t>
+          <t>Thu, 07 May 2026 13:58:54 +0700</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/an-do-san-sang-ho-tro-viet-nam-phat-trien-thi-truong-von-5071229.html</t>
+          <t>https://vnexpress.net/chung-khoan-vuot-dinh-5071073.html</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Giá xăng tăng, dầu giảm</t>
+          <t>Nike chưa thể phục hồi với chiến lược 'Win Now'</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Từ 15h ngày 7/5, giá xăng tăng, còn dầu diesel giảm theo đà biến động của thị trường năng lượng thế giới.</t>
+          <t>Sau 18 tháng triển khai chiến lược vực dậy "Chiến thắng ngay", thị phần của Nike tiếp tục sụt giảm khiến giới đầu tư Phố Wall mất dần kiên nhẫn.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 14:34:36 +0700</t>
+          <t>Thu, 07 May 2026 01:10:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-7-5-5068301.html</t>
+          <t>https://vnexpress.net/nike-chua-the-phuc-hoi-voi-chien-luoc-win-now-5070718.html</t>
         </is>
       </c>
     </row>
@@ -2218,74 +2218,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chứng khoán vượt đỉnh</t>
+          <t>Lưu ý gì khi sử dụng margin trong chứng khoán?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chứng khoán lập kỷ lục mới khi VN-Index đóng cửa trên 1.909 điểm với sự dẫn dắt của cổ phiếu Vingroup và Vinhomes.</t>
+          <t>Margin có thể khuếch đại lợi nhuận, nhưng cũng khiến thua lỗ tăng nhanh, nhà đầu tư cần lưu ý để sử dụng đòn bẩy an toàn trong giao dịch chứng khoán.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 13:58:54 +0700</t>
+          <t>Thu, 07 May 2026 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/chung-khoan-vuot-dinh-5071073.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Nike chưa thể phục hồi với chiến lược 'Win Now'</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Sau 18 tháng triển khai chiến lược vực dậy "Chiến thắng ngay", thị phần của Nike tiếp tục sụt giảm khiến giới đầu tư Phố Wall mất dần kiên nhẫn.</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 01:10:00 +0700</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/nike-chua-the-phuc-hoi-voi-chien-luoc-win-now-5070718.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Lưu ý gì khi sử dụng margin trong chứng khoán?</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Margin có thể khuếch đại lợi nhuận, nhưng cũng khiến thua lỗ tăng nhanh, nhà đầu tư cần lưu ý để sử dụng đòn bẩy an toàn trong giao dịch chứng khoán.</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 00:01:00 +0700</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
         <is>
           <t>https://vnexpress.net/luu-y-gi-khi-su-dung-margin-trong-chung-khoan-5066173.html</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:50:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:45:00 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:34:00 +0700</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thanh toán QR xuyên biên giới tái định hình dòng chảy thương mại khu vực</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sự trỗi dậy của thanh toán QR xuyên biên giới không chỉ giải quyết triệt để bài toán ngoại tệ và tỷ giá cho hàng triệu du khách Việt mỗi năm, mà còn tạo đòn bẩy vĩ mô giúp các doanh nghiệp trong nước đón đầu dòng khách quốc tế, hội nhập sâu rộng vào nền kinh tế số khu vực.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:20:00 +0700</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thanh-toan-qr-xuyen-bien-gioi-tai-dinh-hinh-dong-chay-thuong-mai-khu-vuc-188260511152039861.chn</t>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Đầu tư Sài Gòn VRG sắp chi hơn 968 tỷ đồng trả cổ tức đợt 2/2025</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ngày 15/5/2026 tới đây, Đầu tư Sài Gòn VRG sẽ chốt danh sách cổ đông để thực hiện chi chi trả cổ tức đợt 2 năm 2025 bằng tiền mặt với tỷ lệ 40%. Thời gian thực hiện thanh toán 5/6/2026.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 14:09:00 +0700</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-sai-gon-vrg-sap-chi-hon-968-ty-dong-tra-co-tuc-dot-2-2025-188260511140113381.chn</t>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F88 chào bán thành công 300 tỷ đồng trái phiếu</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kết thúc đợt chào bán ngày 7/5/2026, F88 đã chào bán thành công 3 triệu trái phiếu tên F88BOND.PO.02, mã trái phiếu dự kiến là F88126015, qua đó huy động 300 tỷ đồng.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 14:06:00 +0700</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/f88-chao-ban-thanh-cong-300-ty-dong-trai-phieu-188260511140148051.chn</t>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Một cổ phiếu trên HOSE bất ngờ "trần cứng" 3 phiên liên tiếp, chuyện gì đang xảy ra?</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Không phải cái tên nổi bật trên thị trường, nhưng cổ phiếu này cũng từng gây chú ý hồi đầu năm với chuỗi tăng trần kéo dài hàng chục phiên liên tiếp.</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 11:31:00 +0700</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-tren-hose-bat-ngo-tran-cung-3-phien-lien-tiep-chuyen-gi-dang-xay-ra-188260511112953843.chn</t>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>“Gà đẻ trứng vàng” đồng loạt báo tin vui, CTCK dự báo MWG vượt kế hoạch lợi nhuận 2026</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Những chuỗi chủ lực của MWG là Điện Máy Xanh, Bách Hóa Xanh,… đều ghi nhận tín hiệu tích cực từ hoạt động kinh doanh.</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 11:04:00 +0700</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ga-de-trung-vang-dong-loat-bao-tin-vui-ctck-du-bao-mwg-vuot-ke-hoach-loi-nhuan-2026-188260511110426822.chn</t>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chứng khoán UP trở thành cổ đông lớn tại một công ty thực phẩm</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sau hai lần mua vào cổ phiếu FCC, Chứng khoán UP đã mua vào 830.000 cổ phiếu FCC, chiếm 13,83% Công ty cổ phần Liên hợp Thực phẩm.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:54:00 +0700</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-up-tro-thanh-co-dong-lon-tai-mot-cong-ty-thuc-pham-188260511101355489.chn</t>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>295 người sắp được mua cổ phiếu công ty chứng khoán của ông Nguyễn Duy Hưng với giá cực hời</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cổ phiếu SSI hiện giao dịch quanh vùng 28.500 đồng/cổ phiếu, tương đương vốn hóa hơn 71.000 tỷ đồng.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:53:00 +0700</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/295-nguoi-sap-duoc-mua-co-phieu-cong-ty-chung-khoan-cua-ong-nguyen-duy-hung-voi-gia-cuc-hoi-188260511105332872.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Loạt doanh nghiệp chốt quyền trả cổ tức trong tuần từ ngày 11/5-15/5</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Từ ngày 11/5-15/5, trên các sàn chứng khoán, có 37 doanh nghiệp chốt quyền trả cổ tức cho cổ đông bằng tiền mặt hoặc cổ phiếu.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:32:00 +0700</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loat-doanh-nghiep-chot-quyen-tra-co-tuc-trong-tuan-tu-ngay-11-5-15-5-188260511103244806.chn</t>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Giá vàng, bạc hồi phục mạnh, đã đến thời điểm giải ngân mạnh tay?</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dòng tiền sẽ sớm trở lại với vàng, một trong những tài sản dự trữ hàng đầu trong khi triển vọng thị trường bạc về cơ bản vẫn tích cực, nhu cầu cho kinh tế xanh hay trí tuệ nhân tạo là khá lớn.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:20:00 +0700</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gia-vang-bac-hoi-phuc-manh-da-den-thoi-diem-giai-ngan-manh-tay-188260511102011136.chn</t>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HDBank dự kiến phát hành 15.000 tỷ đồng trái phiếu</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HĐQT HDBank đã chấp thuận chủ trương phát hành riêng lẻ trái phiếu lần 1 năm 2026 với tổng mệnh giá phát hành tối đa 15.000 tỷ đồng.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 10:13:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hdbank-du-kien-phat-hanh-15000-ty-dong-trai-phieu-188260511101352153.chn</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VN-Index vượt đỉnh lịch sử, nhưng ba nhóm cổ phiếu này vẫn “ở dưới mặt đất” với mức giảm sâu trên 30%</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Theo Chứng khoán MB (MBS), dù VN-Index chính thức vượt mốc 1.900 điểm, thị trường vẫn cho thấy sự thiếu đồng thuận rõ rệt.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 08:56:00 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-nhung-ba-nhom-co-phieu-nay-van-o-duoi-mat-dat-voi-muc-giam-sau-tren-30-188260511085600698.chn</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Loạt thông tin tích cực xuất hiện, VN-Index sẽ sớm chinh phục mốc 2.000 điểm?</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chứng khoán ABS kỳ vọng VN-Index có thể sớm vượt vùng đỉnh cũ 1.920 điểm, sau đó tích lũy trên vùng đỉnh với sự lan tỏa của dòng tiền và thanh khoản gia tăng.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:05:00 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loat-thong-tin-tich-cuc-xuat-hien-vn-index-se-som-chinh-phuc-moc-2000-diem-188260510213551528.chn</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chứng khoán VIX triệu tập ĐHĐCĐ thường niên năm 2026</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ngày 27/5/2026 là ngày đăng ký cuối cùng để thực hiện quyền tham dự ĐHĐCĐ thường niên năm 2026 Chứng khoán VIX.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:03:00 +0700</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vix-trieu-tap-dhdcd-thuong-nien-nam-2026-188260510214351235.chn</t>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dòng vốn tỷ USD "chực chờ" đổ bộ Việt Nam, công ty chứng khoán bước vào cuộc đua mới</t>
+          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sau nâng hạng, ngành chứng khoán được kỳ vọng hưởng lợi từ dòng vốn ngoại, thanh khoản cải thiện và làn sóng huy động vốn mới. Tuy nhiên, áp lực lãi suất, chi phí vốn và cạnh tranh công nghệ cũng sẽ khiến cuộc chơi phân hóa mạnh hơn giữa các CTCK.</t>
+          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dong-von-ty-usd-chuc-cho-do-bo-viet-nam-cong-ty-chung-khoan-buoc-vao-cuoc-dua-moi-188260510213652315.chn</t>
+          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VN-Index vượt đỉnh lịch sử, tưởng ai cũng thắng lớn nhưng thực tế lại rất khác!</t>
+          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VN-Index trở lại vùng đỉnh lịch sử trên 1.900 điểm nhưng tài khoản của nhiều nhà đầu tư vẫn thua lỗ.</t>
+          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 18:19:00 +0700</t>
+          <t>Tue, 12 May 26 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-vuot-dinh-lich-su-tuong-ai-cung-thang-lon-nhung-thuc-te-lai-rat-khac-188260510182010552.chn</t>
+          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Đua nhau bán cổ phiếu Thế giới Di động</t>
+          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nhóm quỹ liên quan Dragon Capital đã bán ra 541.366 cổ phiếu MWG của Công ty CP Đầu tư Thế giới Di động, giảm sở hữu về 4,96% vốn điều lệ và không còn là cổ đông lớn. Tương tự, ông Đoàn Văn Hiểu Em - thành viên Hội đồng quản trị MWG - đăng ký bán ra 2 triệu cổ phiếu MWG để giảm sở hữu xuống 1,55 triệu cổ phiếu.</t>
+          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 18:16:00 +0700</t>
+          <t>Tue, 12 May 26 07:36:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dua-nhau-ban-co-phieu-the-gioi-di-dong-188260510181703105.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Góc nhìn chuyên gia: VN-Index khó tăng bền vững nếu không có một nhịp chỉnh lành mạnh trước</t>
+          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, chiến lược hợp lý lúc này là kiên nhẫn chờ nhịp điều chỉnh, phân bổ một phần vào cổ phiếu trụ để đi theo đà thị trường, phần còn lại tập trung vào cổ phiếu có câu chuyện riêng và nền tảng cơ bản rõ ràng.</t>
+          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 16:10:00 +0700</t>
+          <t>Tue, 12 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/goc-nhin-chuyen-gia-vn-index-kho-tang-ben-vung-neu-khong-co-mot-nhip-chinh-lanh-manh-truoc-188260510161025213.chn</t>
+          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nhóm cổ đông Âu Lạc tăng sở lên 6% vốn tại ACB</t>
+          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sau khi ái nữ của Chủ tịch Ngô Thu Thúy mua vào gần 8,4 cổ phiếu ACB trong phiên 4/5/2026, nhóm cổ đông Âu Lạc đã nâng tổng sở hữu lên 6% vốn tại ACB.</t>
+          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 10:59:00 +0700</t>
+          <t>Mon, 11 May 26 22:10:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-co-dong-au-lac-tang-so-len-6-von-tai-acb-188260510100859932.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Về Bộ Công an, Chủ tịch và Tổng Giám đốc FPT Telecom được phong cấp thượng tá</t>
+          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tháng 7/2025, Bộ Công an đã tiếp nhận quyền đại diện chủ sở hữu phần vốn nhà nước tại Công ty FPT Telecom từ Tổng công ty Đầu tư và Kinh doanh vốn Nhà nước (SCIC).</t>
+          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:26:00 +0700</t>
+          <t>Mon, 11 May 26 22:04:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ve-bo-cong-an-chu-tich-va-tong-giam-doc-fpt-telecom-duoc-phong-cap-thuong-ta-188260510002659875.chn</t>
+          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lịch chốt quyền cổ tức 11-15/5: 50 doanh nghiệp đồng loạt “lăn chốt”, Hòa Phát góp mặt, một ngân hàng chi gần 9.000 tỷ trả cổ tức</t>
+          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Loạt doanh nghiệp hot lăn chốt trong tuần này là Hoà Phát, Digiworld, LPB, Dược Hậu Giang,...</t>
+          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:06:00 +0700</t>
+          <t>Mon, 11 May 26 22:00:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lich-chot-quyen-co-tuc-11-15-5-50-doanh-nghiep-dong-loat-lan-chot-hoa-phat-gop-mat-mot-ngan-hang-chi-gan-9000-ty-tra-co-tuc-188260509215718878.chn</t>
+          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
         </is>
       </c>
     </row>
@@ -1381,103 +1381,103 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dấu hiệu tạo đỉnh ngắn hạn của VN-Index</t>
+          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Theo SHS, với việc chỉ số VN-Index, sau 5 tuần tăng liên tiếp từ vùng 1.600 điểm lên sát 1.900 điểm, thị trường đang đối mặt nguy cơ hình thành đỉnh ngắn hạn.</t>
+          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 10 May 26 00:05:00 +0700</t>
+          <t>Mon, 11 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-hieu-tao-dinh-ngan-han-cua-vn-index-188260509215903787.chn</t>
+          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung vẫn ở mức hấp dẫn, một số nhà băng như HDBank, NCB trả 8-9% một năm.</t>
+          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Mon, 11 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 26 15:34:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Thanh toán QR xuyên biên giới tái định hình dòng chảy thương mại khu vực</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Sự trỗi dậy của thanh toán QR xuyên biên giới không chỉ giải quyết triệt để bài toán ngoại tệ và tỷ giá cho hàng triệu du khách Việt mỗi năm, mà còn tạo đòn bẩy vĩ mô giúp các doanh nghiệp trong nước đón đầu dòng khách quốc tế, hội nhập sâu rộng vào nền kinh tế số khu vực.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://cafef.vn/thanh-toan-qr-xuyen-bien-gioi-tai-dinh-hinh-dong-chay-thuong-mai-khu-vuc-188260511152039861.chn</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 20:26:38 +0700</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 19:05:00 +0700</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>'Ấn Độ sẵn sàng hỗ trợ Việt Nam phát triển thị trường vốn'</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lãnh đạo Sàn giao dịch Chứng khoán Quốc gia Ấn Độ cho biết cơ quan này sẵn sàng hỗ trợ quá trình phát triển thị trường vốn của Việt Nam.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 18:37:56 +0700</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/an-do-san-sang-ho-tro-viet-nam-phat-trien-thi-truong-von-5071229.html</t>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Giá xăng tăng, dầu giảm</t>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Từ 15h ngày 7/5, giá xăng tăng, còn dầu diesel giảm theo đà biến động của thị trường năng lượng thế giới.</t>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 14:34:36 +0700</t>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-7-5-5068301.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chứng khoán vượt đỉnh</t>
+          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chứng khoán lập kỷ lục mới khi VN-Index đóng cửa trên 1.909 điểm với sự dẫn dắt của cổ phiếu Vingroup và Vinhomes.</t>
+          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 13:58:54 +0700</t>
+          <t>Fri, 08 May 2026 11:57:38 +0700</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-vuot-dinh-5071073.html</t>
+          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nike chưa thể phục hồi với chiến lược 'Win Now'</t>
+          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sau 18 tháng triển khai chiến lược vực dậy "Chiến thắng ngay", thị phần của Nike tiếp tục sụt giảm khiến giới đầu tư Phố Wall mất dần kiên nhẫn.</t>
+          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 01:10:00 +0700</t>
+          <t>Fri, 08 May 2026 07:36:44 +0700</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nike-chua-the-phuc-hoi-voi-chien-luoc-win-now-5070718.html</t>
+          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,130 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lưu ý gì khi sử dụng margin trong chứng khoán?</t>
+          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Margin có thể khuếch đại lợi nhuận, nhưng cũng khiến thua lỗ tăng nhanh, nhà đầu tư cần lưu ý để sử dụng đòn bẩy an toàn trong giao dịch chứng khoán.</t>
+          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 00:01:00 +0700</t>
+          <t>Fri, 08 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/luu-y-gi-khi-su-dung-margin-trong-chung-khoan-5066173.html</t>
+          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 20:26:38 +0700</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 19:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:50:00 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
+          <t>Tue, 12 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 07:36:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
+          <t>Tue, 12 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
+          <t>Mon, 11 May 26 22:10:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
+          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
+          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:53:00 +0700</t>
+          <t>Mon, 11 May 26 22:04:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
+          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
+          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
+          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:45:00 +0700</t>
+          <t>Mon, 11 May 26 22:00:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
+          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
+          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
+          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:34:00 +0700</t>
+          <t>Mon, 11 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
+          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
         </is>
       </c>
     </row>
@@ -1462,49 +1462,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thanh toán QR xuyên biên giới tái định hình dòng chảy thương mại khu vực</t>
+          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sự trỗi dậy của thanh toán QR xuyên biên giới không chỉ giải quyết triệt để bài toán ngoại tệ và tỷ giá cho hàng triệu du khách Việt mỗi năm, mà còn tạo đòn bẩy vĩ mô giúp các doanh nghiệp trong nước đón đầu dòng khách quốc tế, hội nhập sâu rộng vào nền kinh tế số khu vực.</t>
+          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:20:00 +0700</t>
+          <t>Mon, 11 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thanh-toan-qr-xuyen-bien-gioi-tai-dinh-hinh-dong-chay-thuong-mai-khu-vuc-188260511152039861.chn</t>
+          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Mon, 11 May 26 15:34:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+          <t>Fri, 08 May 2026 11:57:38 +0700</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+          <t>Fri, 08 May 2026 07:36:44 +0700</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+          <t>Fri, 08 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+          <t>Fri, 08 May 2026 02:00:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 20:26:38 +0700</t>
+          <t>Fri, 08 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
         </is>
       </c>
     </row>
@@ -2326,20 +2326,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 20:26:38 +0700</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Thu, 07 May 2026 19:05:00 +0700</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:50:00 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
+          <t>Tue, 12 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 07:36:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
+          <t>Tue, 12 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
+          <t>Mon, 11 May 26 22:10:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ông Phạm Nhật Vượng muốn làm dự án điện gần 158.000 tỷ đồng tại Điện Biên</t>
+          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VinEnergo sẽ triển khai dự án Nhà máy điện mặt trời Điện Biên 1 đã được phê duyệt chủ trương đầu tư, nhằm bổ sung nguồn điện sạch, ổn định cho hệ thống điện khu vực Tây .</t>
+          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:53:00 +0700</t>
+          <t>Mon, 11 May 26 22:04:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ong-pham-nhat-vuong-muon-lam-du-an-dien-gan-158000-ty-dong-tai-dien-bien-188260511155355596.chn</t>
+          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
         </is>
       </c>
     </row>
@@ -1462,49 +1462,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tiếp đà bán ròng hơn 1.000 tỷ phiên đầu tuần, khối ngoại "xả" mạnh cổ phiếu nào?</t>
+          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tại chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 133 tỷ đồng.</t>
+          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:45:00 +0700</t>
+          <t>Mon, 11 May 26 22:00:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tiep-da-ban-rong-hon-1000-ty-phien-dau-tuan-khoi-ngoai-xa-manh-co-phieu-nao-188260511153404318.chn</t>
+          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Không phải vàng, chuyên gia khuyến nghị tăng mạnh tỷ trọng tài sản này trong quý 2: 'Tôi đang giữ 40-50% danh mục'</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chuyên gia cho biết không còn ưu tiên vàng trong quý 2 mà duy trì tỷ trọng cao ở cổ phiếu, tăng tỷ trọng tiền gửi để phòng thủ trước nguy cơ “thiên nga đen” của thị trường.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 15:34:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khong-phai-vang-chuyen-gia-khuyen-nghi-tang-manh-ty-trong-tai-san-nay-trong-quy-2-toi-dang-giu-40-50-danh-muc-188260511153322807.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+          <t>Fri, 08 May 2026 11:57:38 +0700</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+          <t>Fri, 08 May 2026 07:36:44 +0700</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+          <t>Fri, 08 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+          <t>Fri, 08 May 2026 02:00:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+          <t>Fri, 08 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
         </is>
       </c>
     </row>
@@ -2299,76 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+          <t>Thu, 07 May 2026 20:26:38 +0700</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 20:26:38 +0700</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
           <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Kinh tế Nga khó hưởng lợi lớn từ giá dầu cao</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Xung đột với Ukraine và các lệnh trừng phạt mới của phương Tây có thể khiến Nga khó hưởng lợi từ giá dầu tăng cao hai tháng qua.</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 19:05:00 +0700</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/kinh-te-nga-kho-huong-loi-lon-tu-gia-dau-cao-5071115.html</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Mức quan trọng</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Liên kết</t>
         </is>
       </c>
@@ -458,162 +463,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
         </is>
       </c>
     </row>
@@ -625,22 +648,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -652,22 +678,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -679,22 +708,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
@@ -706,49 +738,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -760,22 +798,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -787,22 +828,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -814,22 +858,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -841,22 +888,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -868,49 +918,55 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -922,22 +978,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
@@ -949,49 +1008,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1068,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1098,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1128,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>Tue, 12 May 26 09:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1158,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>Tue, 12 May 26 08:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1188,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>Tue, 12 May 26 00:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
         </is>
       </c>
     </row>
@@ -1138,211 +1218,235 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>Mon, 11 May 26 22:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
+          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
+          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:50:00 +0700</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
+          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
@@ -1354,49 +1458,55 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1518,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1548,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -1462,130 +1578,145 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
@@ -1597,184 +1728,205 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
@@ -1786,211 +1938,235 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>Tue, 12 May 26 07:36:00 +0700</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>Mon, 11 May 26 22:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>Mon, 11 May 26 22:04:00 +0700</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2178,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2208,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2238,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2268,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2298,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2328,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2358,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2388,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2418,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2448,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2478,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2508,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: Sớm giao chỉ tiêu tăng trưởng cho các địa phương, doanh nghiệp Nhà nước</t>
+          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phó thủ tướng Nguyễn Văn Thắng yêu cầu sớm giao chỉ tiêu cho các địa phương, doanh nghiệp Nhà nước để hoàn thành mục tiêu tăng trưởng kinh tế giai đoạn 2026-2030.</t>
+          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 20:26:38 +0700</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/pho-thu-tuong-som-giao-chi-tieu-tang-truong-cho-cac-dia-phuong-doanh-nghiep-nha-nuoc-5071240.html</t>
+          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -558,17 +558,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tòa án Mỹ bác bỏ thuế 10% của ông Trump</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tòa án Thương mại Quốc tế Mỹ (CIT) phán quyết bác bỏ thuế nhập khẩu 10% của Mỹ, nhưng chỉ chặn áp dụng với bang Washington và 2 doanh nghiệp nhỏ.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 07:36:44 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,29 +636,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/toa-an-my-bac-bo-thue-10-cua-ong-trump-5071311.html</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
@@ -708,17 +708,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
@@ -738,17 +738,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 26 12:03:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,29 +756,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,29 +936,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng sau đợt trả cổ tức</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hoàn tất phân phối gần 186,3 triệu cổ phiếu trả cổ tức cho cổ đông, Hoa Sen Group tăng vốn vượt 8.000 tỷ đồng.</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:50:00 +0700</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1146,29 +1146,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hoa-sen-group-tang-von-vuot-8000-ty-dong-sau-dot-tra-co-tuc-188260512095023654.chn</t>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chủ tịch AgriS (SBT) gia tăng sở hữu khi doanh nghiệp bước vào chu kỳ tăng trưởng mới</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bà Đặng Huỳnh Ức My – Chủ tịch HĐQT của CTCP Thành Thành Công – Biên Hòa (AgriS, Hose: SBT) vừa thông báo đăng ký mua 42.755.629 cổ phiếu SBT trong tháng 5, nâng tổng sở hữu lên 13,93%.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 08:00:00 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-agris-sbt-gia-tang-so-huu-khi-doanh-nghiep-buoc-vao-chu-ky-tang-truong-moi-188260512070625123.chn</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Một quỹ đầu tư bất ngờ "bắt đáy" FPT</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Theo SGI Capital, sự lệch pha của dòng tiền đang mở ra cơ hội ở những doanh nghiệp có kết quả kinh doanh tích cực, định giá rẻ nhưng bị thị trường bỏ qua.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 00:01:00 +0700</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-quy-dau-tu-bat-ngo-bat-day-fpt-188260511215609792.chn</t>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biến động nhân sự cấp cao nhiều ngân hàng</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sacombank OCB, Eximbank có thay đổi nhân sự cấp cao ở vị trí tổng giám đốc, phó tổng Giám đốc, thành viên hội đồng quản trị, thành viên ban kiểm soát.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:00:00 +0700</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/bien-dong-nhan-su-cap-cao-nhieu-ngan-hang-188260511220028497.chn</t>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1393,30 +1393,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hãng máy lạnh duy nhất trên sàn lãi kỷ lục</t>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nhờ đẩy mạnh chương trình bán hàng, chính sách giá và chiết khấu, Nagakawa ghi nhận doanh thu và lợi nhuận kỷ lục trong quý đầu năm.</t>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 11:57:38 +0700</t>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-may-lanh-duy-nhat-tren-san-lai-ky-luc-5071398.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
         </is>
       </c>
     </row>
@@ -1428,17 +1428,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
         </is>
       </c>
     </row>
@@ -1608,17 +1608,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,29 +1656,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2028,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Doanh nghiệp thuộc Bộ Công an phát thông báo quan trọng</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Doanh nghiệp này có 2 cổ đông lớn là Bộ Công an nắm hơn 50% vốn và Tập đoàn FPT nắm 45,7% cổ phần.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 07:36:00 +0700</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-thuoc-bo-cong-an-phat-thong-bao-quan-trong-188260512073651516.chn</t>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Một cổ phiếu "họ" Gelex bị tự doanh CTCK bán ròng đột biến trong phiên đầu tuần</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 430 tỷ đồng trên sàn HOSE.</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:10:00 +0700</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-co-phieu-ho-gelex-bi-tu-doanh-ctck-ban-rong-dot-bien-trong-phien-dau-tuan-188260511221057448.chn</t>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nhóm nhà đầu tư VinaCapital rời ghế cổ đông lớn tại TNG</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quỹ đầu tư Cổ phiếu Cổ tức năng động VinaCapital vừa bán ra toàn bộ 219.200 cổ phiếu TNG, qua đó giảm tỷ lệ sở hữu của cả nhóm VinaCapital xuống còn 4,9262% và rời ghế cổ đông lớn tại TNG.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 11 May 26 22:04:00 +0700</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhom-nha-dau-tu-vinacapital-roi-ghe-co-dong-lon-tai-tng-188260511220414411.chn</t>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,29 +2316,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Tue, 12 May 26 09:52:00 +0700</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -2448,17 +2448,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vinpearl hợp tác với ba 'ông lớn' lữ hành Ấn Độ</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vinpearl ký hợp tác với Thomas Cook India, SOTC Travel và MakeMyTrip nhằm khai thác thị trường 1,47 tỷ dân, đưa Việt Nam trở thành điểm đến ưu tiên của du khách Ấn Độ.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 10:00:00 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinpearl-hop-tac-voi-ba-ong-lon-lu-hanh-an-do-5071401.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'Cần nâng nợ thuế cấm xuất cảnh người bỏ địa chỉ kinh doanh lên 5 triệu đồng'</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chuyên gia đề xuất nâng ngưỡng nợ thuế bị tạm hoãn xuất cảnh với cá nhân bỏ địa chỉ kinh doanh lên 5 triệu đồng, thay vì 1 triệu như dự kiến của Bộ Tài chính.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 06:00:00 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/can-nang-no-thue-cam-xuat-canh-nguoi-bo-dia-chi-kinh-doanh-len-5-trieu-dong-5070760.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc 'chai lì' với sự đe dọa của Mỹ</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lợi thế quy mô sản xuất và chuỗi cung ứng đa dạng khiến các hãng xuất khẩu Trung Quốc không còn quá lo ngại trước chính sách của Mỹ như năm ngoái.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 02:00:00 +0700</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,7 +2526,97 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-chai-li-voi-su-de-doa-cua-my-5070924.html</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 12:32:52 +0700</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -643,22 +643,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,29 +666,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
@@ -708,17 +708,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
@@ -738,17 +738,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 12:03:00 +0700</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Wed, 13 May 26 12:03:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,29 +906,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,29 +1086,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
+          <t>Tue, 12 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1146,29 +1146,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 26 14:40:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1176,29 +1176,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
+          <t>Tue, 12 May 26 11:39:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Tue, 12 May 26 11:18:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>VN-Index lên 1.915 điểm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Fri, 08 May 2026 15:54:08 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Cổ phiếu PC1 giảm mạnh</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Fri, 08 May 2026 15:21:50 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,59 +1386,59 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Fri, 08 May 2026 13:09:09 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
         </is>
       </c>
     </row>
@@ -1608,17 +1608,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,29 +1776,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,29 +2016,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
+          <t>Tue, 12 May 26 15:53:00 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
+          <t>Tue, 12 May 26 15:32:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
+          <t>Tue, 12 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
+          <t>Tue, 12 May 26 14:39:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
+          <t>Tue, 12 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 26 13:46:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Tue, 12 May 26 10:51:00 +0700</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Tue, 12 May 26 10:44:00 +0700</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian chào bán 25 triệu trái phiếu chuyển đổi</t>
+          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CII kéo dài thời gian nhận tiền mua trái phiếu tới chậm nhất 17 giờ ngày 25/6/2026 thay vì 17 giờ ngày 2/6/2026 như trước đó.</t>
+          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 09:52:00 +0700</t>
+          <t>Tue, 12 May 26 10:10:00 +0700</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cii-keo-dai-thoi-gian-chao-ban-25-trieu-trai-phieu-chuyen-doi-188260512094932988.chn</t>
+          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Thu, 14 May 2026 01:18:51 GMT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,29 +486,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Thu, 14 May 2026 00:26:34 GMT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,29 +516,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Wed, 13 May 2026 19:00:32 +0700</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
         </is>
       </c>
     </row>
@@ -558,17 +558,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,29 +576,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Wed, 13 May 26 17:30:00 +0700</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,569 +636,569 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 12:03:00 +0700</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Mon, 11 May 2026 12:47:52 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Mon, 11 May 2026 09:53:09 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Giá vàng lao dốc sau khi Mỹ từ chối đề xuất phản hồi của Iran</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Gi#225; v#224;ng thế giới giảm mạnh v#224;o đầu giờ phi#234;n s#225;ng nay (11/5) tại thị trường ch#226;u #193;, sau khi c#243; tin Mỹ từ chối đề xuất m#224; Iran đưa ra để phản hồi kế hoạch h#242;a b#236;nh của Mỹ...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Mon, 11 May 2026 00:44:18 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://vneconomy.vn/gia-vang-lao-doc-sau-khi-my-tu-choi-de-xuat-phan-hoi-cua-iran.htm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Dấu ấn kinh tế thế giới tuần 2-9/5/2026: Đồn đoán về Nhật Bản can thiệp tỷ giá, Mỹ chờ câu trả lời từ Iran</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Trong tuần n#224;y, thị trường t#224;i ch#237;nh to#224;n cầu tin rằng nh#224; chức tr#225;ch Nhật Bản đ#227; c#243; đợt can thiệp thứ hai v#224;o thị trường ngoại hối để bảo vệ tỷ gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Sun, 10 May 2026 00:34:52 GMT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://vneconomy.vn/dau-an-kinh-te-the-gioi-tuan-2-952026-don-doan-ve-nhat-ban-can-thiep-ty-gia-my-cho-cau-tra-loi-tu-iran.htm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Sun, 10 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>SP 500 đóng cửa cao kỷ lục sau báo cáo việc làm, giá dầu chững lại</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ S#225;u (8/5), khi số liệu việc l#224;m khả quan hơn dự b#225;o mang lại cho nh#224; đầu tư sự y#234;n t#226;m về sức khỏe của nền kinh tế...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Sat, 09 May 2026 01:12:23 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/sp-500-dong-cua-cao-ky-luc-sau-bao-cao-viec-lam-gia-dau-chung-lai.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Phiên 12/5: Khối ngoại vẫn bán ròng hơn 800 tỷ đồng, cổ phiếu nào bị "xả" mạnh nhất?</t>
+          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu VIC với giá trị 196 tỷ đồng, xếp sau là VRE với 118 tỷ đồng.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:45:00 +0700</t>
+          <t>Sat, 09 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-12-5-khoi-ngoai-van-ban-rong-hon-800-ty-dong-co-phieu-nao-bi-xa-manh-nhat-188260512151657978.chn</t>
+          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PVTrans sắp phát hành gần 47 triệu cổ phiếu trả cổ tức</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PVTrans lên kế hoạch phát hành gần 47 triệu cổ phiếu trả cổ tức cho cổ đông với tỷ lệ thực hiện quyền 100:10. Nếu thành công, vốn điều lệ của doanh nghiệp sẽ lên mức 5.169 tỷ đồng.</t>
+          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:40:00 +0700</t>
+          <t>Fri, 08 May 2026 21:48:02 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pvtrans-sap-phat-hanh-gan-47-trieu-co-phieu-tra-co-tuc-18826051214334115.chn</t>
+          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank sắp phát hành 59,5 triệu cổ phiếu trả cổ tức</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chứng khoán VietinBank dự kiến phát hành 59,55 triệu cổ phiếu trả cổ tức, tương ứng tỷ lệ thực hiện quyền 100:28.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:39:00 +0700</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-vietinbank-sap-phat-hanh-595-trieu-co-phieu-tra-co-tuc-18826051210395094.chn</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xu hướng chủ đạo vẫn là tăng trưởng, chuyên gia tiết lộ “mỏ vàng” trên sàn chứng khoán</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Theo chuyên gia AAS, việc mua được “hàng tốt” ở “mức giá thấp” là lợi thế lớn nhất để có biên lợi nhuận vượt trội trong tương lai.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 11:18:00 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,29 +1266,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/xu-huong-chu-dao-van-la-tang-truong-chuyen-gia-tiet-lo-mo-vang-tren-san-chung-khoan-18826051211180719.chn</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Wed, 13 May 2026 17:37:35 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VN-Index lên 1.915 điểm</t>
+          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dù hơn 58% mã giảm giá, chứng khoán vẫn đóng cửa ở mức cao kỷ lục 1.915 điểm nhờ sự hỗ trợ của cổ phiếu nhóm Vingroup và ngân hàng.</t>
+          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:54:08 +0700</t>
+          <t>Wed, 13 May 2026 17:12:43 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-len-1-915-diem-5071587.html</t>
+          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 giảm mạnh</t>
+          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cổ phiếu PC1 chạm giá sàn và chốt phiên giảm 5% với thanh khoản lớn.</t>
+          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 15:21:50 +0700</t>
+          <t>Wed, 13 May 26 17:09:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-pc1-giam-manh-5071548.html</t>
+          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CEO Hóa chất Đức Giang: Sẽ kế thừa ý chí, tầm nhìn của ông Đào Hữu Huyền</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ông Lưu Bách Đạt, Tổng giám đốc Hóa chất Đức Giang, hứa dàn lãnh đạo mới sẽ vận hành tốt doanh nghiệp, kế thừa ý chí, tầm nhìn của cựu Chủ tịch Đào Hữu Huyền.</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 13:09:09 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,157 +1416,157 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-hoa-chat-duc-giang-se-ke-thua-y-chi-tam-nhin-cua-ong-dao-huu-huyen-5071498.html</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Wed, 13 May 26 12:03:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
         </is>
       </c>
     </row>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -1638,175 +1638,175 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -1818,55 +1818,55 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Tue, 12 May 2026 19:38:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
         </is>
       </c>
     </row>
@@ -1878,25 +1878,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -1938,437 +1938,437 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 16:44:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trao quyền chọn tài sản mã hóa niêm yết cho các sàn giao dịch</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Về phía quyền lợi và nghĩa vụ chuyên môn, các tổ chức sẽ có một quyền rất quan trọng là quyền lựa chọn tài sản mã hóa để niêm yết và giao dịch theo thông lệ quốc tế, song lãnh đạo UBCKNN khuyến khích sự thận trọng, ưu tiên các tài sản có tính thanh khoản cao và phổ biến để hạn chế rủi ro cho thị trường.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:53:00 +0700</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://cafef.vn/trao-quyen-chon-tai-san-ma-hoa-niem-yet-cho-cac-san-giao-dich-188260512155331827.chn</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gần 800 triệu cổ phiếu Hoà Phát sắp về tài khoản nhà đầu tư</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sau đợt chia này, lượng cổ phiếu lưu hành của Hoà Phát sẽ tăng lên hơn 8,4 tỷ cổ phiếu - tương đương dân số toàn cầu.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:32:00 +0700</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-800-trieu-co-phieu-hoa-phat-sap-ve-tai-khoan-nha-dau-tu-188260512153307166.chn</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lừa đảo trực tuyến hơn 8.000 tỷ đồng năm 2025: Chuyên gia chỉ ra ‘bí kíp’ thúc đẩy niểm tin tài chính số trong kỷ nguyên AI</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Đại tá Nguyễn Hồng Quân, Phó Cục trưởng Cục An ninh mạng và phòng, chống tội phạm sử dụng công nghệ cao, Phó Chủ tịch Liên minh Niềm tin số, nêu bật "nhiệm vụ" chung để nâng cao niềm tin số tài chính trong kỷ nguyên AI.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 15:18:00 +0700</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lua-dao-truc-tuyen-hon-8000-ty-dong-nam-2025-chuyen-gia-chi-ra-bi-kip-thuc-day-niem-tin-tai-chinh-so-trong-ky-nguyen-ai-188260512151809266.chn</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cổ đông liên quan Thành viên HĐQT Vinasun muốn thoái sạch vốn</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tư vấn Kim Ngưu vừa đăng ký bán ra toàn bộ hơn 3,4 triệu cổ phiếu VNS nhằm mục đích cơ cấu danh mục đầu tư. Nếu giao dịch thành công, doanh nghiệp này sẽ rời ghế cổ đông tại Vinasun.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:39:00 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-dong-lien-quan-thanh-vien-hdqt-vinasun-muon-thoai-sach-von-188260512143443164.chn</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính: Sớm nhất trong quý 3 có thể vận hành thị trường tài sản mã hóa</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thứ trưởng Bộ Tài chính Nguyễn Đức Chi chia sẻ những thông tin quan trọng về tiến trình xây dựng thị trường tài sản mã hóa tại Việt Nam</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 14:38:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://cafef.vn/thu-truong-bo-tai-chinh-som-nhat-trong-quy-3-co-the-van-hanh-thi-truong-tai-san-ma-hoa-188260512143753521.chn</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Doanh nghiệp dược hàng đầu Việt Nam chính thức về tay “gã khổng lồ” Trung Quốc</t>
+          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Giá trị giao dịch ước tính vào khoảng 6.000 tỷ đồng.</t>
+          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 13:46:00 +0700</t>
+          <t>Sun, 10 May 2026 03:40:28 GMT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://cafef.vn/doanh-nghiep-duoc-hang-dau-viet-nam-chinh-thuc-ve-tay-ga-khong-lo-trung-quoc-188260512134636898.chn</t>
+          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Sun, 10 May 2026 03:02:35 GMT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gemadept chốt ngày chi hơn 938 tỷ đồng trả cổ tức năm 2025</t>
+          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ngày 22/5/2026 tới đây, Gemadept sẽ chốt danh sách cổ đông để thực hiện chi trả cổ tức năm 2025 bằng tiền mặt với tỷ lệ 22%. Ngày thanh toán dự kiến 29/5/2026.</t>
+          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:51:00 +0700</t>
+          <t>Sat, 09 May 2026 12:40:53 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gemadept-chot-ngay-chi-hon-938-ty-dong-tra-co-tuc-nam-2025-188260512094843159.chn</t>
+          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sẽ đưa Blockchain, Big data, AI vào hoạt động giám sát thị trường; sớm nhất trong quý 3 sẽ vận hành thị trường tài sản mã hoá chính thức tại Việt Nam</t>
+          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN cho biết thời gian tới sẽ đưa công nghệ chuỗi khối (blockchain), dữ liệu lớn (big data) và trí tuệ nhân tạo (AI) vào hoạt động giám sát thị trường thông qua hệ thống thông tin tổng thể và kho dữ liệu tập trung.</t>
+          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:44:00 +0700</t>
+          <t>Sat, 09 May 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://cafef.vn/se-dua-blockchain-big-data-ai-vao-hoat-dong-giam-sat-thi-truong-som-nhat-trong-quy-3-se-van-hanh-thi-truong-tai-san-ma-hoa-chinh-thuc-tai-viet-nam-188260512104430607.chn</t>
+          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lãnh đạo doanh nghiệp hé lộ lý do đề xuất xây 2 toà tháp tưởng niệm giữa trung tâm Hà Nội</t>
+          <t>“Lệch pha” ngày càng rõ, VN-Index áp sát ngưỡng 1920 điểm, cổ phiếu đỏ la liệt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lý giải việc điều chỉnh quy hoạch, ông Đinh Ngọc Dương cho rằng mô hình “công viên nhà tang lễ” là hướng tiếp cận mới nhằm đáp ứng nhu cầu tổ chức tang lễ văn minh hơn tại đô thị lớn, với nhiều không gian xanh và trải nghiệm tiễn biệt mang tính nhân văn hơn.</t>
+          <t>VN-Index nh#237;ch th#234;m 6,36 điểm trong phi#234;n h#244;m nay tiến l#234;n mức 1915,37 điểm. Chỉ “nhấn” th#234;m ch#250;t nữa l#224; chỉ số c#243; đỉnh cao lịch sử mới v#224; điều n#224;y ho#224;n to#224;n khả thi nếu VIC, VHM tiếp tục mạnh. Tuy nhi#234;n nh#224; đầu tư c#243; hưởng lợi hay kh#244;ng lại l#224; vấn đề kh#225;c.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 10:10:00 +0700</t>
+          <t>Fri, 08 May 2026 08:49:38 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://cafef.vn/lanh-dao-doanh-nghiep-he-lo-ly-do-de-xuat-xay-2-toa-thap-tuong-niem-giua-trung-tam-ha-noi-188260512100853346.chn</t>
+          <t>https://vneconomy.vn/lech-pha-ngay-cang-ro-vn-index-ap-sat-nguong-1920-diem-co-phieu-do-la-liet.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,29 +2406,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,29 +2436,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
@@ -2538,17 +2538,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,37 +2586,2137 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>VnExpress Business</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Công ty điện mặt trời của Trung Nam lỗ gần 1.000 tỷ đồng</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Trung Nam Thuận Nam, chủ đầu tư nhà máy điện mặt trời 450 MW ở Khánh Hòa, năm ngoái lỗ trước thuế 970 tỷ đồng, nâng lỗ lũy kế lên trên 1.800 tỷ.</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Fri, 08 May 2026 12:32:52 +0700</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/cong-ty-dien-mat-troi-cua-trung-nam-lo-gan-1-000-ty-dong-5071456.html</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 18:10:03 +0700</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 17:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 16:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 13:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 10:49:47 +0700</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 09:41:32 +0700</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 08:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 18:17:00 +0700</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 26 17:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CafeF</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 26 16:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Nhịp đập Thị trường 12/05: Áp lực bán hạ nhiệt, VN-Index trở lại vùng 1,900</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Thị trường thót tim với pha giảm mạnh của VIC trong ATC, tuy vậy, mọi thứ nhanh chóng qua đi. Kết phiên, VN-Index dừng ở 1,901.1 điểm. HNX-Index có một phiên tích cực khi tăng tới hơn 5 điểm, tương ứng mức 2%.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 16:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1205-ap-luc-ban-ha-nhiet-vn-index-tro-lai-vung-1900-1636-1441235.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Phân tích kỹ thuật phiên chiều 12/05: Tiếp tục điều chỉnh</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VN-Index tiếp tục điều chỉnh sau khi không thể vượt qua đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index tiếp tục tăng điểm và đang kiểm tra lại đường SMA 50 ngày trong bối cảnh khối lượng giao dịch trồi sụt thất thường.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 13:08:50 +0700</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1205-tiep-tuc-dieu-chinh-585-1441309.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Vietstock</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UBCKNN yêu cầu CTCK giám sát việc nhân viên "phím hàng" trên mạng xã hội</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>UBCKNN vừa có văn bản gửi các công ty chứng khoán, yêu cầu tăng cường rà soát và giám sát hoạt động của người hành nghề chứng khoán trên mạng xã hội, trong bối cảnh các nội dung phân tích, khuyến nghị đầu tư ngày càng phổ biến trên các nền tảng mạng xã hội.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 12:52:33 +0700</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>http://vietstock.vn/2026/05/ubcknn-yeu-cau-ctck-giam-sat-viec-nhan-vien-phim-hang-tren-mang-xa-hoi-143-1441306.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 03:13:57 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 03:03:32 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 03:02:08 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VnExpress Business</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>VNeconomy</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 09:36:08 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/blog-chung-khoan-co-hoi-ngay-cang-mong-1291631.htm</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,52 +1153,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt tăng hợp tác thương mại, hàng không</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thủ tướng Sri Lanka muốn doanh nghiệp Việt mở rộng hợp tác trong lĩnh vực thương mại, chế biến thực phẩm, logistics, hàng không và du lịch.</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 21:48:02 +0700</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-tuong-sri-lanka-muon-doanh-nghiep-viet-tang-hop-tac-thuong-mai-hang-khong-5071709.html</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,29 +1266,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:37:35 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
+          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
+          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:12:43 +0700</t>
+          <t>Wed, 13 May 2026 17:37:35 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
+          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
+          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
+          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:09:00 +0700</t>
+          <t>Wed, 13 May 2026 17:12:43 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
+          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
         </is>
       </c>
     </row>
@@ -1398,17 +1398,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Wed, 13 May 26 17:09:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 12:03:00 +0700</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -1608,17 +1608,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Wed, 13 May 26 12:03:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
         </is>
       </c>
     </row>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,29 +1776,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 19:38:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,29 +1866,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Tue, 12 May 2026 19:38:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cổ phiếu Sacombank (STB) tăng cận trần sau biến động nhân sự cấp cao</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cổ phiếu STB của Sacombank bất ngờ trở thành tâm điểm hút dòng tiền từ các nhà đầu tư trong phiên 12/5, khi tăng cận trần – lập đỉnh giá lịch sử mới ngay sau thông tin ngân hàng bổ nhiệm nhân sự cấp cao.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:44:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-sacombank-stb-tang-can-tran-sau-bien-dong-nhan-su-cap-cao-188260512160131532.chn</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -3673,22 +3673,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Đại diện UBCKNN: Khi nào có sàn giao dịch tài sản mã hoá đầu tiên phụ thuộc hoàn toàn vào năng lực của doanh nghiệp</t>
+          <t>Nhịp đập Thị trường 12/05: Áp lực bán hạ nhiệt, VN-Index trở lại vùng 1,900</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Liên quan tới lộ trình triển khai thị trường tài sản mã hóa chính thức, ông Hòa cho biết tiến độ hiện nay không phụ thuộc vào cơ quan quản lý mà phụ thuộc chủ yếu vào năng lực của doanh nghiệp.</t>
+          <t>Thị trường thót tim với pha giảm mạnh của VIC trong ATC, tuy vậy, mọi thứ nhanh chóng qua đi. Kết phiên, VN-Index dừng ở 1,901.1 điểm. HNX-Index có một phiên tích cực khi tăng tới hơn 5 điểm, tương ứng mức 2%.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 16:53:00 +0700</t>
+          <t>Tue, 12 May 2026 16:52:00 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,29 +3696,29 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dai-dien-ubcknn-bao-gio-co-san-giao-dich-tai-san-ma-hoa-dau-tien-phu-thuoc-hoan-toan-vao-nang-luc-cua-doanh-nghiep-188260512165347989.chn</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1205-ap-luc-ban-ha-nhiet-vn-index-tro-lai-vung-1900-1636-1441235.htm</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 12/05: Áp lực bán hạ nhiệt, VN-Index trở lại vùng 1,900</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Thị trường thót tim với pha giảm mạnh của VIC trong ATC, tuy vậy, mọi thứ nhanh chóng qua đi. Kết phiên, VN-Index dừng ở 1,901.1 điểm. HNX-Index có một phiên tích cực khi tăng tới hơn 5 điểm, tương ứng mức 2%.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:52:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1205-ap-luc-ban-ha-nhiet-vn-index-tro-lai-vung-1900-1636-1441235.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Phân tích kỹ thuật phiên chiều 12/05: Tiếp tục điều chỉnh</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>VN-Index tiếp tục điều chỉnh sau khi không thể vượt qua đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index tiếp tục tăng điểm và đang kiểm tra lại đường SMA 50 ngày trong bối cảnh khối lượng giao dịch trồi sụt thất thường.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 13:08:50 +0700</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1205-tiep-tuc-dieu-chinh-585-1441309.htm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 12/05: Tiếp tục điều chỉnh</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VN-Index tiếp tục điều chỉnh sau khi không thể vượt qua đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index tiếp tục tăng điểm và đang kiểm tra lại đường SMA 50 ngày trong bối cảnh khối lượng giao dịch trồi sụt thất thường.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 13:08:50 +0700</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1205-tiep-tuc-dieu-chinh-585-1441309.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>UBCKNN yêu cầu CTCK giám sát việc nhân viên "phím hàng" trên mạng xã hội</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UBCKNN vừa có văn bản gửi các công ty chứng khoán, yêu cầu tăng cường rà soát và giám sát hoạt động của người hành nghề chứng khoán trên mạng xã hội, trong bối cảnh các nội dung phân tích, khuyến nghị đầu tư ngày càng phổ biến trên các nền tảng mạng xã hội.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:52:33 +0700</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ubcknn-yeu-cau-ctck-giam-sat-viec-nhan-vien-phim-hang-tren-mang-xa-hoi-143-1441306.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,29 +3966,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,29 +4056,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,29 +4116,29 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,29 +4236,29 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 02:31:04 GMT</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,29 +4356,29 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,29 +4386,29 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,29 +4446,29 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Sun, 10 May 2026 03:13:57 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,29 +4476,29 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Sun, 10 May 2026 03:03:32 GMT</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4518,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
+          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:13:57 GMT</t>
+          <t>Sun, 10 May 2026 03:02:08 GMT</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4536,29 +4536,29 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
+          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:03:32 GMT</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -4566,29 +4566,29 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:08 GMT</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -4608,17 +4608,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -4626,95 +4626,35 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Fri, 08 May 2026 09:36:08 GMT</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>1</v>
       </c>
       <c r="F141" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Fri, 08 May 2026 09:36:08 GMT</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" t="inlineStr">
         <is>
           <t>https://vneconomy.vn/blog-chung-khoan-co-hoi-ngay-cang-mong-1291631.htm</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -1158,17 +1158,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
+          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
+          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:16:00 +0700</t>
+          <t>Thu, 14 May 26 10:47:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1176,29 +1176,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
+          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:00:00 +0700</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Thu, 14 May 2026 03:07:13 GMT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:37:35 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:12:43 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
+          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
+          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:09:00 +0700</t>
+          <t>Wed, 13 May 2026 17:37:35 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
+          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Wed, 13 May 2026 17:12:43 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 26 17:09:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -1608,17 +1608,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 12:03:00 +0700</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Wed, 13 May 26 12:03:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
         </is>
       </c>
     </row>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Wed, 13 May 26 09:50:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 26 09:31:00 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
         </is>
       </c>
     </row>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Wed, 13 May 26 09:29:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,29 +1776,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 26 08:17:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,29 +1866,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
+          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
+          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 19:38:00 +0700</t>
+          <t>Wed, 13 May 26 00:10:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
+          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 2026 19:38:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Tue, 12 May 26 18:24:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2028,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,29 +2106,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:40:28 GMT</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:35 GMT</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
+          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
+          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 12:40:53 GMT</t>
+          <t>Sun, 10 May 2026 03:40:28 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
+          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
+          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 02:00:00 GMT</t>
+          <t>Sun, 10 May 2026 03:02:35 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
+          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>“Lệch pha” ngày càng rõ, VN-Index áp sát ngưỡng 1920 điểm, cổ phiếu đỏ la liệt</t>
+          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VN-Index nh#237;ch th#234;m 6,36 điểm trong phi#234;n h#244;m nay tiến l#234;n mức 1915,37 điểm. Chỉ “nhấn” th#234;m ch#250;t nữa l#224; chỉ số c#243; đỉnh cao lịch sử mới v#224; điều n#224;y ho#224;n to#224;n khả thi nếu VIC, VHM tiếp tục mạnh. Tuy nhi#234;n nh#224; đầu tư c#243; hưởng lợi hay kh#244;ng lại l#224; vấn đề kh#225;c.</t>
+          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 08 May 2026 08:49:38 GMT</t>
+          <t>Sat, 09 May 2026 12:40:53 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,59 +2346,59 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lech-pha-ngay-cang-ro-vn-index-ap-sat-nguong-1920-diem-co-phieu-do-la-liet.htm</t>
+          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Sat, 09 May 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,29 +2406,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
@@ -2448,17 +2448,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,29 +2466,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,29 +2616,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:10:03 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
+          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
+          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:20:45 +0700</t>
+          <t>Wed, 13 May 2026 18:10:03 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,29 +2706,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Wed, 13 May 2026 17:20:45 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:47:00 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Wed, 13 May 2026 16:47:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
         </is>
       </c>
     </row>
@@ -3108,17 +3108,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 13:03:11 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
@@ -3168,17 +3168,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
+          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
+          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:49:47 +0700</t>
+          <t>Wed, 13 May 2026 13:03:11 +0700</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 10:49:47 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 09:41:32 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 09:41:32 +0700</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:00:00 +0700</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:00:00 +0700</t>
+          <t>Wed, 13 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3438,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,29 +3486,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 18:17:00 +0700</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 2026 18:17:00 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK liên tục bán ra hàng trăm tỷ đồng một cổ phiếu họ Gelex</t>
+          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 164 tỷ đồng trên HOSE.</t>
+          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:48:00 +0700</t>
+          <t>Tue, 12 May 26 17:52:00 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-lien-tuc-ban-ra-hang-tram-ty-dong-mot-co-phieu-ho-gelex-188260512174822907.chn</t>
+          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,22 +1993,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VN-Index trở lại mốc 1.900 điểm, dòng tiền tìm đến cổ phiếu bất động sản</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán ngày 12-5 ghi nhận nhịp hồi phục đáng chú ý khi VN-Index lấy lại mốc 1.900 điểm sau phiên rung lắc mạnh đầu ngày</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,29 +2016,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-tro-lai-moc-1900-diem-dong-tien-tim-den-co-phieu-bat-dong-san-188260512175253.chn</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,29 +2076,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,29 +2106,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Sun, 10 May 2026 03:40:28 GMT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
+          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:40:28 GMT</t>
+          <t>Sun, 10 May 2026 03:02:35 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
+          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
+          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
+          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:35 GMT</t>
+          <t>Sat, 09 May 2026 12:40:53 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
+          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
+          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
+          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 12:40:53 GMT</t>
+          <t>Sat, 09 May 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,37 +2346,37 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
+          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 02:00:00 GMT</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Nhịp đập Thị trường 14/05: Tạo mẫu hình “chữ V” ngay đầu phiên</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>VN-Index mở đầu phiên 14/05 vô cùng rung lắc khi có lúc điều chỉnh về 1,885 điểm nhưng lập tức hồi phục trở về mốc 1,900 điểm.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Thu, 14 May 2026 10:55:07 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,29 +2406,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-tao-mau-hinh-chu-v-ngay-dau-phien-1636-1442403.htm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,29 +2436,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,29 +2616,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,29 +2676,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:10:03 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
+          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
+          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:20:45 +0700</t>
+          <t>Wed, 13 May 2026 18:10:03 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Wed, 13 May 2026 17:20:45 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:47:00 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Wed, 13 May 2026 16:47:00 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3078,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3138,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,29 +3156,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 13:03:11 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
+          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
+          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:49:47 +0700</t>
+          <t>Wed, 13 May 2026 13:03:11 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 10:49:47 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 09:41:32 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 09:41:32 +0700</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,29 +3336,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
+          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:00:00 +0700</t>
+          <t>Wed, 13 May 26 09:34:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
+          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
         </is>
       </c>
     </row>
@@ -3378,17 +3378,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:00:00 +0700</t>
+          <t>Wed, 13 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
         </is>
       </c>
     </row>
@@ -3498,17 +3498,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 00:04:00 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Tue, 12 May 26 21:23:00 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 18:17:00 +0700</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kiểm soát hoạt động của người hành nghề môi giới chứng khoán trên mạng xã hội</t>
+          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cần rà soát hoạt động của môi giới chứng khoán nhằm bảo đảm không thực hiện những hoạt động khuyến nghị, tư vấn vượt quá phạm vi.</t>
+          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 17:52:00 +0700</t>
+          <t>Tue, 12 May 2026 18:17:00 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://cafef.vn/kiem-soat-hoat-dong-cua-nguoi-hanh-nghe-moi-gioi-chung-khoan-tren-mang-xa-hoi-188260512175208987.chn</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
         </is>
       </c>
     </row>
@@ -3853,22 +3853,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 12/05: Tiếp tục điều chỉnh</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VN-Index tiếp tục điều chỉnh sau khi không thể vượt qua đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index tiếp tục tăng điểm và đang kiểm tra lại đường SMA 50 ngày trong bối cảnh khối lượng giao dịch trồi sụt thất thường.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 13:08:50 +0700</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1205-tiep-tuc-dieu-chinh-585-1441309.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,29 +4056,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+          <t>Mon, 11 May 2026 02:31:04 GMT</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,29 +4326,29 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Sun, 10 May 2026 03:13:57 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
+          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
+          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:13:57 GMT</t>
+          <t>Sun, 10 May 2026 03:03:32 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
+          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
+          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:03:32 GMT</t>
+          <t>Sun, 10 May 2026 03:02:08 GMT</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,29 +4506,29 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
+          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
+          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
+          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:08 GMT</t>
+          <t>Sun, 10 May 2026 07:00:07 +0700</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
+          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
         </is>
       </c>
     </row>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Sat, 09 May 2026 19:58:16 +0700</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Sat, 09 May 2026 13:00:55 +0700</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -4596,65 +4596,35 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Fri, 08 May 2026 09:36:08 GMT</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>1</v>
       </c>
       <c r="F140" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Fri, 08 May 2026 09:36:08 GMT</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" t="inlineStr">
         <is>
           <t>https://vneconomy.vn/blog-chung-khoan-co-hoi-ngay-cang-mong-1291631.htm</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
+          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
+          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 01:18:51 GMT</t>
+          <t>Fri, 15 May 2026 00:40:12 GMT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,29 +486,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
+          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
+          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:26:34 GMT</t>
+          <t>Thu, 14 May 2026 16:37:00 +0700</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,29 +516,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
+          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:32 +0700</t>
+          <t>Thu, 14 May 2026 14:34:59 +0700</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,29 +546,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
+          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
+          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:10 +0700</t>
+          <t>Thu, 14 May 2026 06:50:35 GMT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,29 +576,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
+          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
+          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
+          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:30:00 +0700</t>
+          <t>Thu, 14 May 2026 06:47:13 GMT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,29 +606,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Thu, 14 May 2026 01:18:51 GMT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
+          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
+          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 03:47:17 GMT</t>
+          <t>Thu, 14 May 2026 00:26:34 GMT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,29 +666,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
+          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
+          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:04:51 GMT</t>
+          <t>Wed, 13 May 2026 19:00:32 +0700</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:57:58 GMT</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,29 +726,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
+          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
+          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:18:43 GMT</t>
+          <t>Wed, 13 May 26 17:30:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,29 +756,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
+          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 14:06:05 GMT</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 01:19:45 GMT</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:02:03 GMT</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:01:27 GMT</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:47:52 GMT</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:53:09 GMT</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Giá vàng lao dốc sau khi Mỹ từ chối đề xuất phản hồi của Iran</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm mạnh v#224;o đầu giờ phi#234;n s#225;ng nay (11/5) tại thị trường ch#226;u #193;, sau khi c#243; tin Mỹ từ chối đề xuất m#224; Iran đưa ra để phản hồi kế hoạch h#242;a b#236;nh của Mỹ...</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:44:18 GMT</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,29 +996,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/gia-vang-lao-doc-sau-khi-my-tu-choi-de-xuat-phan-hoi-cua-iran.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dấu ấn kinh tế thế giới tuần 2-9/5/2026: Đồn đoán về Nhật Bản can thiệp tỷ giá, Mỹ chờ câu trả lời từ Iran</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trong tuần n#224;y, thị trường t#224;i ch#237;nh to#224;n cầu tin rằng nh#224; chức tr#225;ch Nhật Bản đ#227; c#243; đợt can thiệp thứ hai v#224;o thị trường ngoại hối để bảo vệ tỷ gi#225; đồng y#234;n...</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:34:52 GMT</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dau-an-kinh-te-the-gioi-tuan-2-952026-don-doan-ve-nhat-ban-can-thiep-ty-gia-my-cho-cau-tra-loi-tu-iran.htm</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MSCI và FTSE khác nhau thế nào trong nâng hạng thị trường chứng khoán?</t>
+          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cùng là nâng hạng thị trường chứng khoán, nhưng MSCI và FTSE có tiêu chí, tầm ảnh hưởng và sức hấp dẫn khác nhau.</t>
+          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 00:02:00 +0700</t>
+          <t>Mon, 11 May 2026 12:47:52 GMT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msci-va-ftse-khac-nhau-the-nao-trong-nang-hang-thi-truong-chung-khoan-5070886.html</t>
+          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SP 500 đóng cửa cao kỷ lục sau báo cáo việc làm, giá dầu chững lại</t>
+          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ S#225;u (8/5), khi số liệu việc l#224;m khả quan hơn dự b#225;o mang lại cho nh#224; đầu tư sự y#234;n t#226;m về sức khỏe của nền kinh tế...</t>
+          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 01:12:23 GMT</t>
+          <t>Mon, 11 May 2026 09:53:09 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sp-500-dong-cua-cao-ky-luc-sau-bao-cao-viec-lam-gia-dau-chung-lai.htm</t>
+          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CEO Nvidia, Apple sẽ cùng ông Trump đến Trung Quốc</t>
+          <t>Giá vàng lao dốc sau khi Mỹ từ chối đề xuất phản hồi của Iran</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp, trong đó có CEO Nvidia, Apple, Qualcomm, Citigroup và Boeing sẽ cùng Tổng thống Mỹ đến Trung Quốc tuần tới.</t>
+          <t>Gi#225; v#224;ng thế giới giảm mạnh v#224;o đầu giờ phi#234;n s#225;ng nay (11/5) tại thị trường ch#226;u #193;, sau khi c#243; tin Mỹ từ chối đề xuất m#224; Iran đưa ra để phản hồi kế hoạch h#242;a b#236;nh của Mỹ...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 00:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:44:18 GMT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1146,37 +1146,37 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-nvidia-apple-se-cung-ong-trump-den-trung-quoc-5071620.html</t>
+          <t>https://vneconomy.vn/gia-vang-lao-doc-sau-khi-my-tu-choi-de-xuat-phan-hoi-cua-iran.htm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
+          <t>Giá vàng tuần này có thể tăng</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
+          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:47:00 +0700</t>
+          <t>Mon, 11 May 2026 00:00:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
+          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
+          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
+          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:16:00 +0700</t>
+          <t>Fri, 15 May 26 08:50:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
+          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
+          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
+          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 03:07:13 GMT</t>
+          <t>Fri, 15 May 26 08:22:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
+          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
+          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
+          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:00:00 +0700</t>
+          <t>Fri, 15 May 26 07:26:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
+          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Fri, 15 May 26 07:25:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Fri, 15 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Fri, 15 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 2026 18:48:56 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
+          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
+          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:37:35 +0700</t>
+          <t>Thu, 14 May 2026 18:32:44 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
+          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
+          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
+          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:12:43 +0700</t>
+          <t>Thu, 14 May 2026 10:18:48 GMT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
+          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
+          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
+          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:09:00 +0700</t>
+          <t>Thu, 14 May 2026 09:36:21 GMT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Thu, 14 May 2026 16:06:50 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Thu, 14 May 2026 15:30:47 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Thu, 14 May 26 13:36:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Thu, 14 May 2026 12:30:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Thu, 14 May 26 10:47:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FPT báo lãi tháng 4/2026 tăng 21%</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FPT cho biết khối lượng đơn hàng ký mới tại thị trường nước ngoài đã tăng vọt 30% so với cùng kỳ.</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 12:03:00 +0700</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fpt-bao-lai-thang-4-2026-tang-21-188260513120329893.chn</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chủ tịch Đoàn Nguyên Đức gom thêm cổ phiếu HAG</t>
+          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ông Đoàn Nguyên Đức- Chủ tịch HĐQT Hoàng Anh Gia Lai, đã mua vào 4 triệu cổ phiếu HAG bằng phương thức khớp lệnh trên sàn, qua đó nâng sở hữu lên 25,09%.</t>
+          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:50:00 +0700</t>
+          <t>Thu, 14 May 2026 03:07:13 GMT</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-doan-nguyen-duc-gom-them-co-phieu-hag-188260513092755881.chn</t>
+          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dabaco chia cổ tức tổng tỷ lệ 15%</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dabaco sẽ trả cổ tức 3% bằng tiền, tức 300 đồng/cổ phiếu và 12% bằng cổ phiếu. Dự kiến thực hiện trong quý II/2026.</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:31:00 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dabaco-chia-co-tuc-tong-ty-le-15-188260513092502696.chn</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vinhomes phát hành liên tiếp 2 lô trái phiếu trị giá 3.000 tỷ đồng</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ngày 11/5 vừa qua, Vinhomes đã phát hành liên tiếp 02 lô trái phiếu trong cùng ngày 11/5/2026 với tổng giá trị huy động 3.000 tỷ đồng.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:29:00 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,29 +1776,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vinhomes-phat-hanh-lien-tiep-2-lo-trai-phieu-tri-gia-3000-ty-dong-188260513092558919.chn</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo Imexpharm bán cổ phiếu trong cùng một phiên</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tổng giám đốc Trần Thị Đào cùng 2 Phó Tổng giám đốc và Kế toán trưởng Imexpharm đồng loạt bán cổ phiếu IMP trong cùng một phiên.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 08:17:00 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nhieu-lanh-dao-imexpharm-ban-co-phieu-trong-cung-mot-phien-188260513072238693.chn</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,29 +1866,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SACOMBANK lập kỷ lục: Từ “bàn tay vàng” của ông Nguyễn Đức Thuỵ đến pha đổi tên đậm chất “phong thuỷ”</t>
+          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sự xuất hiện của ông Nguyễn Đức Thuỵ tại SACOMBANK từ cuối năm 2025 kéo theo hàng loạt thay đổi mang tính chiến lược đối với ngân hàng.</t>
+          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:10:00 +0700</t>
+          <t>Wed, 13 May 2026 17:37:35 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,29 +1896,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/sacombank-lap-ky-luc-tu-ban-tay-vang-cua-ong-nguyen-duc-thuy-den-pha-doi-ten-dam-chat-phong-thuy-188260512232819282.chn</t>
+          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Thêm công ty chứng khoán hạ dự phóng VN-Index năm 2026</t>
+          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CTCK này cho rằng nền tảng vĩ mô ổn định, triển vọng tăng trưởng lợi nhuận tích cực và định giá còn tương đối hấp dẫn vẫn là cơ sở để VN-Index duy trì xu hướng tăng trong năm 2026.</t>
+          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 17:12:43 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/them-cong-ty-chung-khoan-ha-du-phong-vn-index-nam-2026-188260512213008592.chn</t>
+          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 12/05: Khối ngoại và tự doanh lại cùng bán ròng, FPT tiếp tục thành tâm điểm</t>
+          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trong phiên thị trường chứng khoán bật tăng trong phiên chiều đầy hứng khởi, khối tự doanh công ty chứng khoán và nhà đầu tư nước ngoài lại đồng thuận bán ròng.</t>
+          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 19:38:00 +0700</t>
+          <t>Wed, 13 May 26 17:09:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1205-khoi-ngoai-va-tu-doanh-lai-cung-ban-rong-fpt-tiep-tuc-thanh-tam-diem-830-1441753.htm</t>
+          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gần 7 triệu cổ phiếu sang tay, STB lập đỉnh</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sau pha điều chỉnh ở phiên trước, thị trường chứng khoán hôm nay (12/5) hồi phục trở lại khi VN-Index lấy lại mốc 1.900 điểm. Dòng tiền tập trung vào nhóm ngân hàng và dầu khí, trong đó STB trở thành tâm điểm với mức tăng cận trần, lập đỉnh giá lịch sử mới.</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 18:24:00 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gan-7-trieu-co-phieu-sang-tay-stb-lap-dinh-188260512174905008.chn</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,29 +2016,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Wed, 13 May 26 16:14:00 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,29 +2076,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Wed, 13 May 26 13:53:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:40:28 GMT</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nhà đầu tư cá nhân mua ròng 1.200 tỷ phiên cuối tuần, tiếp tục mạnh tay gom FPT</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n tuần qua mua r#242;ng 1221,4 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 809,9 tỷ đồng.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:35 GMT</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-1200-ty-phien-cuoi-tuan-tiep-tuc-manh-tay-gom-fpt.htm</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cuộc đua tăng vốn: Các công ty chứng khoán tăng thêm 100.000 tỷ trong năm 2026</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tổng quy m#244; tăng vốn to#224;n ng#224;nh năm 2026 ước t#237;nh c#243; thể tiếp tục duy tr#236; ở mức cao tương đương 2025 (~100 ngh#236;n tỷ đồng).</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 12:40:53 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cuoc-dua-tang-von-cac-cong-ty-chung-khoan-tang-them-100000-ty-trong-nam-2026.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thị trường chứng khoán Việt Nam  2025 và triển vọng 2026</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n (TTCK) Việt Nam trong năm 2025 trải qua nhiều phi#234;n tăng giảm đan xen nhưng nh#236;n chung duy tr#236; hoạt động ổn định v#224; ghi nhận những kết quả nổi bật nhờ sự hỗ trợ t#237;ch cực từ nền tảng kinh tế vĩ m#244; trong nước v#224; sự chỉ đạo, điều h#224;nh chủ động, linh hoạt, quyết liệt của Ch#237;nh phủ, Thủ tướng Ch#237;nh phủ.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 02:00:00 GMT</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,127 +2346,127 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-chung-khoan-viet-nam-2025-va-trien-vong-2026.htm</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 11:24:00 +0700</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 14/05: Tạo mẫu hình “chữ V” ngay đầu phiên</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VN-Index mở đầu phiên 14/05 vô cùng rung lắc khi có lúc điều chỉnh về 1,885 điểm nhưng lập tức hồi phục trở về mốc 1,900 điểm.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:55:07 +0700</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-tao-mau-hinh-chu-v-ngay-dau-phien-1636-1442403.htm</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Sun, 10 May 2026 03:40:28 GMT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Fri, 15 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Fri, 15 May 26 07:28:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Fri, 15 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dưa địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Fri, 15 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 2026 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,29 +2616,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 2026 21:42:38 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Thu, 14 May 2026 14:16:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,29 +2676,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Thu, 14 May 2026 18:27:22 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,29 +2706,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
+          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:10:03 +0700</t>
+          <t>Thu, 14 May 2026 15:48:25 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
+          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
+          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:20:45 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
+          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Thu, 14 May 26 15:36:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 13/05: Khối ngoại liên tục bán ròng, VN-Index cheo leo tại mốc 1,900 điểm</t>
+          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 2.73 điểm (-0.14%), xuống mức 1,898.37 điểm; HNX-Index tăng 1.34 điểm (+0.53%), lên mức 254.62 điểm. Độ rộng toàn thị trường với sắc đỏ lấn lướt khi bên bán có 353 mã giảm và bên mua có 335 mã tăng. Tương tự, sắc đỏ lấn lướt trong rổ VN30 với 15 mã giảm, 13 mã tăng và 2 mã tham chiếu.</t>
+          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:47:00 +0700</t>
+          <t>Thu, 14 May 2026 08:29:36 GMT</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1305-khoi-ngoai-lien-tuc-ban-rong-vn-index-cheo-leo-tai-moc-1900-diem-1636-1441856.htm</t>
+          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Thu, 14 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Thu, 14 May 2026 14:32:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Thu, 14 May 2026 13:02:11 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Thu, 14 May 2026 05:07:25 GMT</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,29 +3036,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
@@ -3168,17 +3168,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 13/05: Tín hiệu trái chiều xuất hiện</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VN-Index giảm điểm khi tiếp tục kiểm tra lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). HNX-Index có phiên tăng điểm thứ 3 liên tiếp và  đang nằm trên đường Middle của Bollinger Bands.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 13:03:11 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1305-tin-hieu-trai-chieu-xuat-hien-585-1442015.htm</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anpha Petrol nói gì sau khi cổ phiếu tăng trần 5 phiên liền?</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Giai đoạn 04-08/05, cổ phiếu CTCP Tập đoàn Dầu khí An Pha (HOSE: ASP) tăng trần liên tiếp dẫn đến phải giải trình với Sở Giao dịch Chứng khoán TPHCM (HOSE). Ngay trong ngày 08/05, Doanh nghiệp đã đưa ra văn bản chính thức.</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:49:47 +0700</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/anpha-petrol-noi-gi-sau-khi-co-phieu-tang-tran-5-phien-lien-830-1441846.htm</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
@@ -3258,17 +3258,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
@@ -3288,17 +3288,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FID nhận ‘combo’ cảnh báo, kiểm soát</t>
+          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sở Giao dịch Chứng khoán Hà Nội (HNX) vừa ban hành các quyết định liên quan đến việc xử lý vi phạm đối với CTCP Đầu tư và Phát triển Doanh nghiệp Việt Nam (HNX: FID).</t>
+          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 09:41:32 +0700</t>
+          <t>Wed, 13 May 2026 18:10:03 +0700</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/fid-nhan-8216combo8217-canh-bao-kiem-soat-830-1441642.htm</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 17:20:45 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc muốn bán 15 triệu cổ phiếu AgriS</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bà Huỳnh Bích Ngọc đăng ký bán ra 15 triệu cổ phiếu SBT của AgriS nhằm mục đích cơ cấu danh mục đầu tư.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 09:34:00 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ba-huynh-bich-ngoc-muon-ban-15-trieu-co-phieu-agris-188260513092914186.chn</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 13/05</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:00:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1305-830-1441641.htm</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>13/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:00:00 +0700</t>
+          <t>Wed, 13 May 26 16:11:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1305-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1441766.htm</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3438,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tiền lớn chọn lọc, chuyên gia chỉ tên nhóm cổ phiếu xếp hạng cao trên thị trường</t>
+          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dòng tiền tiếp tục ưu tiên các cổ phiếu có sức mạnh vượt trội, chuyên gia ABS đã tiến hành lọc ra các nhóm ngành và cổ phiếu có mức độ mạnh nhất so với thị trường chung.</t>
+          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:05:00 +0700</t>
+          <t>Wed, 13 May 26 15:50:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,29 +3486,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tien-lon-chon-loc-chuyen-gia-chi-ten-nhom-co-phieu-xep-hang-cao-tren-thi-truong-188260512213550455.chn</t>
+          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VN-Index áp sát đỉnh lịch sử, CTCK cảnh báo kịch bản “xanh vỏ đỏ lòng”</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VNDirect khuyến nghị chiến lược giao dịch linh hoạt, tận dụng cơ hội chốt lời quanh vùng đỉnh và xem xét giải ngân trở lại nếu chỉ số về vùng hỗ trợ quanh 1.820 điểm.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:04:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vn-index-ap-sat-dinh-lich-su-ctck-canh-bao-kich-ban-xanh-vo-do-long-188260512212732752.chn</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
@@ -3528,17 +3528,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán vốn nghìn tỷ bị phạt nặng</t>
+          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chứng khoán Bảo Minh bị xử phạt tổng cộng 780.000.000 đồng do hàng loạt sai phạm.</t>
+          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 00:02:00 +0700</t>
+          <t>Wed, 13 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-cong-ty-chung-khoan-von-nghin-ty-bi-phat-nang-188260512212628665.chn</t>
+          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
         </is>
       </c>
     </row>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
@@ -3588,17 +3588,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quy mô tài sản truyền thống lên tới 1,6 nghìn tỷ USD, Việt Nam có tiềm năng lớn mã hóa tài sản thực</t>
+          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chuyên gia tài chính cấp cao đến từ Singapore cho rằng khung pháp lý và sự ủng hộ từ Chính phủ sẽ tiếp tục đóng vai trò quan trọng trong quá trình phát triển của thị trường tài sản mã hóa.</t>
+          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 12 May 26 21:23:00 +0700</t>
+          <t>Wed, 13 May 26 15:20:00 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-mo-tai-san-truyen-thong-len-toi-16-nghin-ty-usd-viet-nam-co-tiem-nang-lon-ma-hoa-tai-san-thuc-188260512212342162.chn</t>
+          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Wed, 13 May 26 15:18:00 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vietstock Daily 13/05/2026: Thận trọng trở lại</t>
+          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VN-Index hồi phục nhưng khối lượng giao dịch sụt giảm xuống dưới mức trung bình 20 ngày cho thấy tâm lý thận trọng của nhà đầu tư. Chỉ báo Stochastic Oscillator đã cắt xuống đường signal trong vùng overbought nên tình trạng rung lắc nhiều khả năng sẽ còn tiếp diễn trong những phiên tới.</t>
+          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 18:17:00 +0700</t>
+          <t>Wed, 13 May 26 14:41:00 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,29 +3666,29 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-13052026-than-trong-tro-lai-1636-1441621.htm</t>
+          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 12/05: Áp lực bán hạ nhiệt, VN-Index trở lại vùng 1,900</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thị trường thót tim với pha giảm mạnh của VIC trong ATC, tuy vậy, mọi thứ nhanh chóng qua đi. Kết phiên, VN-Index dừng ở 1,901.1 điểm. HNX-Index có một phiên tích cực khi tăng tới hơn 5 điểm, tương ứng mức 2%.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:52:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1205-ap-luc-ban-ha-nhiet-vn-index-tro-lai-vung-1900-1636-1441235.htm</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
@@ -3888,17 +3888,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -3918,17 +3918,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,29 +4056,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,29 +4356,29 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,29 +4386,29 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Xu thế dòng tiền: VN-Index lên đỉnh cao lịch sử mới, thị trường vẫn kém vui</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Thị trường tuần đầu th#225;ng 5 đ#227; x#225;c lập đỉnh cao lịch sử mới của VN-Index khi đ#243;ng cửa tại 1915,37 điểm. Chỉ số cũng ghi nhận tuần tăng thứ 7 li#234;n tiếp. D#249; vậy hiện tượng “xanh vỏ đỏ l#242;ng” gần như trọn tuần khi kiến nh#224; đầu tư kh#244;ng c#243; trải nghiệm t#237;ch cực.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:13:57 GMT</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/xu-the-dong-tien-vn-index-len-dinh-cao-lich-su-moi-thi-truong-van-kem-vui.htm</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rủi ro với mặt bằng chung cổ phiếu giảm đi đáng kể</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Yếu tố quan trọng nhất m#224; thị trường thế giới đang tr#244;ng chờ l#224; triển vọng Mỹ v#224; Iran sớm đạt được thỏa thuận về việc chấm dứt xung đột, rất khả thi...</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:03:32 GMT</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-voi-mat-bang-chung-co-phieu-giam-di-dang-ke.htm</t>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VN-Index đã vượt đỉnh, nhưng vẫn cần thêm đồng thuận để hoàn toàn bật lên khỏi vùng 1900 – 1920</t>
+          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường tuần từ 11-15/5/2026.</t>
+          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:02:08 GMT</t>
+          <t>Mon, 11 May 2026 02:31:04 GMT</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-da-vuot-dinh-nhung-van-can-them-dong-thuan-de-hoan-toan-bat-len-khoi-vung-1900-1920.htm</t>
+          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4518,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kinh tế Việt - Ấn: Rộng cửa đón tỷ USD</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chuyến thăm Ấn Độ của Tổng Bí thư, Chủ tịch nước Tô Lâm mở ra dư địa thúc đẩy thương mại song phương, hướng tới mục tiêu 25 tỷ USD vào năm 2030.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:00:07 +0700</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kinh-te-viet-an-rong-cua-don-ty-usd-5072031.html</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Việt Nam chi gần tỷ USD nhập hạt điều trong một tháng</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Là nước xuất khẩu điều nhân lớn nhất thế giới, nhưng riêng tháng 4, các doanh nghiệp Việt đã chi gần 943 triệu USD để nhập khẩu điều thô.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 19:58:16 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/viet-nam-chi-gan-ty-usd-nhap-hat-dieu-trong-mot-thang-5071916.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Có nên bán nhà Hà Nội khi giá đã giảm 1 tỷ đồng?</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Theo chuyên gia, thị trường bất động sản không trả tiền theo "ký ức" mà theo khả năng, cần đưa ra giá bán phù hợp với thanh khoản thực tế.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 13:00:55 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -4596,37 +4596,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-nen-ban-nha-ha-noi-khi-gia-da-giam-1-ty-dong-5071849.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Blog chứng khoán: Cơ hội ngày càng mỏng</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>T#226;m l#253; ch#225;n nản d#226;ng cao hơn trong phi#234;n cuối tuần bất chấp VNI thực sự đ#243;ng cửa ở đỉnh cao lịch sử mới. Độ rộng rất ti#234;u cực v#224; cổ phiếu bị #233;p xuống bi#234;n độ kh#225; rộng trong phi#234;n x#225;c nhận b#234;n b#225;n đ#227; tạo #225;p lực đủ lớn.</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Fri, 08 May 2026 09:36:08 GMT</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-co-hoi-ngay-cang-mong-1291631.htm</t>
+          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dragon Capital: Giá cổ phiếu còn dưa địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức. Thời gian thực hiện trong quý III/2026.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:50:00 +0700</t>
+          <t>Fri, 15 May 26 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
+          <t>https://cafef.vn/hodeco-se-phat-hanh-gan-30-trieu-co-phieu-tra-co-tuc-188260515100220542.chn</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
+          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
+          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:22:00 +0700</t>
+          <t>Fri, 15 May 26 08:50:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
+          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
         </is>
       </c>
     </row>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
+          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
+          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:26:00 +0700</t>
+          <t>Fri, 15 May 26 08:22:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
+          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
+          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
+          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:25:00 +0700</t>
+          <t>Fri, 15 May 26 07:26:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
+          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
+          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
+          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:08:00 +0700</t>
+          <t>Fri, 15 May 26 07:25:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
+          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
+          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:05:00 +0700</t>
+          <t>Fri, 15 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
+          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
+          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
+          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:48:56 +0700</t>
+          <t>Fri, 15 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
+          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
+          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
+          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:32:44 +0700</t>
+          <t>Thu, 14 May 2026 18:48:56 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
+          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
+          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
+          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:18:48 GMT</t>
+          <t>Thu, 14 May 2026 18:32:44 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
+          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
+          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
+          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:36:21 GMT</t>
+          <t>Thu, 14 May 2026 10:18:48 GMT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
+          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:06:50 +0700</t>
+          <t>Thu, 14 May 2026 09:36:21 GMT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Thu, 14 May 2026 16:06:50 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
+          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
+          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:30:47 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
+          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
+          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 13:36:00 +0700</t>
+          <t>Thu, 14 May 2026 15:30:47 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
+          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
+          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
+          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 12:30:00 +0700</t>
+          <t>Thu, 14 May 26 13:36:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
+          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
+          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
+          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:47:00 +0700</t>
+          <t>Thu, 14 May 2026 12:30:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
+          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
+          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
+          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:16:00 +0700</t>
+          <t>Thu, 14 May 26 10:47:00 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
+          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 03:07:13 GMT</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
+          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
+          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:00:00 +0700</t>
+          <t>Thu, 14 May 2026 03:07:13 GMT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
+          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:37:35 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDJ ký hợp đồng kiểm toán mới kỳ vọng khắc phục tình trạng cổ phiếu bị cảnh báo</t>
+          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CTCP IDJ Việt Nam (HNX: IDJ) vừa báo cáo cơ quan quản lý về các biện pháp và lộ trình khắc phục tình trạng cổ phiếu bị cảnh báo, với trọng tâm là việc ký hợp đồng kiểm toán Báo cáo tài chính năm 2025 với Công ty TNHH Kiểm toán và Tư vấn UHY (UHY). Công ty cho biết sẽ thực hiện việc Công bố Báo cáo tài chính 2025 đã được kiểm toán đúng theo các quy định của pháp luật để sớm đưa cổ phiếu ra khỏi diện bị cảnh báo</t>
+          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:12:43 +0700</t>
+          <t>Wed, 13 May 2026 17:37:35 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/idj-ky-hop-dong-kiem-toan-moi-ky-vong-khac-phuc-tinh-trang-co-phieu-bi-canh-bao-830-1442032.htm</t>
+          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSIAM bắt tay 2 định chế tài chính, mở rộng cơ hội đầu tư và tài trợ vốn giữa Nhật Bản và Việt Nam</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phát huy chuyên môn, mạng lưới và nguồn lực của từng bên, SSIAM, CCIX và DCI sẽ chủ động tìm kiếm, cấu trúc và triển khai các cơ hội đầu tư và tài trợ vốn trung, dài hạn, góp phần thúc đẩy tăng trưởng bền vững cho doanh nghiệp Việt Nam và nền kinh tế.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 13:53:00 +0700</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ssiam-bat-tay-2-dinh-che-tai-chinh-mo-rong-co-hoi-dau-tu-va-tai-tro-von-giua-nhat-ban-va-viet-nam-188260513135311114.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,29 +2346,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Mon, 11 May 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Mon, 11 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,29 +2406,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Sun, 10 May 2026 03:40:28 GMT</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,37 +2436,37 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
+          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
+          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:40:28 GMT</t>
+          <t>Fri, 15 May 2026 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
+          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
         </is>
       </c>
     </row>
@@ -3643,22 +3643,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp “lạ” trả cổ tức kỷ lục 60% bằng tiền mặt</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Đây là công ty duy nhất trên sàn bán các loại kềm.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 14:41:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-la-tra-co-tuc-ky-luc-60-bang-tien-mat-18826051314410115.chn</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3678,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,29 +3756,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
@@ -3918,17 +3918,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,29 +4056,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,29 +4296,29 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,29 +4326,29 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+          <t>Mon, 11 May 2026 02:31:04 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,29 +4476,29 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+          <t>Mon, 11 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4518,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Sun, 10 May 2026 17:40:04 +0700</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
         </is>
       </c>
     </row>
@@ -4548,53 +4548,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Sun, 10 May 2026 12:48:02 +0700</t>
         </is>
       </c>
       <c r="E138" t="n">
         <v>1</v>
       </c>
       <c r="F138" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>VnExpress Business</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" t="inlineStr">
         <is>
           <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -468,17 +468,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
+          <t>Ba cổ phiếu ngân hàng tiềm năng tăng giá tốt nhất trong bối cảnh lãi suất cao đe dọa NIM, nợ xấu tăng</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
+          <t>VnDirect kỳ vọng NIM to#224;n ng#224;nh sẽ dần cải thiện v#224;o cuối năm khi mặt bằng l#227;i suất c#243; xu hướng hạ nhiệt v#224; hoạt động thu hồi nợ thường t#237;ch cực hơn trong nửa cuối năm. Theo đ#243;, kỳ vọng NIM to#224;n ng#224;nh năm 2026 sẽ duy tr#236; quanh mức 3,1%.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 00:40:12 GMT</t>
+          <t>Fri, 15 May 2026 04:42:52 GMT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,29 +486,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
+          <t>https://vneconomy.vn/ba-co-phieu-ngan-hang-tiem-nang-tang-gia-tot-nhat-trong-boi-canh-lai-suat-cao-de-doa-nim-no-xau-tang.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
+          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
+          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:37:00 +0700</t>
+          <t>Fri, 15 May 2026 00:40:12 GMT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,29 +516,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giá xăng, dầu cùng giảm</t>
+          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
+          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:34:59 +0700</t>
+          <t>Thu, 14 May 2026 16:37:00 +0700</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,29 +546,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
+          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:50:35 GMT</t>
+          <t>Thu, 14 May 2026 14:34:59 +0700</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
+          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
+          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:47:13 GMT</t>
+          <t>Thu, 14 May 2026 06:50:35 GMT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
+          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
+          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
+          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 01:18:51 GMT</t>
+          <t>Thu, 14 May 2026 06:47:13 GMT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
+          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:26:34 GMT</t>
+          <t>Thu, 14 May 2026 01:18:51 GMT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,29 +666,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
+          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
+          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:32 +0700</t>
+          <t>Thu, 14 May 2026 00:26:34 GMT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
+          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
+          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
+          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:10 +0700</t>
+          <t>Wed, 13 May 2026 19:00:32 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,29 +726,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
+          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:30:00 +0700</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,29 +756,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Wed, 13 May 26 17:30:00 +0700</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,29 +786,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 03:47:17 GMT</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:04:51 GMT</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:57:58 GMT</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:18:43 GMT</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 14:06:05 GMT</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 01:19:45 GMT</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:02:03 GMT</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:01:27 GMT</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:47:52 GMT</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
+          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
+          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:53:09 GMT</t>
+          <t>Mon, 11 May 2026 12:47:52 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
+          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Giá vàng lao dốc sau khi Mỹ từ chối đề xuất phản hồi của Iran</t>
+          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm mạnh v#224;o đầu giờ phi#234;n s#225;ng nay (11/5) tại thị trường ch#226;u #193;, sau khi c#243; tin Mỹ từ chối đề xuất m#224; Iran đưa ra để phản hồi kế hoạch h#242;a b#236;nh của Mỹ...</t>
+          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:44:18 GMT</t>
+          <t>Mon, 11 May 2026 09:53:09 GMT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1146,59 +1146,59 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/gia-vang-lao-doc-sau-khi-my-tu-choi-de-xuat-phan-hoi-cua-iran.htm</t>
+          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này có thể tăng</t>
+          <t>VMSC tiếp tục đăng ký bán cổ phiếu MSB sau nhiều lần thoái vốn bất thành</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tiếp đà phục hồi tuần qua, Phố Wall lẫn nhà đầu tư cá nhân cùng dự báo giá vàng tăng, với kỳ vọng hạ nhiệt căng thẳng Mỹ - Iran.</t>
+          <t>VMSC tiếp tục đăng ký bán toàn bộ 984.246 cổ phiếu còn lại tại MSB sau khi không hoàn tất kế hoạch thoái vốn trước đó do điều kiện thị trường không thuận lợi.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:00:00 +0700</t>
+          <t>Fri, 15 May 26 16:02:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-tuan-nay-co-the-tang-5072198.html</t>
+          <t>https://cafef.vn/vmsc-tiep-tuc-dang-ky-ban-co-phieu-msb-sau-nhieu-lan-thoai-von-bat-thanh-188260515155023356.chn</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức</t>
+          <t>Bộ Tài chính đề xuất nới chuẩn phát hành trái phiếu cho doanh nghiệp PPP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức. Thời gian thực hiện trong quý III/2026.</t>
+          <t>Trong bối cảnh c#225;c dự #225;n hạ tầng cần nguồn vốn lớn, Bộ T#224;i ch#237;nh đề xuất điều chỉnh quy định ph#225;t h#224;nh tr#225;i phiếu theo hướng linh hoạt hơn cho doanh nghiệp PPP, nhằm ph#249; hợp với đặc th#249; t#224;i trợ dự #225;n v#224; mở rộng khả năng huy động vốn d#224;i hạn cho hạ tầng…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 10:02:00 +0700</t>
+          <t>Fri, 15 May 2026 08:45:41 GMT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hodeco-se-phat-hanh-gan-30-trieu-co-phieu-tra-co-tuc-188260515100220542.chn</t>
+          <t>https://vneconomy.vn/bo-tai-chinh-de-xuat-noi-chuan-phat-hanh-trai-phieu-cho-doanh-nghiep-ppp.htm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
+          <t>Cổ phiếu dầu khí tiếp tục tăng mạnh, VN-Index “mệt nhoài” tại vùng đỉnh</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
+          <t>Những nỗ lực thiết lập đỉnh cao mới v#224; thực sự đột ph#225; của VN-Index vẫn kh#244;ng thể th#224;nh c#244;ng khi sự “r#227; đ#225;m” trong nh#243;m dẫn dắt chưa kết th#250;c. Nh#243;m ng#226;n h#224;ng sau phi#234;n b#249;ng nổ h#244;m qua đ#227; “nguội” kh#225; nhanh, trong khi VIC, VHM cũng thiếu sức mạnh.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:50:00 +0700</t>
+          <t>Fri, 15 May 2026 08:29:28 GMT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-tiep-tuc-tang-manh-vn-index-met-nhoai-tai-vung-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
+          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:22:00 +0700</t>
+          <t>Fri, 15 May 2026 11:00:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
+          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức. Thời gian thực hiện trong quý III/2026.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:26:00 +0700</t>
+          <t>Fri, 15 May 26 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
+          <t>https://cafef.vn/hodeco-se-phat-hanh-gan-30-trieu-co-phieu-tra-co-tuc-188260515100220542.chn</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
+          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
+          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:25:00 +0700</t>
+          <t>Fri, 15 May 26 08:50:00 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
+          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
+          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
+          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:08:00 +0700</t>
+          <t>Fri, 15 May 26 08:22:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
+          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
+          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:05:00 +0700</t>
+          <t>Fri, 15 May 26 07:26:00 +0700</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
+          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
+          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
+          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:48:56 +0700</t>
+          <t>Fri, 15 May 26 07:25:00 +0700</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
+          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
+          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
+          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:32:44 +0700</t>
+          <t>Fri, 15 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
+          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
+          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
+          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:18:48 GMT</t>
+          <t>Fri, 15 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
+          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
+          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
+          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:36:21 GMT</t>
+          <t>Thu, 14 May 2026 18:48:56 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
+          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:06:50 +0700</t>
+          <t>Thu, 14 May 2026 18:32:44 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
+          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
+          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Thu, 14 May 2026 10:18:48 GMT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
+          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
+          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
+          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:30:47 +0700</t>
+          <t>Thu, 14 May 2026 09:36:21 GMT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 13:36:00 +0700</t>
+          <t>Thu, 14 May 2026 16:06:50 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,29 +1626,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
+          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
+          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 12:30:00 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,29 +1656,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
+          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
+          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:47:00 +0700</t>
+          <t>Thu, 14 May 2026 15:30:47 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
+          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
         </is>
       </c>
     </row>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
+          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
+          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:16:00 +0700</t>
+          <t>Thu, 14 May 26 13:36:00 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
+          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
+          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
+          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 03:07:13 GMT</t>
+          <t>Thu, 14 May 2026 12:30:00 +0700</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
+          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
+          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
+          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:00:00 +0700</t>
+          <t>Thu, 14 May 26 10:47:00 +0700</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
+          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
         </is>
       </c>
     </row>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,29 +1806,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Thu, 14 May 2026 03:07:13 GMT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,29 +1866,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,29 +1896,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MSR bán thành công 2% cổ phần, đáp ứng điều kiện công ty đại chúng</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ngày 13/05/2026, CTCP Tập đoàn Masan (HOSE: MSN) công bố công ty con mà Masan sở hữu 100% vốn đã hoàn tất việc bán 21.99 triệu cp, tương đương 2% tổng số cổ phiếu đang lưu hành của CTCP Masan High-Tech Materials (UPCoM: MSR), thông qua các giao dịch trên hệ thống UPCoM theo đúng quy định hiện hành.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:37:35 +0700</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/msr-ban-thanh-cong-2-co-phan-dap-ung-dieu-kien-cong-ty-dai-chung-830-1442192.htm</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
+          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
+          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:09:00 +0700</t>
+          <t>Thu, 14 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
+          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Wed, 13 May 2026 19:17:24 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 26 17:09:00 +0700</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2028,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chứng khoán 13-5: Điều gì khiến cổ phiếu dầu khí bùng nổ?</t>
+          <t>Công bố giá xăng E10 Petrolimex</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phiên giao dịch ngày 13-5 ghi nhận diễn biến đầy biến động của thị trường chứng khoán khi áp lực bán mạnh xuất hiện ở nhóm cổ phiếu vốn hóa lớn</t>
+          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:14:00 +0700</t>
+          <t>Wed, 13 May 26 16:45:00 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-13-5-dieu-gi-khien-co-phieu-dau-khi-bung-no-18826051316143265.chn</t>
+          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,29 +2346,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MSR đạt doanh thu gần 3.000 tỷ trong quý I</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Doanh thu Masan High-Tech Materials (MSR) tăng gần 115% so với cùng kỳ, đạt 2.993 tỷ trong quý I/2026 nhờ sự cải thiện đồng thời của giá hàng hóa, sản lượng và cấu trúc tài chính.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:00:00 +0700</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2376,89 +2376,89 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/msr-dat-doanh-thu-gan-3-000-ty-trong-quy-i-5072256.html</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chuỗi nhà thuốc của Thế Giới Di Động sắp hết lỗ</t>
+          <t>Cổ phiếu trong hệ sinh thái của 'Bầu Thụy' dậy sóng</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thế Giới Di Động cho biết chuỗi nhà thuốc An Khang "gần ngưỡng hòa vốn" và có thể đóng góp lợi nhuận sau khoảng 8 năm doanh nghiệp này tham gia mảng bán lẻ dược.</t>
+          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:02:00 +0700</t>
+          <t>Fri, 15 May 26 17:57:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuoi-nha-thuoc-cua-the-gioi-di-dong-sap-het-lo-5072234.html</t>
+          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sau tái cấu trúc, Nam Hoa (NHT) hoạt động có lãi, trả cổ tức bằng tiền mặt 30%</t>
+          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hội đồng quản trị C#244;ng ty Cổ phần Sản xuất v#224; Thương mại Nam Hoa (m#227; chứng kho#225;n: NHT) vừa th#244;ng qua nghị quyết chi trả cổ tức bằng tiền mặt tỷ lệ 30% cho năm 2025 (tương ứng 3.000 đồng/cổ phiếu). Đ#226;y l#224; mức chi trả cao, phản #225;nh sự phục hồi ấn tượng v#224; d#242;ng tiền ổn định của doanh nghiệp sau giai đoạn t#225;i cấu tr#250;c mạnh mẽ…</t>
+          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 03:40:28 GMT</t>
+          <t>Fri, 15 May 26 17:24:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/sau-tai-cau-truc-nam-hoa-nht-hoat-dong-co-lai-tra-co-tuc-bang-tien-mat-30.htm</t>
+          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
+          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:02:00 +0700</t>
+          <t>Fri, 15 May 2026 16:38:21 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
+          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:00:00 +0700</t>
+          <t>Fri, 15 May 2026 16:12:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
         </is>
       </c>
     </row>
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
+          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:28:00 +0700</t>
+          <t>Fri, 15 May 26 15:48:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
+          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 06:02:00 +0700</t>
+          <t>Fri, 15 May 2026 15:15:53 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
+          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
+          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:01:00 +0700</t>
+          <t>Fri, 15 May 26 14:50:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
+          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
+          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
+          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:41:13 GMT</t>
+          <t>Fri, 15 May 2026 14:30:47 +0700</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,29 +2616,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
+          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 21:42:38 +0700</t>
+          <t>Fri, 15 May 2026 13:11:32 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
+          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:16:00 GMT</t>
+          <t>Fri, 15 May 2026 12:03:11 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,29 +2676,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
+          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:27:22 +0700</t>
+          <t>Fri, 15 May 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
+          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:48:25 +0700</t>
+          <t>Fri, 15 May 2026 11:55:07 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
+          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Fri, 15 May 2026 10:58:20 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
+          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
+          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:36:00 +0700</t>
+          <t>Fri, 15 May 2026 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
+          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:29:36 GMT</t>
+          <t>Fri, 15 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
+          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 14:38:00 +0700</t>
+          <t>Fri, 15 May 26 07:28:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
+          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
         </is>
       </c>
     </row>
@@ -2868,17 +2868,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
+          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:32:00 +0700</t>
+          <t>Fri, 15 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
+          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
+          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 13:02:11 +0700</t>
+          <t>Fri, 15 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
+          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
         </is>
       </c>
     </row>
@@ -2928,17 +2928,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
+          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:07:25 GMT</t>
+          <t>Thu, 14 May 2026 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
+          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 11:24:00 +0700</t>
+          <t>Thu, 14 May 2026 21:42:38 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Thu, 14 May 2026 14:16:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 2026 18:27:22 +0700</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,29 +3036,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 2026 15:48:25 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 26 15:36:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 08:29:36 GMT</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,29 +3156,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 2026 14:32:00 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Thu, 14 May 2026 13:02:11 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Thu, 14 May 2026 05:07:25 GMT</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vietstock Daily 14/05/2026: Phân hóa rõ nét</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VN-Index rung lắc mạnh khi test lại đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm). Chỉ báo Stochastic Oscillator tiếp tục giảm trong khi MACD cũng đang thu hẹp khoảng cách với đường signal. Nếu chỉ báo này cắt xuống đường signal trong các phiên tới thì rủi ro ngắn hạn sẽ gia tăng.</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:10:03 +0700</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-14052026-phan-hoa-ro-net-1636-1442207.htm</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
@@ -3318,17 +3318,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cổ đông lớn sang tay cổ phiếu CK8 giữa nguy cơ hủy tư cách đại chúng</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bà Ngô Thị Minh Phương trở thành cổ đông lớn của CTCP Cơ khí 120 (UPCoM: CK8) sau khi mua vào 665.8 ngàn cổ phiếu. Ở chiều ngược lại, bà Trần Thị Yến Hà đã bán ra đúng bằng số lượng này và thoái sạch vốn CK8. Thương vụ sang tay diễn ra trong bối cảnh công ty đang đối mặt với nguy cơ bị hủy tư cách đại chúng do vốn chủ sở hữu rớt xuống mức âm.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:20:45 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/co-dong-lon-sang-tay-co-phieu-ck8-giua-nguy-co-huy-tu-cach-dai-chung-739-1442149.htm</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp đầu ngành sắp lăn chốt cổ tức tiền mặt 83%, "đại gia" Thái Lan vớ bẫm</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Đây cũng là mức cổ tức tiền mặt cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:11:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-doanh-nghiep-dau-nganh-sap-lan-chot-co-tuc-tien-mat-83-dai-gia-thai-lan-vo-bam-188260513161023867.chn</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3438,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fecon sắp phát hành lô trái phiếu 125 tỷ đồng</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fecon dự kiến phát hành 1.250 trái phiếu mã FCN12601 ra thị trường trong nước vào ngày 15/5/2026, mệnh giá 100 triệu đồng/trái phiếu, qua đó huy động 125 tỷ đồng.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:50:00 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fecon-sap-phat-hanh-lo-trai-phieu-125-ty-dong-188260513144942479.chn</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
@@ -3498,17 +3498,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Phiên 13/5: Khối ngoại tiếp đà bán ròng nghìn tỷ, ngược chiều gom mạnh một cổ phiếu ngân hàng</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm trừ khi bán ròng khoảng 1.475 tỷ đồng.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:45:00 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://cafef.vn/phien-13-5-khoi-ngoai-tiep-da-ban-rong-nghin-ty-nguoc-chieu-gom-manh-mot-co-phieu-ngan-hang-1882605131542172.chn</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vừa về tay ông lớn dược phẩm Trung Quốc, loạt lãnh đạo Imexpharm cùng bán ra lượng cổ phiếu</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nhiều lãnh đạo của Công ty cổ phần Dược phẩm Imexpharm (MCK: IMP, sàn: HoSE) vừa báo cáo kết quả bán ra cổ phiếu.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:20:00 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vua-ve-tay-ong-lon-duoc-pham-trung-quoc-loat-lanh-dao-imexpharm-cung-ban-ra-luong-co-phieu-188260513145031724.chn</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Người nhà lãnh đạo SeABank đăng ký mua 5 triệu cổ phiếu SSB</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ông Lê Hữu Báu, chồng của bà Nguyễn Thị Nga- Phó Chủ tịch thường trực HĐQT SeABank, vừa đăng ký mua 5 triệu cổ phiếu SSB nhằm mục đích tăng tỷ lệ sở hữu.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 15:18:00 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://cafef.vn/nguoi-nha-lanh-dao-seabank-dang-ky-mua-5-trieu-co-phieu-ssb-188260513145128351.chn</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3678,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,29 +3816,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -3918,17 +3918,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,29 +3966,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
+          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
+          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
+          <t>Mon, 11 May 2026 15:49:54 +0700</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>12,8 nghìn tỷ đồng trái phiếu có vấn đề trong quý 1/2026, chủ yếu ở nhóm Bất động sản</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tỷ lệ tr#225;i phiếu c#243; vấn đề ph#225;t sinh mới đ#227; giảm từ năm 2024, cho thấy khả năng trả nợ cũng như năng lực t#224;i ch#237;nh của c#225;c tổ chức ph#225;t h#224;nh đ#227; cải thiện đ#225;ng kể trong c#225;c năm gần đ#226;y.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 02:31:04 GMT</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,29 +4476,29 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/128-nghin-ty-dong-trai-phieu-co-van-de-trong-quy-12026-chu-yeu-o-nhom-bat-dong-san.htm</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VN-Index được dự đoán sớm vượt 2.000 điểm</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nhiều nhóm phân tích cho rằng VN-Index tháng này có thể vượt 2.000 điểm nhờ lực kéo từ cổ phiếu trụ và thanh khoản dồi dào.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 00:05:00 +0700</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,29 +4506,29 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-duoc-du-doan-som-vuot-2-000-diem-5072145.html</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sổ đỏ cấp sai quy định được xem xét điều chỉnh, nộp bổ sung thuế</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Các dự án được cấp sổ đỏ sai quy định trước đây sẽ được xem xét điều chỉnh và nộp bổ sung nghĩa vụ tài chính, theo cơ chế đặc thù của Chính phủ.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 17:40:04 +0700</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4536,29 +4536,29 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/so-do-cap-sai-quy-dinh-duoc-xem-xet-dieu-chinh-nop-bo-sung-thue-5072135.html</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Đề xuất doanh nghiệp nộp thuế thay người gom ve chai, phế liệu</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VCCI đề nghị Bộ Tài chính bổ sung cơ chế khai, nộp thuế thay với hộ kinh doanh ve chai, đồng nát và sửa cách tính thuế với mô hình tài xế công nghệ.</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 12:48:02 +0700</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-doanh-nghiep-nop-thue-thay-nguoi-gom-ve-chai-phe-lieu-5072084.html</t>
+          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -703,22 +703,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Theo dấu dòng tiền cá mập 13/05: Khối ngoại bán ròng phiên thứ mười bốn liên tiếp</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trong phiên rung lắc của thị trường, cả khối tự doanh và khối ngoại đều bán ròng.</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:32 +0700</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,29 +726,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/theo-dau-dong-tien-ca-map-1305-khoi-ngoai-ban-rong-phien-thu-muoi-bon-lien-tiep-830-1442280.htm</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
+          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
+          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:10 +0700</t>
+          <t>Wed, 13 May 26 17:30:00 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,29 +756,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
+          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:30:00 +0700</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,29 +786,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 03:47:17 GMT</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:04:51 GMT</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:57:58 GMT</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:18:43 GMT</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 14:06:05 GMT</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 01:19:45 GMT</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:02:03 GMT</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
+          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
+          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:01:27 GMT</t>
+          <t>Tue, 12 May 2026 05:33:34 +0700</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
+          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Mon, 11 May 2026 12:47:52 GMT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
+          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
+          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:47:52 GMT</t>
+          <t>Mon, 11 May 2026 09:53:09 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,37 +1116,37 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
+          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
+          <t>Chứng khoán Tuần 11-15/05/2026: Đỉnh cao gió lớn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
+          <t>VN-Index điều chỉnh trở lại trong phiên cuối tuần sau khi thiết lập đỉnh lịch sử mới. Dù nhóm cổ phiếu vốn hóa lớn đang luân phiên dẫn dắt và giữ nhịp cho chỉ số, phần còn lại của thị trường vẫn phân hóa rõ nét. Bên cạnh đó, việc thanh khoản chưa cải thiện cùng với áp lực bán ròng kéo dài từ khối ngoại khiến rủi ro rung lắc vẫn hiện hữu tại vùng giá cao.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:53:09 GMT</t>
+          <t>Fri, 15 May 2026 18:16:40 +0700</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
+          <t>http://vietstock.vn/2026/05/chung-khoan-tuan-11-15052026-dinh-cao-gio-lon-1636-1443135.htm</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cổ phiếu trong hệ sinh thái của 'Bầu Thụy' dậy sóng</t>
+          <t>Chứng khoán Việt Nam "gồng mình" giữa lúc thị trường châu Á đỏ lửa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
+          <t>Khép lại phiên giao dịch ngày 15-5, thị trường chứng khoán Việt Nam chịu áp lực điều chỉnh sau nhịp phục hồi mạnh trước đó</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:57:00 +0700</t>
+          <t>Fri, 15 May 26 18:45:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-gong-minh-giua-luc-thi-truong-chau-a-do-lua-188260515184509181.chn</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
+          <t>Sốt dòng tiền ở nhóm cổ phiếu dầu khí</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
+          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:24:00 +0700</t>
+          <t>Fri, 15 May 26 17:57:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,29 +2436,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
+          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
+          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:38:21 +0700</t>
+          <t>Fri, 15 May 26 17:24:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,29 +2466,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
+          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:12:00 +0700</t>
+          <t>Fri, 15 May 2026 16:38:21 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
+          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 15:48:00 +0700</t>
+          <t>Fri, 15 May 2026 16:12:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 15:15:53 +0700</t>
+          <t>Fri, 15 May 26 15:48:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
+          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 14:50:00 +0700</t>
+          <t>Fri, 15 May 2026 15:15:53 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
+          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
+          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:30:47 +0700</t>
+          <t>Fri, 15 May 26 14:50:00 +0700</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
+          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
         </is>
       </c>
     </row>
@@ -2628,17 +2628,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
+          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
+          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:11:32 +0700</t>
+          <t>Fri, 15 May 2026 14:30:47 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
+          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
+          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:03:11 +0700</t>
+          <t>Fri, 15 May 2026 13:11:32 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
+          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:00:00 +0700</t>
+          <t>Fri, 15 May 2026 12:03:11 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
+          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:55:07 +0700</t>
+          <t>Fri, 15 May 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
     </row>
@@ -2748,17 +2748,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
+          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:58:20 +0700</t>
+          <t>Fri, 15 May 2026 11:55:07 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
+          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:02:00 +0700</t>
+          <t>Fri, 15 May 2026 10:58:20 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
     </row>
@@ -2808,17 +2808,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
+          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:00:00 +0700</t>
+          <t>Fri, 15 May 2026 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
+          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:28:00 +0700</t>
+          <t>Fri, 15 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 06:02:00 +0700</t>
+          <t>Fri, 15 May 26 07:28:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
+          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
+          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:01:00 +0700</t>
+          <t>Fri, 15 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
+          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
+          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:41:13 GMT</t>
+          <t>Fri, 15 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
+          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 21:42:38 +0700</t>
+          <t>Thu, 14 May 2026 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:16:00 GMT</t>
+          <t>Thu, 14 May 2026 21:42:38 +0700</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
+          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
+          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:27:22 +0700</t>
+          <t>Thu, 14 May 2026 14:16:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,29 +3036,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
+          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:48:25 +0700</t>
+          <t>Thu, 14 May 2026 18:27:22 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
+          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Thu, 14 May 2026 15:48:25 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
     </row>
@@ -3108,17 +3108,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
+          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
+          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:36:00 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
+          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
+          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
+          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:29:36 GMT</t>
+          <t>Thu, 14 May 26 15:36:00 +0700</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,29 +3156,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
+          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
+          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
+          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 14:38:00 +0700</t>
+          <t>Thu, 14 May 2026 08:29:36 GMT</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
+          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
+          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
+          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:32:00 +0700</t>
+          <t>Thu, 14 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
+          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
         </is>
       </c>
     </row>
@@ -3228,17 +3228,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
+          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
+          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 13:02:11 +0700</t>
+          <t>Thu, 14 May 2026 14:32:00 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
+          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
+          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
+          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:07:25 GMT</t>
+          <t>Thu, 14 May 2026 13:02:11 +0700</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
+          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
+          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 11:24:00 +0700</t>
+          <t>Thu, 14 May 2026 05:07:25 GMT</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
+          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,29 +3336,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,29 +3486,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3678,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,29 +3756,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,29 +3966,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,29 +3996,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,29 +4296,29 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,29 +4326,29 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VN-Index giảm gần 20 điểm phiên đầu tuần</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bốn cổ phiếu liên quan đến Vingroup đều giảm, dao động 1-6,5%, trở thành tác nhân chính khiến VN-Index mất gần 20 điểm trong phiên đầu tuần.</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:49:54 +0700</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-giam-gan-20-diem-phien-dau-tuan-5072618.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,22 +2023,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Công bố giá xăng E10 Petrolimex</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tập đoàn Xăng dầu Việt Nam (Petrolimex) vừa thông báo giá bán xăng sinh học E10 RON 95 áp dụng từ ngày 0h ngày 13/5. Theo đó, giá bán xăng sinh học E10 RON 95-V tại cửa hàng xăng dầu tại thị trường vùng 1 là 24.630 đồng/lít, tại các thị trường vùng 2 là 25.120 đồng/lít.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:45:00 +0700</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cong-bo-gia-xang-e10-petrolimex-188260513154754794.chn</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>VN-Index quay lại mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Tue, 12 May 2026 16:10:36 +0700</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Tue, 12 May 2026 12:13:58 +0700</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,37 +2346,37 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>Chứng khoán Việt Nam "gồng mình" giữa lúc thị trường châu Á đỏ lửa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Khép lại phiên giao dịch ngày 15-5, thị trường chứng khoán Việt Nam chịu áp lực điều chỉnh sau nhịp phục hồi mạnh trước đó</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Fri, 15 May 26 18:45:00 +0700</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-gong-minh-giua-luc-thi-truong-chau-a-do-lua-188260515184509181.chn</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam "gồng mình" giữa lúc thị trường châu Á đỏ lửa</t>
+          <t>Sốt dòng tiền ở nhóm cổ phiếu dầu khí</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Khép lại phiên giao dịch ngày 15-5, thị trường chứng khoán Việt Nam chịu áp lực điều chỉnh sau nhịp phục hồi mạnh trước đó</t>
+          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 18:45:00 +0700</t>
+          <t>Fri, 15 May 26 17:57:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-viet-nam-gong-minh-giua-luc-thi-truong-chau-a-do-lua-188260515184509181.chn</t>
+          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sốt dòng tiền ở nhóm cổ phiếu dầu khí</t>
+          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
+          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:57:00 +0700</t>
+          <t>Fri, 15 May 26 17:24:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,29 +2436,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
+          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
+          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:24:00 +0700</t>
+          <t>Fri, 15 May 2026 16:38:21 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,29 +2466,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:38:21 +0700</t>
+          <t>Fri, 15 May 2026 16:12:00 +0700</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,29 +2496,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
+          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:12:00 +0700</t>
+          <t>Fri, 15 May 26 15:48:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
+          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
+          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 15:48:00 +0700</t>
+          <t>Fri, 15 May 2026 15:15:53 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
+          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 15:15:53 +0700</t>
+          <t>Fri, 15 May 26 14:50:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
+          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
+          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 14:50:00 +0700</t>
+          <t>Fri, 15 May 2026 14:30:47 +0700</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
+          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
         </is>
       </c>
     </row>
@@ -2628,17 +2628,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
+          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
+          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:30:47 +0700</t>
+          <t>Fri, 15 May 2026 13:11:32 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
+          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:11:32 +0700</t>
+          <t>Fri, 15 May 2026 12:03:11 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
+          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:03:11 +0700</t>
+          <t>Fri, 15 May 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
+          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
+          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:00:00 +0700</t>
+          <t>Fri, 15 May 2026 11:55:07 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
+          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
         </is>
       </c>
     </row>
@@ -2748,17 +2748,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
+          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:55:07 +0700</t>
+          <t>Fri, 15 May 2026 10:58:20 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
+          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:58:20 +0700</t>
+          <t>Fri, 15 May 2026 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
         </is>
       </c>
     </row>
@@ -2808,17 +2808,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:02:00 +0700</t>
+          <t>Fri, 15 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
+          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:00:00 +0700</t>
+          <t>Fri, 15 May 26 07:28:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
+          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
+          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:28:00 +0700</t>
+          <t>Fri, 15 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
+          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 06:02:00 +0700</t>
+          <t>Fri, 15 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
+          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
+          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:01:00 +0700</t>
+          <t>Thu, 14 May 2026 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
+          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:41:13 GMT</t>
+          <t>Thu, 14 May 2026 21:42:38 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 21:42:38 +0700</t>
+          <t>Thu, 14 May 2026 14:16:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
+          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
+          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:16:00 GMT</t>
+          <t>Thu, 14 May 2026 18:27:22 +0700</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,29 +3036,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
+          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:27:22 +0700</t>
+          <t>Thu, 14 May 2026 15:48:25 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
+          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:48:25 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
         </is>
       </c>
     </row>
@@ -3108,17 +3108,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
+          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
+          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Thu, 14 May 26 15:36:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
+          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
+          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
+          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:36:00 +0700</t>
+          <t>Thu, 14 May 2026 08:29:36 GMT</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,29 +3156,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
+          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
+          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
+          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:29:36 GMT</t>
+          <t>Thu, 14 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
+          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
+          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
+          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 14:38:00 +0700</t>
+          <t>Thu, 14 May 2026 14:32:00 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
+          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
         </is>
       </c>
     </row>
@@ -3228,17 +3228,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
+          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
+          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:32:00 +0700</t>
+          <t>Thu, 14 May 2026 13:02:11 +0700</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
+          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
+          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 13:02:11 +0700</t>
+          <t>Thu, 14 May 2026 05:07:25 GMT</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
+          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:07:25 GMT</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 11:24:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,29 +3336,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 26 00:06:00 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,29 +3486,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Wed, 13 May 26 18:44:00 +0700</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Wed, 13 May 26 16:48:00 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3678,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,29 +3756,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,29 +3966,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Tue, 12 May 2026 16:21:11 +0700</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,29 +3996,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 12:05:00 +0700</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,29 +4176,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,29 +4296,29 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Mon, 11 May 2026 21:19:05 +0700</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,29 +4326,29 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 07:08:33 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 05:10:22 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 03:23:29 GMT</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
+          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
         </is>
       </c>
     </row>
@@ -4518,53 +4518,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
+          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
+          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
+          <t>Mon, 11 May 2026 02:33:57 GMT</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>1</v>
       </c>
       <c r="F137" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" t="inlineStr">
         <is>
           <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
         </is>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ba cổ phiếu ngân hàng tiềm năng tăng giá tốt nhất trong bối cảnh lãi suất cao đe dọa NIM, nợ xấu tăng</t>
+          <t>Chứng khoán Mỹ giảm điểm mạnh vì cổ phiếu công nghệ bị bán, giá dầu leo thang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VnDirect kỳ vọng NIM to#224;n ng#224;nh sẽ dần cải thiện v#224;o cuối năm khi mặt bằng l#227;i suất c#243; xu hướng hạ nhiệt v#224; hoạt động thu hồi nợ thường t#237;ch cực hơn trong nửa cuối năm. Theo đ#243;, kỳ vọng NIM to#224;n ng#224;nh năm 2026 sẽ duy tr#236; quanh mức 3,1%.</t>
+          <t>Lợi suất tr#225;i phiếu tăng mạnh cũng l#224; một nguy#234;n nh#226;n quan trọng khiến cổ phiếu bị b#225;n th#225;o...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 04:42:52 GMT</t>
+          <t>Sat, 16 May 2026 01:44:28 GMT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,29 +486,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ba-co-phieu-ngan-hang-tiem-nang-tang-gia-tot-nhat-trong-boi-canh-lai-suat-cao-de-doa-nim-no-xau-tang.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-giam-diem-manh-vi-co-phieu-cong-nghe-bi-ban-gia-dau-leo-thang.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
+          <t>Giá vàng thế giới xuống thấp nhất gần 2 tuần</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
+          <t>Đôla Mỹ đắt lên và lợi suất trái phiếu chính phủ Mỹ tăng cao khiến giá vàng thế giới mất hơn 100 USD phiên cuối tuần.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 00:40:12 GMT</t>
+          <t>Sat, 16 May 2026 07:13:12 +0700</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,29 +516,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
+          <t>https://vnexpress.net/gia-vang-the-gioi-xuong-thap-nhat-gan-2-tuan-5074551.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
+          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
+          <t>Ngân hàng Nhà nước vừa nới cách tính tỷ lệ dư nợ cho vay trên tổng tiền gửi (LDR), qua đó hỗ trợ thanh khoản cho nhóm ngân hàng quốc doanh.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:37:00 +0700</t>
+          <t>Fri, 15 May 2026 19:15:20 +0700</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,29 +546,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
+          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giá xăng, dầu cùng giảm</t>
+          <t>Ba cổ phiếu ngân hàng tiềm năng tăng giá tốt nhất trong bối cảnh lãi suất cao đe dọa NIM, nợ xấu tăng</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
+          <t>VnDirect kỳ vọng NIM to#224;n ng#224;nh sẽ dần cải thiện v#224;o cuối năm khi mặt bằng l#227;i suất c#243; xu hướng hạ nhiệt v#224; hoạt động thu hồi nợ thường t#237;ch cực hơn trong nửa cuối năm. Theo đ#243;, kỳ vọng NIM to#224;n ng#224;nh năm 2026 sẽ duy tr#236; quanh mức 3,1%.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:34:59 +0700</t>
+          <t>Fri, 15 May 2026 04:42:52 GMT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
+          <t>https://vneconomy.vn/ba-co-phieu-ngan-hang-tiem-nang-tang-gia-tot-nhat-trong-boi-canh-lai-suat-cao-de-doa-nim-no-xau-tang.htm</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
+          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
+          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:50:35 GMT</t>
+          <t>Fri, 15 May 2026 00:40:12 GMT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,29 +606,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
+          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
+          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:47:13 GMT</t>
+          <t>Thu, 14 May 2026 16:37:00 +0700</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,29 +636,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
+          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 01:18:51 GMT</t>
+          <t>Thu, 14 May 2026 14:34:59 +0700</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
+          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
+          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:26:34 GMT</t>
+          <t>Thu, 14 May 2026 06:50:35 GMT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
+          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
+          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
+          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:10 +0700</t>
+          <t>Thu, 14 May 2026 06:47:13 GMT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,29 +726,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FDI thế hệ mới cần cùng Việt Nam tạo ra giá trị mới, năng lực mới, vị thế mới</t>
+          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phát biểu tại Diễn đàn Nhịp cầu Phát triển Việt Nam 2026 chiều nay, 13/5, Phó Thủ tướng Nguyễn Văn Thắng nhấn mạnh, FDI thế hệ mới không chỉ đến Việt Nam để sản xuất, để khai thác thị trường, mà cần cùng Việt Nam tạo ra giá trị mới, năng lực mới và vị thế mới trong chuỗi giá trị toàn cầu.</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:30:00 +0700</t>
+          <t>Thu, 14 May 2026 01:18:51 GMT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,29 +756,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cafef.vn/fdi-the-he-moi-can-cung-viet-nam-tao-ra-gia-tri-moi-nang-luc-moi-vi-the-moi-188260513165309213.chn</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Thu, 14 May 2026 00:26:34 GMT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,29 +786,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 03:47:17 GMT</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,29 +816,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
+          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
+          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:04:51 GMT</t>
+          <t>Wed, 13 May 2026 11:18:27 +0700</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:57:58 GMT</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:18:43 GMT</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 14:06:05 GMT</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 01:19:45 GMT</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:02:03 GMT</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:01:27 GMT</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,29 +1026,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm ngân hàng nào cao nhất?</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lãi suất tiết kiệm hạ nhiệt sau chỉ đạo của Thống đốc song mặt bằng chung với các khoản thỏa thuận vẫn ở mức hấp dẫn, một số nhà băng trả 8-9% một năm.</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:33:34 +0700</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lai-suat-tiet-kiem-ngan-hang-nao-cao-nhat-5072646.html</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:47:52 GMT</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
+          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
+          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
+          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:53:09 GMT</t>
+          <t>Mon, 11 May 2026 12:47:52 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,37 +1116,37 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
+          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chứng khoán Tuần 11-15/05/2026: Đỉnh cao gió lớn</t>
+          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VN-Index điều chỉnh trở lại trong phiên cuối tuần sau khi thiết lập đỉnh lịch sử mới. Dù nhóm cổ phiếu vốn hóa lớn đang luân phiên dẫn dắt và giữ nhịp cho chỉ số, phần còn lại của thị trường vẫn phân hóa rõ nét. Bên cạnh đó, việc thanh khoản chưa cải thiện cùng với áp lực bán ròng kéo dài từ khối ngoại khiến rủi ro rung lắc vẫn hiện hữu tại vùng giá cao.</t>
+          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 18:16:40 +0700</t>
+          <t>Mon, 11 May 2026 09:53:09 GMT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/chung-khoan-tuan-11-15052026-dinh-cao-gio-lon-1636-1443135.htm</t>
+          <t>https://vneconomy.vn/australia-khoi-xuong-dieu-tra-doi-voi-thep-ma-kem-nhap-khau-tu-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -1158,17 +1158,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VMSC tiếp tục đăng ký bán cổ phiếu MSB sau nhiều lần thoái vốn bất thành</t>
+          <t>Chứng khoán Nhất Việt chốt ngày phát hành gần 14 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VMSC tiếp tục đăng ký bán toàn bộ 984.246 cổ phiếu còn lại tại MSB sau khi không hoàn tất kế hoạch thoái vốn trước đó do điều kiện thị trường không thuận lợi.</t>
+          <t>Ngày 27/5 tới, Chứng khoán Nhất Việt sẽ phát hành gần 14 triệu cổ phiếu trả cổ tức cho cổ đông.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 16:02:00 +0700</t>
+          <t>Sat, 16 May 26 10:01:00 +0700</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1176,29 +1176,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vmsc-tiep-tuc-dang-ky-ban-co-phieu-msb-sau-nhieu-lan-thoai-von-bat-thanh-188260515155023356.chn</t>
+          <t>https://cafef.vn/chung-khoan-nhat-viet-chot-ngay-phat-hanh-gan-14-trieu-co-phieu-tra-co-tuc-188260516094932433.chn</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bộ Tài chính đề xuất nới chuẩn phát hành trái phiếu cho doanh nghiệp PPP</t>
+          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trong bối cảnh c#225;c dự #225;n hạ tầng cần nguồn vốn lớn, Bộ T#224;i ch#237;nh đề xuất điều chỉnh quy định ph#225;t h#224;nh tr#225;i phiếu theo hướng linh hoạt hơn cho doanh nghiệp PPP, nhằm ph#249; hợp với đặc th#249; t#224;i trợ dự #225;n v#224; mở rộng khả năng huy động vốn d#224;i hạn cho hạ tầng…</t>
+          <t>Theo chuyên gia Dragon Capital, cổ phiếu Vingroup tăng mạnh nhưng phù hợp với sức khỏe tài chính, mức này còn thấp hơn nhiều so với cổ phiếu trụ nước khác.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:45:41 GMT</t>
+          <t>Sat, 16 May 2026 09:41:14 +0700</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/bo-tai-chinh-de-xuat-noi-chuan-phat-hanh-trai-phieu-cho-doanh-nghiep-ppp.htm</t>
+          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí tiếp tục tăng mạnh, VN-Index “mệt nhoài” tại vùng đỉnh</t>
+          <t>Nhiều người lo nhóm Vingroup "quá nóng", chuyên gia Dragon Capital đưa ví dụ cổ phiếu tăng đến 55 lần</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Những nỗ lực thiết lập đỉnh cao mới v#224; thực sự đột ph#225; của VN-Index vẫn kh#244;ng thể th#224;nh c#244;ng khi sự “r#227; đ#225;m” trong nh#243;m dẫn dắt chưa kết th#250;c. Nh#243;m ng#226;n h#224;ng sau phi#234;n b#249;ng nổ h#244;m qua đ#227; “nguội” kh#225; nhanh, trong khi VIC, VHM cũng thiếu sức mạnh.</t>
+          <t>Theo ông Tuấn, khi một cổ phiếu tăng mạnh, tâm lý chung của thị trường thường mặc định đó là vùng đỉnh. Tuy nhiên, đây là nhận định mang tính chủ quan.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:29:28 GMT</t>
+          <t>Sat, 16 May 26 00:03:00 +0700</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-tiep-tuc-tang-manh-vn-index-met-nhoai-tai-vung-dinh.htm</t>
+          <t>https://cafef.vn/nhieu-nguoi-lo-nhom-vingroup-qua-nong-chuyen-gia-dragon-capital-dua-vi-du-co-phieu-tang-den-55-lan-188260515231922301.chn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Một cổ phiếu đứng trước nguy cơ hủy niêm yết: Lỗ lũy kế hơn 500 tỷ đồng, nhiều quý liền “trắng” doanh thu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
+          <t>Cổ phiếu DDG đứng trước nguy cơ hủy niêm yết bắt buộc khi tình hình sản xuất, kinh doanh rơi vào trạng thái đình trệ.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:00:00 +0700</t>
+          <t>Sat, 16 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1266,29 +1266,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
+          <t>https://cafef.vn/mot-co-phieu-dung-truoc-nguy-co-huy-niem-yet-lo-luy-ke-hon-500-ty-dong-nhieu-quy-lien-trang-doanh-thu-188260515211717672.chn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức</t>
+          <t>Green SM hợp tác 75 doanh nghiệp, triển khai gần 18.500 xe VinFast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức. Thời gian thực hiện trong quý III/2026.</t>
+          <t>Hãng taxi điện ký biên bản ghi nhớ, thỏa thuận đặt cọc với các doanh nghiệp vận tải, sắp vận hành 18.497 ôtô điện VinFast tại thị trường Philippines, hôm 15/5.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 10:02:00 +0700</t>
+          <t>Fri, 15 May 2026 20:00:00 +0700</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hodeco-se-phat-hanh-gan-30-trieu-co-phieu-tra-co-tuc-188260515100220542.chn</t>
+          <t>https://vnexpress.net/green-sm-hop-tac-75-doanh-nghiep-trien-khai-gan-18-500-xe-vinfast-5074490.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
+          <t>Chứng khoán Tuần 11-15/05/2026: Đỉnh cao gió lớn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
+          <t>VN-Index điều chỉnh trở lại trong phiên cuối tuần sau khi thiết lập đỉnh lịch sử mới. Dù nhóm cổ phiếu vốn hóa lớn đang luân phiên dẫn dắt và giữ nhịp cho chỉ số, phần còn lại của thị trường vẫn phân hóa rõ nét. Bên cạnh đó, việc thanh khoản chưa cải thiện cùng với áp lực bán ròng kéo dài từ khối ngoại khiến rủi ro rung lắc vẫn hiện hữu tại vùng giá cao.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:50:00 +0700</t>
+          <t>Fri, 15 May 2026 18:16:40 +0700</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
+          <t>http://vietstock.vn/2026/05/chung-khoan-tuan-11-15052026-dinh-cao-gio-lon-1636-1443135.htm</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
+          <t>VMSC tiếp tục đăng ký bán cổ phiếu MSB sau nhiều lần thoái vốn bất thành</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
+          <t>VMSC tiếp tục đăng ký bán toàn bộ 984.246 cổ phiếu còn lại tại MSB sau khi không hoàn tất kế hoạch thoái vốn trước đó do điều kiện thị trường không thuận lợi.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 08:22:00 +0700</t>
+          <t>Fri, 15 May 26 16:02:00 +0700</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
+          <t>https://cafef.vn/vmsc-tiep-tuc-dang-ky-ban-co-phieu-msb-sau-nhieu-lan-thoai-von-bat-thanh-188260515155023356.chn</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
+          <t>Bộ Tài chính đề xuất nới chuẩn phát hành trái phiếu cho doanh nghiệp PPP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
+          <t>Trong bối cảnh c#225;c dự #225;n hạ tầng cần nguồn vốn lớn, Bộ T#224;i ch#237;nh đề xuất điều chỉnh quy định ph#225;t h#224;nh tr#225;i phiếu theo hướng linh hoạt hơn cho doanh nghiệp PPP, nhằm ph#249; hợp với đặc th#249; t#224;i trợ dự #225;n v#224; mở rộng khả năng huy động vốn d#224;i hạn cho hạ tầng…</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:26:00 +0700</t>
+          <t>Fri, 15 May 2026 08:45:41 GMT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1386,29 +1386,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
+          <t>https://vneconomy.vn/bo-tai-chinh-de-xuat-noi-chuan-phat-hanh-trai-phieu-cho-doanh-nghiep-ppp.htm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
+          <t>Cổ phiếu dầu khí tiếp tục tăng mạnh, VN-Index “mệt nhoài” tại vùng đỉnh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
+          <t>Những nỗ lực thiết lập đỉnh cao mới v#224; thực sự đột ph#225; của VN-Index vẫn kh#244;ng thể th#224;nh c#244;ng khi sự “r#227; đ#225;m” trong nh#243;m dẫn dắt chưa kết th#250;c. Nh#243;m ng#226;n h#224;ng sau phi#234;n b#249;ng nổ h#244;m qua đ#227; “nguội” kh#225; nhanh, trong khi VIC, VHM cũng thiếu sức mạnh.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:25:00 +0700</t>
+          <t>Fri, 15 May 2026 08:29:28 GMT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-tiep-tuc-tang-manh-vn-index-met-nhoai-tai-vung-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
+          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:08:00 +0700</t>
+          <t>Fri, 15 May 2026 11:00:00 +0700</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
+          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
+          <t>Hodeco sẽ phát hành gần 30 triệu cổ phiếu trả cổ tức. Thời gian thực hiện trong quý III/2026.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:05:00 +0700</t>
+          <t>Fri, 15 May 26 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
+          <t>https://cafef.vn/hodeco-se-phat-hanh-gan-30-trieu-co-phieu-tra-co-tuc-188260515100220542.chn</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
+          <t>DDG đối diện nguy cơ hủy niêm yết sau chuỗi kinh doanh thua lỗ kéo dài</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
+          <t>Cổ phiếu DDG đang đứng trước nguy cơ bị hủy niêm yết bắt buộc sau nhiều năm chìm trong khó khăn tài chính. Không chỉ thua lỗ liên tiếp trong 3 năm, doanh nghiệp còn liên tục nhận ý kiến kiểm toán ngoại trừ, trong bối cảnh áp lực nợ vay và công nợ ngày càng gia tăng.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:48:56 +0700</t>
+          <t>Fri, 15 May 26 08:50:00 +0700</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
+          <t>https://cafef.vn/ddg-doi-dien-nguy-co-huy-niem-yet-sau-chuoi-kinh-doanh-thua-lo-keo-dai-188260515085017664.chn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
+          <t>PAN Group “chơi lớn” với cổ đông: Thưởng cổ phiếu 20% kèm cổ tức tiền mặt 30%</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
+          <t>Tổng lợi ích cổ đông nhận được trong đợt này lên tới 50% - mức mà rất ít doanh nghiệp niêm yết trên sàn hiện nay duy trì được.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:32:44 +0700</t>
+          <t>Fri, 15 May 26 08:22:00 +0700</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
+          <t>https://cafef.vn/pan-group-choi-lon-voi-co-dong-thuong-co-phieu-20-kem-co-tuc-tien-mat-30-188260515082222878.chn</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
+          <t>Vietcombank dự kiến phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
+          <t>HĐQT Vietcombank đã phê duyệt phương án phát hành tối đa 10.000 tỷ đồng trái phiếu tăng vốn cấp 2 theo hình thức riêng lẻ năm 2026.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:18:48 GMT</t>
+          <t>Fri, 15 May 26 07:26:00 +0700</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
+          <t>https://cafef.vn/vietcombank-du-kien-phat-hanh-toi-da-10000-ty-dong-trai-phieu-tang-von-cap-2-188260515072637945.chn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
+          <t>TCBS chốt danh sách cổ đông nhận cổ tức bằng cổ phiếu tỷ lệ 20%</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
+          <t>Ngày 26/5 tới, TCBS sẽ chốt danh sách cổ đông để phát hành 462,3 triệu cổ phiếu để trả cổ tức. Tỷ lệ thực hiện quyền 5:1.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:36:21 GMT</t>
+          <t>Fri, 15 May 26 07:25:00 +0700</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
+          <t>https://cafef.vn/tcbs-chot-danh-sach-co-dong-nhan-co-tuc-bang-co-phieu-ty-le-20-188260515072515224.chn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Việt Nam sắp có ngân hàng đầu tiên vượt 110.000 tỷ vốn điều lệ, nhưng không phải "Big 4"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+          <t>Đây là kế hoạch tăng vốn điều lệ lớn nhất nhất ngành ngân hàng Việt Nam trong năm nay.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:06:50 +0700</t>
+          <t>Fri, 15 May 26 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+          <t>https://cafef.vn/viet-nam-sap-co-ngan-hang-dau-tien-vuot-110000-ty-von-dieu-le-nhung-khong-phai-big-4-188260514231946025.chn</t>
         </is>
       </c>
     </row>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
+          <t>Lợi nhuận lập đỉnh, một doanh nghiệp trả cổ tức tiền mặt kỷ lục hơn 63%</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
+          <t>Đây là mức cổ tức cao nhất trong lịch sử hoạt động của doanh nghiệp.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Fri, 15 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
+          <t>https://cafef.vn/loi-nhuan-lap-dinh-mot-doanh-nghiep-tra-co-tuc-tien-mat-ky-luc-hon-63-188260514225550021.chn</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
+          <t>DGC gấp rút kiểm toán báo cáo tài chính để cổ phiếu sớm thoát diện kiểm soát</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
+          <t>CTCP Tập đoàn Hóa chất Đức Giang (HOSE: DGC) cho biết đang đẩy nhanh kiểm toán báo cáo tài chính 2025 để sớm đưa cổ phiếu ra khỏi diện kiểm soát, sau giai đoạn biến động lớn khi nhiều lãnh đạo cấp cao bị khởi tố và hoạt động kinh doanh chịu áp lực vì mất nguồn quặng tự khai thác.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:30:47 +0700</t>
+          <t>Thu, 14 May 2026 18:48:56 +0700</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
+          <t>http://vietstock.vn/2026/05/dgc-gap-rut-kiem-toan-bao-cao-tai-chinh-de-co-phieu-som-thoat-dien-kiem-soat-830-1442666.htm</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
+          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
+          <t>Ủy ban Chứng khoán yêu cầu các doanh nghiệp nhà nước đẩy mạnh cổ phần hóa, thoái vốn gắn với niêm yết và đăng ký giao dịch trên thị trường.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 13:36:00 +0700</t>
+          <t>Thu, 14 May 2026 18:32:44 +0700</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
+          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
+          <t>Cổ phần hóa doanh nghiệp nhà nước: Nâng cao chất lượng và niêm yết</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
+          <t>Ng#224;y 14/5/2026, Ủy ban Chứng kho#225;n Nh#224; nước phối hợp với Cục Ph#225;t triển doanh nghiệp nh#224; nước - Bộ T#224;i ch#237;nh tổ chức Hội nghị phổ biến quy định của ph#225;p luật về c#244;ng ty đại ch#250;ng, huy động vốn, tho#225;i vốn đối với c#225;c doanh nghiệp nh#224; nước cổ phần h#243;a đang ni#234;m yết, đăng k#253; giao dịch tr#234;n thị trường chứng kho#225;n.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 12:30:00 +0700</t>
+          <t>Thu, 14 May 2026 10:18:48 GMT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
+          <t>https://vneconomy.vn/co-phan-hoa-doanh-nghiep-nha-nuoc-nang-cao-chat-luong-va-niem-yet.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
+          <t>Blog chứng khoán: Trụ ngân hàng đủ sức thay thế?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
+          <t>Sự cộng hưởng hiếm c#243; giữa nh#243;m Vin v#224; c#225;c trụ ng#226;n h#224;ng gi#250;p VNI c#243; phi#234;n tăng mạnh l#234;n đỉnh cao mới. Tuy nhi#234;n sự cộng hưởng lan tỏa đến c#225;c cổ phiếu vẫn chưa tương xứng, đặc biệt thanh khoản lại thể hiện mức sụt giảm đ#225;ng kể.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:47:00 +0700</t>
+          <t>Thu, 14 May 2026 09:36:21 GMT</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1776,29 +1776,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-tru-ngan-hang-du-suc-thay-the.htm</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 10:16:00 +0700</t>
+          <t>Thu, 14 May 2026 16:06:50 +0700</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1806,29 +1806,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
+          <t>Chứng khoán Việt Nam lập kỷ lục chưa từng có, nhưng "bữa tiệc" không dành cho tất cả</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
+          <t>Sự bứt phá của nhóm Vingroup tạo hiệu ứng mạnh lên chỉ số chung, nhưng cũng khiến bức tranh thị trường trở nên “lệch pha”.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 03:07:13 GMT</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-lap-ky-luc-chua-tung-co-nhung-bua-tiec-khong-danh-cho-tat-ca-188260514151243612.chn</t>
         </is>
       </c>
     </row>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
+          <t>Sau 3 năm thua lỗ, DDG tiếp tục báo lỗ quý 1, đối diện nguy cơ hủy niêm yết</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
+          <t>Ngày 11/05, Sở Giao dịch Chứng khoán Hà Nội (HNX) thông báo đưa cổ phiếu DDG của CTCP Đầu tư Công nghiệp Xuất nhập khẩu Đông Dương vào diện cảnh báo do doanh nghiệp thua lỗ trong 3 năm liên tiếp (2023 - 2025), đồng thời báo cáo tài chính riêng và hợp nhất đều nhận ý kiến kiểm toán ngoại trừ trong cùng giai đoạn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 10:00:00 +0700</t>
+          <t>Thu, 14 May 2026 15:30:47 +0700</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
+          <t>http://vietstock.vn/2026/05/sau-3-nam-thua-lo-ddg-tiep-tuc-bao-lo-quy-1-doi-dien-nguy-co-huy-niem-yet-830-1442453.htm</t>
         </is>
       </c>
     </row>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
+          <t>Chứng khoán T-Cap thay Chủ tịch và Tổng Giám đốc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
+          <t>Bà Nguyễn Thị Hằng rời ghế Chủ tịch HĐQT để đảm nhiệm chức Tổng giám đốc Chứng khoán T-Cap. Tân Chủ tịch thay thế là ông Phạm Văn Khiêm.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 09:42:00 +0700</t>
+          <t>Thu, 14 May 26 13:36:00 +0700</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1896,29 +1896,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
+          <t>https://cafef.vn/chung-khoan-t-cap-thay-chu-tich-va-tong-giam-doc-188260514113110855.chn</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
+          <t>Triển vọng cổ phiếu 2026: Điểm tựa từ lợi nhuận doanh nghiệp và định giá</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
+          <t>Chứng khoán Việt Nam đang mở ra biên an toàn hấp dẫn khi định giá P/E lùi về vùng thấp nhất 1 thập kỷ. Sự bứt phá của lợi nhuận doanh nghiệp ngay trong quý 1/2026, cùng câu chuyện giải ngân hạ tầng và cột mốc nâng hạng thị trường từ FTSE, hứa hẹn tạo nên những động lực cốt lõi định hình lại dòng tiền đầu tư trong thời gian tới, dẫu bài toán về rủi ro tập trung vốn hóa vẫn là một biến số cần cẩn trọng.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:10:00 +0700</t>
+          <t>Thu, 14 May 2026 12:30:00 +0700</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
+          <t>http://vietstock.vn/2026/05/trien-vong-co-phieu-2026-diem-tua-tu-loi-nhuan-doanh-nghiep-va-dinh-gia-830-1442416.htm</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Phó Giám đốc SSI Research chỉ ra hai cổ phiếu bán lẻ "sáng cửa" nhờ câu chuyện IPO khủng và định giá hấp dẫn</t>
+          <t>Một văn bản quan trọng có thể đẩy nhanh tiến độ GPMB, CTCK chỉ ra loạt doanh nghiệp bất động sản dự báo hưởng lợi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mặc dù triển vọng dài hạn của ngành bán lẻ vẫn rất khả quan với định giá P/E dự phóng thấp hơn trung bình 5 năm, song chuyên gia cho rằng nhà đầu tư ngắn hạn cần giữ thái độ thận trọng.</t>
+          <t>Theo ACBS, dự thảo Luật Đất đai sửa đổi 2026 có thể giúp rút ngắn thời gian thu hồi đất, minh bạch hóa chi phí đền bù và tạo lợi thế cho các doanh nghiệp có nền tảng tài chính tốt.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:03:00 +0700</t>
+          <t>Thu, 14 May 26 10:47:00 +0700</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://cafef.vn/pho-giam-doc-ssi-research-chi-ra-hai-co-phieu-ban-le-sang-cua-nho-cau-chuyen-ipo-khung-va-dinh-gia-hap-dan-188260513222817243.chn</t>
+          <t>https://cafef.vn/mot-van-ban-quan-trong-co-the-day-nhanh-tien-do-gpmb-ctck-chi-ra-loat-doanh-nghiep-bat-dong-san-du-bao-huong-loi-188260514104732194.chn</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Một doanh nghiệp cao su bất ngờ tăng trần 5 phiên, HOSE yêu cầu giải trình</t>
+          <t>Cục trưởng Cục Phát triển DNNN: Huy động vốn qua thị trường chứng khoán là một kênh quan trọng đối với DNNN đã cổ phần hoá</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Trong 5 phiên liên tiếp từ 07-13/05/2026, cổ phiếu HRC của CTCP Cao su Hòa Bình (Horuco) đều tím trần. Với diễn biến này, Sở Giao dịch Chứng khoán TP.HCM (HOSE) đã có văn bản yêu cầu Horuco giải trình.</t>
+          <t>Cùng với chủ trương đẩy mạnh cổ phần hoá, thoái vốn, tuy giảm mạnh về số lượng nhưng các DNNN vẫn nắm giữ nguồn lực lớn về vốn, tài sản, công nghệ, nhân lực chất lượng cao, đóng góp đáng kể vào ngân sách nhà nước.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:17:24 +0700</t>
+          <t>Thu, 14 May 26 10:16:00 +0700</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1986,29 +1986,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/mot-doanh-nghiep-cao-su-bat-ngo-tang-tran-5-phien-hose-yeu-cau-giai-trinh-830-1442288.htm</t>
+          <t>https://cafef.vn/cuc-truong-cuc-phat-trien-dnnn-huy-dong-von-qua-thi-truong-chung-khoan-la-mot-kenh-quan-trong-doi-voi-dnnn-da-co-phan-hoa-188260514101608969.chn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gelex Electric tăng vốn điều lệ vượt 6.400 tỷ đồng sau đợt phát hành cổ phiếu thưởng</t>
+          <t>Chuyên gia SSI Research: Thiếu vắng thông tin thị trường có thể biến động mạnh, quan sát nhóm bán lẻ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kết thúc đợt phát hành ngày 6/5/2026, Gelex Electric đã phân phối thành công gần 274,5 triệu cổ phiếu cho 5.060 cổ đông, qua đó tăng vốn điều lệ lên mức gần 6.405 tỷ đồng.</t>
+          <t>Thị trường chứng kho#225;n đ#227; phục hồi khoảng 300 điểm từ đ#225;y th#225;ng 3 v#224; đ#227; phản #225;nh phần lớn c#225;c th#244;ng tin t#237;ch cực như n#226;ng hạng, hạ nhiệt căng thẳng Trung Đ#244;ng v#224; kết quả kinh doanh khả quan. Trong khi th#225;ng 5 l#224; giai đoạn thiếu th#244;ng tin hỗ trợ hơn, thị trường c#243; thể biến động mạnh hơn.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 17:09:00 +0700</t>
+          <t>Thu, 14 May 2026 03:07:13 GMT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2016,29 +2016,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://cafef.vn/gelex-electric-tang-von-dieu-le-vuot-6400-ty-dong-sau-dot-phat-hanh-co-phieu-thuong-188260513164543308.chn</t>
+          <t>https://vneconomy.vn/chuyen-gia-ssi-research-thieu-vang-thong-tin-thi-truong-co-the-bien-dong-manh-quan-sat-nhom-ban-le.htm</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
+          <t>Ngày 14/05/2026: 10 cổ phiếu nóng dưới góc nhìn PTKT của Vietstock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
+          <t>Các cổ phiếu nóng được phân tích trong báo cáo của Phòng Tư vấn Vietstock gồm: GEX, HDB, MSN, MBB, NLG, SHB, TPB, TCB, VPB, VNM.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:25:11 +0700</t>
+          <t>Thu, 14 May 2026 10:00:00 +0700</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
+          <t>http://vietstock.vn/2026/05/ngay-14052026-10-co-phieu-nong-duoi-goc-nhin-ptkt-cua-vietstock-585-1442206.htm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
+          <t>Chủ tịch UBCKNN chỉ ra yếu tố "sống còn" để chứng khoán Việt Nam thu hút dòng vốn ngoại</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
+          <t>Theo lãnh đạo UBCKNN, việc minh bạch hóa thông tin và huy động vốn thông qua thị trường quốc tế là yếu tố rất quan trọng, đặc biệt trong việc thu hút các nhà đầu tư tổ chức và nhà đầu tư nước ngoài có xu hướng gắn bó dài hạn với doanh nghiệp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:44:52 GMT</t>
+          <t>Thu, 14 May 26 09:42:00 +0700</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2076,29 +2076,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
+          <t>https://cafef.vn/chu-tich-ubcknn-chi-ra-yeu-to-song-con-de-chung-khoan-viet-nam-thu-hut-dong-von-ngoai-188260514094307668.chn</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
+          <t>Dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM, Xây dựng Hòa Bình đang làm ăn ra sao?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
+          <t>Dù ghi nhận lợi nhuận quý I/2026 tăng gấp hơn 4 lần so với cùng kỳ, Xây dựng Hòa Bình vẫn tiếp tục dẫn đầu danh sách chậm đóng bảo hiểm TP.HCM với số tiền gần 71,1 tỷ đồng.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:03:42 GMT</t>
+          <t>Thu, 14 May 26 08:10:00 +0700</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2106,29 +2106,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
+          <t>https://cafef.vn/dan-dau-danh-sach-cham-dong-bao-hiem-tphcm-xay-dung-hoa-binh-dang-lam-an-ra-sao-188260514081107854.chn</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
+          <t>Cổ phiếu dầu khí hút tiền nhà đầu tư trong nước</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
+          <t>Toàn bộ cổ phiếu dầu khí bật mạnh, trong đó GAS chạm trần và dẫn đầu danh sách "trụ đỡ" của VN-Index trước áp lực xả hàng cổ phiếu Vingroup.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:07:49 GMT</t>
+          <t>Wed, 13 May 2026 16:25:11 +0700</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
+          <t>https://vnexpress.net/co-phieu-dau-khi-hut-tien-nha-dau-tu-trong-nuoc-5073515.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
+          <t>SSIAM - CCIX và Daiwa ký kết hợp tác, mở rộng đầu tư vốn Nhật Bản vào Việt Nam</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
+          <t>SSI, CCI CrossBorder (CCIX) v#224; Daiwa Corporate Investment (DCI) vừa k#253; kết Thỏa thuận hợp tác nhằm thiết lập khu#244;n khổ hợp t#225;c chiến lược, hướng tới tạo lập v#224; mở rộng c#225;c cơ hội đồng đầu tư v#224; k#234;́t n#244;́i t#224;i trợ vốn giữa các định ch#234;́ tài chính Nhật Bản với c#225;c doanh nghiệp Việt Nam.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:08:00 +0700</t>
+          <t>Wed, 13 May 2026 07:44:52 GMT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
+          <t>https://vneconomy.vn/ssiam-ccix-va-daiwa-ky-ket-hop-tac-mo-rong-dau-tu-von-nhat-ban-vao-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
+          <t>Cổ phiếu dầu khí phục hồi mạnh, GAS kịch trần</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
+          <t>Sự yếu ớt của nh#243;m cổ phiếu dẫn dắt tiếp tục g#226;y sức #233;p l#234;n VN-Index s#225;ng nay d#249; độ rộng chỉ số kh#244;ng thực sự k#233;m. Mức độ ph#226;n h#243;a v#224; ổn định ở chỉ số tạo điều kiện cho d#242;ng tiền ngắn hạn hoạt động mạnh hơn, đặc biệt nh#243;m dầu kh#237; đang phục hồi kh#225; ấn tượng.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 09:16:01 GMT</t>
+          <t>Wed, 13 May 2026 05:03:42 GMT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2196,29 +2196,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
+          <t>https://vneconomy.vn/co-phieu-dau-khi-phuc-hoi-manh-gas-kich-tran.htm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VN-Index quay lại mốc 1.900 điểm</t>
+          <t>Ngại rủi ro, quỹ SGI Capital duy trì tiền mặt cao hơn 70%</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bất chấp hai cổ phiếu "họ" Vingroup tiếp tục giảm, VN-Index vẫn tăng hơn 5 điểm, lên 1.901 điểm nhờ trạng thái hưng phấn của nhóm dầu khí và một số mã ngân hàng.</t>
+          <t>SGI Capital tiếp tục giữ tỷ trọng tiền mặt cao l#234;n 70,49%, c#242;n lại l#224; ph#226;n bổ v#224;o danh mục c#225;c cổ phiếu gồm DRI, VIP, FMC, BWE, TLG, FPT, ACB, SIP, MWG.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:10:36 +0700</t>
+          <t>Wed, 13 May 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vn-index-quay-lai-moc-1-900-diem-5073096.html</t>
+          <t>https://vneconomy.vn/ngai-rui-ro-quy-sgi-capital-duy-tri-tien-mat-cao-hon-70.htm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
+          <t>Vì sao nhà đầu tư 'chưa về bờ' dù VN-Index vượt đỉnh?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
+          <t>Nhiều nhà đầu tư vẫn đang lỗ vài chục phần trăm vì danh mục tập trung vào chứng khoán, công nghệ, dầu khí mà không có cổ phiếu họ Vingroup.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:52:14 GMT</t>
+          <t>Wed, 13 May 2026 06:08:00 +0700</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
+          <t>https://vnexpress.net/vi-sao-nha-dau-tu-chua-ve-bo-du-vn-index-vuot-dinh-5072532.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SJC lãi kỷ lục dù doanh thu thấp nhất 10 năm</t>
+          <t>Blog chứng khoán: Thanh khoản giảm mạnh, thị trường “xoay trụ”?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Doanh thu ở mức thấp nhất một thập kỷ, Công ty SJC vẫn có lợi nhuận sau thuế tăng 9% lên mức kỷ lục 425,5 tỷ đồng năm ngoái.</t>
+          <t>Ảnh hưởng của c#225;c cổ phiếu vốn h#243;a lớn nhất l#224; VIC, VHM, VCB kh#244;ng qu#225; mạnh trong khi kh#225; nhiều blue-chips tầm trung lại mạnh l#234;n. VNI được neo giữ tốt tạo điều kiện cho số lớn cổ phiếu phục hồi.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:13:58 +0700</t>
+          <t>Tue, 12 May 2026 09:16:01 GMT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sjc-lai-ky-luc-du-doanh-thu-thap-nhat-10-nam-5072912.html</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-thanh-khoan-giam-manh-thi-truong-xoay-tru.htm</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
+          <t>Ước tính 17/26 ngân hàng niêm yết không đạt tỷ lệ cấp tín dụng so với huy động vốn theo tiêu chí mới</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
+          <t>Chứng kho#225;n Rồng Việt (VDSC) ước t#237;nh c#243; 17/26 ng#226;n h#224;ng ni#234;m yết kh#244;ng đạt tỷ lệ cấp t#237;n dụng so với huy động vốn (CDR) trong qu#253; 1/2026 nếu chiếu theo quy định mới dự kiến, như một c#225;ch để h#236;nh dung th#225;ch thức rất lớn trong hai năm tới li#234;n quan chi ph#237; tu#226;n thủ.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:49:46 GMT</t>
+          <t>Tue, 12 May 2026 06:52:14 GMT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
+          <t>https://vneconomy.vn/uoc-tinh-1726-ngan-hang-niem-yet-khong-dat-ty-le-cap-tin-dung-so-voi-huy-dong-von-theo-tieu-chi-moi.htm</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
+          <t>Loại trừ nhóm Vingroup, định giá thị trường ngày càng rẻ hơn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
+          <t>Khi d#242;ng tiền đầu cơ theo đuổi lợi nhuận ngắn hạn v#224; v#224;o một nh#243;m cổ phiếu định gi#225; rất cao, thị trường lại bắt đầu cho ch#250;ng ta những cơ hội đầu tư c#225;c doanh nghiệp c#243; kết quả kinh doanh t#237;ch cực với định gi#225; rẻ nhưng bị d#242;ng tiền bỏ qua.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:27:18 GMT</t>
+          <t>Mon, 11 May 2026 12:49:46 GMT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2346,37 +2346,37 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
+          <t>https://vneconomy.vn/loai-tru-nhom-vingroup-dinh-gia-thi-truong-ngay-cang-re-hon.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chứng khoán Việt Nam "gồng mình" giữa lúc thị trường châu Á đỏ lửa</t>
+          <t>Blue-chips giảm la liệt, “tiền nóng” co cụm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Khép lại phiên giao dịch ngày 15-5, thị trường chứng khoán Việt Nam chịu áp lực điều chỉnh sau nhịp phục hồi mạnh trước đó</t>
+          <t>Gần như to#224;n bộ cổ phiếu trong rổ blue-chips VN30 lao dốc chiều nay, bao gồm cả c#225;c trụ dẫn VIC, VHM. Điều ng#224;y ngay lập tức t#225;c động đến VN-Index, đẩy chỉ số n#224;y đảo chiều giảm 1,04% v#224; đ#225;nh mất lu#244;n mốc 1900 điểm.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 18:45:00 +0700</t>
+          <t>Mon, 11 May 2026 08:27:18 GMT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://cafef.vn/chung-khoan-viet-nam-gong-minh-giua-luc-thi-truong-chau-a-do-lua-188260515184509181.chn</t>
+          <t>https://vneconomy.vn/blue-chips-giam-la-liet-tien-nong-co-cum.htm</t>
         </is>
       </c>
     </row>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sốt dòng tiền ở nhóm cổ phiếu dầu khí</t>
+          <t>DN dược vừa bị thu hồi lô thuốc nhỏ mắt: Mỗi năm thu 500 tỷ, từng bị phạt vì chất lượng thuốc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
+          <t>Pharmedic – doanh nghiệp dược vừa bị yêu cầu thu hồi lô thuốc nhỏ mắt trên toàn quốc, kinh doanh ổn định với doanh thu khoảng 500 tỷ mỗi năm.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:57:00 +0700</t>
+          <t>Sat, 16 May 26 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
+          <t>https://cafef.vn/dn-duoc-vua-bi-thu-hoi-lo-thuoc-nho-mat-moi-nam-thu-500-ty-tung-bi-phat-vi-chat-luong-thuoc-188260515234831986.chn</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
+          <t>Một cổ phiếu bị khối ngoại "xả" hơn 1.000 tỷ đồng trong tuần 11-15/5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
+          <t>Khối ngoại vẫn là điểm trừ lớn khi áp lực bán chưa có dấu hiệu hạ nhiệt rõ rệt.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 17:24:00 +0700</t>
+          <t>Sat, 16 May 26 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
+          <t>https://cafef.vn/mot-co-phieu-bi-khoi-ngoai-xa-hon-1000-ty-dong-trong-tuan-11-15-5-188260515235502376.chn</t>
         </is>
       </c>
     </row>
@@ -2448,17 +2448,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
+          <t>VN-Index tăng hoặc giảm không phản ánh đầy đủ thực trạng của thị trường chứng khoán, mà do bị ảnh hưởng bởi các cổ phiếu trụ.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:38:21 +0700</t>
+          <t>Sat, 16 May 2026 00:02:00 +0700</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2466,29 +2466,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
+          <t>Nhà đầu tư cá nhân mua ròng đột biến, gần 2.000 tỷ đồng</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n mua r#242;ng 1.946,9 tỷ đồng, trong đ#243; họ mua r#242;ng khớp lệnh l#224; 642,0 tỷ đồng.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:12:00 +0700</t>
+          <t>Fri, 15 May 2026 15:14:21 GMT</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
+          <t>https://vneconomy.vn/nha-dau-tu-ca-nhan-mua-rong-dot-bien-gan-2000-ty-dong.htm</t>
         </is>
       </c>
     </row>
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
+          <t>Lý do lương lãnh đạo Vietnam Airlines giảm 40-50%</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
+          <t>Ngành hàng không đang chịu sức ép rất lớn từ giá nhiên liệu bay. Vietnam Airlines phải cắt giảm mạnh các khoản đầu tư và chi phí vận hành. Doanh nghiệp áp dụng chính sách nghỉ không lương ở một số bộ phận, đồng thời giảm sâu thu nhập của đội ngũ lãnh đạo cấp cao. Theo đó, lương chủ tịch và tổng giám đốc giảm 50%, các phó tổng giám đốc giảm 40% và lãnh đạo cấp ban giảm 30%.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 15:48:00 +0700</t>
+          <t>Fri, 15 May 26 21:27:00 +0700</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2526,29 +2526,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
+          <t>https://cafef.vn/ly-do-luong-lanh-dao-vietnam-airlines-giam-40-50-188260515212806106.chn</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Thị trường tiền số hôm nay, 15-5: Giá Bitcoin sắp rơi mạnh?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
+          <t>Chuyên gia nhận định giá Bitcoin muốn tăng cần giữ vững trên mốc 82.000 USD. Ngược lại, giá có thể lùi về vùng 74.000 - 77.000 USD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 15:15:53 +0700</t>
+          <t>Fri, 15 May 26 21:25:00 +0700</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://cafef.vn/thi-truong-tien-so-hom-nay-15-5-gia-bitcoin-sap-roi-manh-188260515212557351.chn</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng liên quan đến ông Nguyễn Đức Thụy bất ngờ "tím lịm" 4 phiên liên tiếp</t>
+          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
+          <t>Sạc hệ thống pin lưu trữ (BESS) lúc giá rẻ và dùng vào giờ cao điểm giúp doanh nghiệp giảm đáng kể tiền điện hàng tháng, theo chuyên gia.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 14:50:00 +0700</t>
+          <t>Fri, 15 May 2026 20:00:00 +0700</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
+          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Thu hồi toàn quốc thuốc nhỏ mắt của Pharmedic, cổ phiếu PMC sụt gần 10%</t>
+          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ngày 14/05, Sở Y tế Lâm Đồng thông báo thu hồi trên toàn quốc lô thuốc Dung dịch nhỏ mắt Natri clorid 0.9% do không đạt tiêu chuẩn chất lượng về chỉ tiêu độ trong, thuộc mức độ vi phạm 3.</t>
+          <t>Đại diện Tân Hiệp Phát cho rằng doanh nghiệp tư nhân sẵn sàng đầu tư dài hạn, đổi mới công nghệ và cạnh tranh bằng năng lực thực chất nếu môi trường kinh doanh minh bạch, ổn định và dễ dự đoán.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:30:47 +0700</t>
+          <t>Fri, 15 May 2026 19:00:00 +0700</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2616,29 +2616,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/thu-hoi-toan-quoc-thuoc-nho-mat-cua-pharmedic-co-phieu-pmc-sut-gan-10-830-1442914.htm</t>
+          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
+          <t>Chứng khoán Việt Nam "gồng mình" giữa lúc thị trường châu Á đỏ lửa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
+          <t>Khép lại phiên giao dịch ngày 15-5, thị trường chứng khoán Việt Nam chịu áp lực điều chỉnh sau nhịp phục hồi mạnh trước đó</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:11:32 +0700</t>
+          <t>Fri, 15 May 26 18:45:00 +0700</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2646,29 +2646,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
+          <t>https://cafef.vn/chung-khoan-viet-nam-gong-minh-giua-luc-thi-truong-chau-a-do-lua-188260515184509181.chn</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Sốt dòng tiền ở nhóm cổ phiếu dầu khí</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
+          <t>Sau phiên lập đỉnh lịch sử 1.925 điểm, thị trường chứng khoán rung lắc mạnh trong ngày hôm nay (15/5) khi áp lực chốt lời lan rộng ở nhóm bluechip. Dù VN-Index giảm điểm, dòng tiền vẫn sôi động tại nhóm dầu khí. Đáng chú ý, cổ phiếu trong hệ sinh thái của "Bầu Thụy" liên tiếp tăng trần.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:03:11 +0700</t>
+          <t>Fri, 15 May 26 17:57:00 +0700</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2676,29 +2676,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
+          <t>https://cafef.vn/co-phieu-trong-he-sinh-thai-cua-bau-thuy-day-song-188260515170812506.chn</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
+          <t>Một thế lực vừa bán ròng đột biến gần 900 tỷ đồng cổ phiếu HOSE phiên cuối tuần</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
+          <t>Tự doanh CTCK bán ròng đột biến 870 tỷ đồng trên HOSE.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:00:00 +0700</t>
+          <t>Fri, 15 May 26 17:24:00 +0700</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
+          <t>https://cafef.vn/mot-the-luc-vua-ban-rong-dot-bien-gan-900-ty-dong-co-phieu-hose-phien-cuoi-tuan-188260515172436811.chn</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
+          <t>Áp lực bán chốt lời lan rộng sau khi VN-Index lập kỷ lục, nhất là ở các cổ phiếu trụ, khiến chứng khoán giảm gần 4 điểm.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:55:07 +0700</t>
+          <t>Fri, 15 May 2026 16:38:21 +0700</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Nhịp đập Thị trường 15/05: Nhóm năng lượng tiếp tục lội ngược dòng, VN-Index chưa thoát thế giằng co</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
+          <t>Kết thúc phiên giao dịch, VN-Index giảm 3.86 điểm (-0.2%), xuống mức 1,921.6 điểm; HNX-Index tăng 2.35 điểm (+0.92%), lên mức 257.42 điểm. Độ rộng toàn thị trường với sắc đỏ có phần lấn lướt hơn khi bên bán có 424 mã giảm và bên mua có 326 mã tăng. Sắc đỏ áp đảo trong rổ VN30 với 21 mã giảm và 9 mã tăng.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:58:20 +0700</t>
+          <t>Fri, 15 May 2026 16:12:00 +0700</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1505-nhom-nang-luong-tiep-tuc-loi-nguoc-dong-vn-index-chua-thoat-the-giang-co-1636-1442806.htm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
+          <t>Khối ngoại quay đầu bán ròng hơn 800 tỷ phiên VN-Index rung lắc, "xả" mạnh một cổ phiếu Bluechips</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
+          <t>Chiều mua, khối ngoại mua ròng mạnh nhất cổ phiếu BSR với giá trị khoảng 88 tỷ đồng.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 10:02:00 +0700</t>
+          <t>Fri, 15 May 26 15:48:00 +0700</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
+          <t>https://cafef.vn/khoi-ngoai-quay-dau-ban-rong-hon-800-ty-phien-vn-index-rung-lac-xa-manh-mot-co-phieu-bluechips-188260515154726983.chn</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Vietnam Airlines cắt giảm các dự án đầu tư, chi phí vận hành và điều chỉnh quỹ lương lãnh đạo để tiết kiệm chi phí trong bối cảnh giá nhiên liệu thế giới tăng mạnh.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 08:00:00 +0700</t>
+          <t>Fri, 15 May 2026 15:15:53 +0700</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
+          <t>Một cổ phiếu bất ngờ "tím lịm" 4 phiên liên tiếp</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
+          <t>Trong quá khứ, cổ phiếu này từng làm mưa làm gió trên thị trường với mức tăng sốc.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 07:28:00 +0700</t>
+          <t>Fri, 15 May 26 14:50:00 +0700</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
+          <t>https://cafef.vn/co-phieu-tung-lien-quan-den-ong-nguyen-duc-thuy-bat-ngo-tim-lim-4-phien-lien-tiep-188260515144918809.chn</t>
         </is>
       </c>
     </row>
@@ -2868,17 +2868,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Phân tích kỹ thuật phiên chiều 15/05: Giằng co</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>VN-Index giằng co sau khi vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) và có thể xảy ra hiện tượng throwdown trong ngắn hạn. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 06:02:00 +0700</t>
+          <t>Fri, 15 May 2026 13:11:32 +0700</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1505-giang-co-585-1442906.htm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
+          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 15 May 26 00:01:00 +0700</t>
+          <t>Fri, 15 May 2026 12:03:11 +0700</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2916,29 +2916,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
+          <t>Tổng Công ty Xây dựng Số 1 - CTCP (CC1) cho biết chọn Công ty TNHH Kiểm toán và Tư vấn UHY để tiến hành kỳ kiểm toán cho báo cáo tài chính 2025.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:41:13 GMT</t>
+          <t>Fri, 15 May 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
     </row>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t>Cổ phiếu Boeing mất gần 5% sau khi ông Trump cho biết Trung Quốc đồng ý mua 200 phi cơ, chỉ bằng nửa dự báo của giới phân tích.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 21:42:38 +0700</t>
+          <t>Fri, 15 May 2026 11:55:07 +0700</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2976,29 +2976,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
+          <t>Pomina, doanh nghiệp từng dẫn đầu thị phần thép xây dựng giai đoạn 2010, tiếp tục báo lỗ quý đầu năm nay, nâng lỗ lũy kế lên 3.660 tỷ đồng.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:16:00 GMT</t>
+          <t>Fri, 15 May 2026 10:58:20 +0700</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
+          <t>Chương trình IR Awards 2026 chính thức khởi động</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
+          <t>Chương trình vinh danh Doanh nghiệp niêm yết có hoạt động IR tốt nhất năm 2026 (IR Awards 2026) chính thức được khởi động. Đây là năm thứ 16 sự kiện được tổ chức bởi Vietstock, phối hợp cùng Hiệp hội Các nhà quản trị tài chính Việt Nam (VAFE), Tạp chí điện tử Tài chính và Cuộc sống (FiLi).</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 18:27:22 +0700</t>
+          <t>Fri, 15 May 2026 10:02:00 +0700</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3036,29 +3036,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
+          <t>http://vietstock.vn/2026/05/chuong-trinh-ir-awards-2026-chinh-thuc-khoi-dong-830-1442469.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 15/05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 15:48:25 +0700</t>
+          <t>Fri, 15 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1505-830-1441634.htm</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3078,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
+          <t>Dàn tỷ phú nổi tiếng thế giới tháp tùng Tổng thống Mỹ tới Trung Quốc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
+          <t>Hơn 10 lãnh đạo doanh nghiệp hàng đầu của Mỹ, trong đó có CEO Tesla Elon Musk, CEO Apple Tim Cook tháp tùng Tổng thống Donald Trump tới Bắc Kinh, Trung Quốc vào rạng sáng 14/5 (theo giờ địa phương).</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:45:00 +0700</t>
+          <t>Fri, 15 May 26 07:28:00 +0700</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
+          <t>https://cafef.vn/dan-ty-phu-noi-tieng-the-gioi-thap-tung-tong-thong-my-toi-trung-quoc-188260515072904742.chn</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
+          <t>15/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 15:36:00 +0700</t>
+          <t>Fri, 15 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
+          <t>http://vietstock.vn/2026/05/1505-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442740.htm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
+          <t>Dragon Capital: Giá cổ phiếu còn dư địa để phản ánh sát hơn nền tảng doanh nghiệp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
+          <t>Trong báo cáo mới nhất, Dragon Capital cho rằng câu chuyện nâng hạng không phải là điểm tựa duy nhất của thị trường.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:29:36 GMT</t>
+          <t>Fri, 15 May 26 00:01:00 +0700</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3156,29 +3156,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
+          <t>https://cafef.vn/dragon-capital-gia-co-phieu-con-dua-dia-de-phan-anh-sat-hon-nen-tang-doanh-nghiep-188260514223457193.chn</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
+          <t>Công ty chứng khoán nhận định gì khi VN-Index có đỉnh cao lịch sử mới?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 15/5/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 14:38:00 +0700</t>
+          <t>Thu, 14 May 2026 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
+          <t>https://vneconomy.vn/cong-ty-chung-khoan-nhan-dinh-gi-khi-vn-index-co-dinh-cao-lich-su-moi.htm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:32:00 +0700</t>
+          <t>Thu, 14 May 2026 21:42:38 +0700</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
+          <t>Khối ngoại bất ngờ mua ròng, tự doanh và tổ chức bán mạnh</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
+          <t>Khối ngoại h#244;m nay đảo chiều mua r#242;ng nhẹ 214,0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ mua r#242;ng 72,6 tỷ đồng. Nh#224; đầu tư c#225; nh#226;n trong nước mua r#242;ng 1223,6 tỷ đồng. Ph#237;a b#225;n đối ứng l#224; tự doanh v#224; tổ chức...</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 13:02:11 +0700</t>
+          <t>Thu, 14 May 2026 14:16:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-bat-ngo-mua-rong-tu-doanh-va-to-chuc-ban-manh.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
+          <t>Vietstock Daily 15/05/2026: Chinh phục đỉnh cao</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
+          <t>VN-Index bật tăng mạnh với cây nến xanh dài đồng thời phá vỡ hoàn toàn đỉnh cũ tháng 1/2026. Tuy nhiên, việc xuất hiện các phiên tăng giảm đan xen kèm theo khối lượng giao dịch trồi sụt thất thường cho thấy tâm lý nhà đầu tư còn thiếu sự ổn định.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:07:25 GMT</t>
+          <t>Thu, 14 May 2026 18:27:22 +0700</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3276,29 +3276,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
+          <t>http://vietstock.vn/2026/05/vietstock-daily-15052026-chinh-phuc-dinh-cao-1636-1442611.htm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
+          <t>Dù việc kiểm định nông sản đang quá tải, doanh nghiệp xin đầu tư phòng kiểm nghiệm vẫn phải chờ duyệt tới nửa năm vì nhiều thủ tục, theo Thứ trưởng Nông nghiệp &amp; Môi trường Hoàng Trung.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 11:24:00 +0700</t>
+          <t>Thu, 14 May 2026 15:48:25 +0700</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3306,29 +3306,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
+          <t>Khối ngoại đảo chiều mua ròng trong phiên VN-Index lập đỉnh lịch sử, gom mạnh hai cổ phiếu bluechips</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
+          <t>Giao dịch của khối ngoại là điểm cộng khi đảo chiều mua ròng sau chuỗi "xả hàng" miệt mài.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 09:02:00 +0700</t>
+          <t>Thu, 14 May 26 15:45:00 +0700</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
+          <t>https://cafef.vn/khoi-ngoai-dao-chieu-mua-rong-trong-phien-vn-index-lap-dinh-lich-su-gom-manh-hai-co-phieu-bluechips-188260514151318811.chn</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
+          <t>Đứng đầu “đế chế” nghìn tỷ USD, tài sản của Chủ tịch Samsung vẫn thua ông Phạm Nhật Vượng</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
+          <t>Tài sản của ông Phạm Nhật Vượng và Lee Jae-yong đều tăng vọt nhờ cổ phiếu Vingroup và và Samsung Electronics “bốc đầu”.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 08:30:00 +0700</t>
+          <t>Thu, 14 May 26 15:36:00 +0700</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3366,29 +3366,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
+          <t>https://cafef.vn/dung-dau-de-che-nghin-ty-usd-tai-san-cua-chu-tich-samsung-van-thua-ong-pham-nhat-vuong-188260514153649369.chn</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
+          <t>VN-Index đóng cửa ở đỉnh cao lịch sử mới, dòng tiền vẫn rất thận trọng</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
+          <t>Khả năng duy tr#236; sức mạnh của nh#243;m cổ phiếu dẫn dắt trong phi#234;n chiều nay l#224; một đảm bảo để VN-Index chốt s#225;t đỉnh cao nhất ng#224;y. Chỉ số đ#243;ng cửa đạt 1925,46 điểm, ch#237;nh thức c#243; đỉnh cao lịch sử mới. Tuy nhi#234;n thanh khoản sụt giảm mạnh 28% tr#234;n hai s#224;n cho thấy vẫn c#243; sự thiếu tin tưởng của d#242;ng tiền.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 08:00:00 +0700</t>
+          <t>Thu, 14 May 2026 08:29:36 GMT</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
+          <t>https://vneconomy.vn/vn-index-dong-cua-o-dinh-cao-lich-su-moi-dong-tien-van-rat-than-trong.htm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
+          <t>Hàng chục doanh nghiệp lớn đối mặt nguy cơ bị hủy tư cách đại chúng nếu không làm điều này trước 1/1/2027</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
+          <t>Các doanh nghiệp không đáp ứng điều kiện về cơ cấu cổ đông hoặc vốn chủ sở hữu sẽ được gia hạn một năm để khắc phục, đồng nghĩa với việc mốc 1/1/2027 sẽ trở thành “deadline” cuối cùng trước khi bị hủy tư cách công ty đại chúng theo quy định.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:02:00 +0700</t>
+          <t>Thu, 14 May 26 14:38:00 +0700</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
+          <t>https://cafef.vn/hang-chuc-doanh-nghiep-lon-doi-mat-nguy-co-bi-huy-tu-cach-dai-chung-neu-khong-lam-dieu-nay-truoc-1-1-2027-188260514143734406.chn</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>Công ty xây dựng của BCG lại bị nhắc chậm công bố BCTC quý 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
+          <t>CTCP Tập đoàn Xây dựng TRACODI (HOSE: TCD) bị HOSE nhắc nhở lần 2 vì chưa công bố báo cáo tài chính quý 1/2026. Đây là lần mới nhất trong chuỗi vi phạm công bố thông tin kéo dài của doanh nghiệp xây dựng thuộc hệ sinh thái Bamboo Capital.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 05:00:00 +0700</t>
+          <t>Thu, 14 May 2026 14:32:00 +0700</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>http://vietstock.vn/2026/05/cong-ty-xay-dung-cua-bcg-lai-bi-nhac-cham-cong-bo-bctc-quy-1-830-1442456.htm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cổ phiếu từng gây sốt với 20 phiên kịch trần liên tiếp lại "nổi sóng"</t>
+          <t>Phân tích kỹ thuật phiên chiều 14/05: Có thể vượt đỉnh tháng 1/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thị giá nhờ đó tăng một mạch từ vùng 30.000 đồng lên sát 100.000 đồng, tương ứng tăng xấp xỉ 220% chỉ sau khoảng 1 tháng.</t>
+          <t>VN-Index tăng mạnh trở lại và có thể vượt đỉnh cũ tháng 01/2026 (tương đương vùng 1,900-1,920 điểm) trong các phiên tới. HNX-Index diễn biến giằng co đồng thời xuất hiện mẫu hình nến gần giống Long-Legged Doji.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 14 May 26 00:06:00 +0700</t>
+          <t>Thu, 14 May 2026 13:02:11 +0700</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3486,29 +3486,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://cafef.vn/co-phieu-tung-gay-sot-voi-20-phien-kich-tran-lien-tiep-lai-noi-song-188260513223933796.chn</t>
+          <t>http://vietstock.vn/2026/05/phan-tich-ky-thuat-phien-chieu-1405-co-the-vuot-dinh-thang-12026-585-1442458.htm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>Đồng thuận bất ngờ, VN-Index lại “nhăm nhe” vượt đỉnh</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
+          <t>Nửa đầu phi#234;n giao dịch s#225;ng nay thị trường rất yếu với c#225;c trụ lũ lượt đỏ, nhưng từ 10h30 trở đi, nh#243;m dẫn dắt đồng thuận bất ngờ. Loạt cổ phiếu lớn phục hồi v#224; tăng mạnh đẩy VN-Index leo dốc li#234;n tục v#224; chốt phi#234;n tăng 1,06% l#234;n mức 1918,51 điểm.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:05:00 +0700</t>
+          <t>Thu, 14 May 2026 05:07:25 GMT</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3516,29 +3516,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://vneconomy.vn/dong-thuan-bat-ngo-vn-index-lai-nham-nhe-vuot-dinh.htm</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
+          <t>Đầu tư Thương mại SMC muốn huy động hơn 368 tỷ đồng từ cổ đông để trả nợ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
+          <t>Đầu tư Thương mại SMC muốn chào bán hơn 36,8 triệu cổ phiếu cho cổ đông với giá 10.000 đồng/cổ phiếu, nhằm huy động hơn 368 tỷ đồng để thanh toán các khoản nợ vay và nợ nhà cung cấp của công ty.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:24:07 GMT</t>
+          <t>Thu, 14 May 26 11:24:00 +0700</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
+          <t>https://cafef.vn/dau-tu-thuong-mai-smc-muon-huy-dong-hon-368-ty-dong-tu-co-dong-de-tra-no-188260514112146077.chn</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng gần 400 tỷ trong phiên 13/5, cổ phiếu nào là tâm điểm?</t>
+          <t>Hơn nửa số mã dầu khí vẫn giữ xu hướng tăng dài hạn suốt 5 tháng</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tự doanh CTCK bán ròng 379 tỷ đồng trên HOSE.</t>
+          <t>Sau nhịp tăng mạnh đầu năm 2026, nhóm dầu khí đã trải qua giai đoạn điều chỉnh sâu khi hàng loạt cổ phiếu đầu ngành giảm 30-50% so với vùng đỉnh gần nhất. Tuy nhiên, dòng tiền tại nhóm này vẫn chưa rút lui hoàn toàn khi hơn 50% số mã được theo dõi đã duy trì xu hướng tăng dài hạn trong 5 tháng.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 18:44:00 +0700</t>
+          <t>Thu, 14 May 2026 09:02:00 +0700</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3576,29 +3576,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://cafef.vn/tu-doanh-ctck-ban-rong-gan-400-ty-trong-phien-13-5-co-phieu-nao-la-tam-diem-188260513184457858.chn</t>
+          <t>http://vietstock.vn/2026/05/hon-nua-so-ma-dau-khi-van-giu-xu-huong-tang-dai-han-suot-5-thang-830-1442029.htm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>CafeF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
+          <t>Quỹ Đầu tư do bà Nguyễn Thanh Phượng làm Chủ tịch bán hết cổ phiếu VCI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
+          <t>Quỹ Đầu tư Bản Việt Discovery bán ra toàn bộ 135.000 cổ phiếu VCI trong thời gian từ 6-8/5/2026, qua đó không còn là cổ đông của Vietcap.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 18:30:33 +0700</t>
+          <t>Thu, 14 May 26 08:30:00 +0700</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
+          <t>https://cafef.vn/quy-dau-tu-do-ba-nguyen-thanh-phuong-lam-chu-tich-ban-het-co-phieu-vci-188260514080941252.chn</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CafeF</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>"Vàng đang trên đà vọt lên 10.000 USD", một tỷ phú dồn cả tỷ USD mua vàng, bạc dù vừa "thua đau đớn"</t>
+          <t>Top cổ phiếu đáng chú ý đầu phiên 14/05</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Có một người đàn ông đang đặt cược 98% gia tài tỷ USD của mình vào kim loại quý, ngay giữa lúc thị trường rung lắc dữ dội nhất.</t>
+          <t>Danh sách các mã cổ phiếu tăng và giảm mạnh nhất những phiên gần đây theo số liệu thống kê của Vietstock.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 13 May 26 16:48:00 +0700</t>
+          <t>Thu, 14 May 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://cafef.vn/vang-dang-tren-da-vot-len-10000-usd-mot-ty-phu-don-ca-ty-usd-mua-vang-bac-du-vua-thua-dau-don-188260513164354302.chn</t>
+          <t>http://vietstock.vn/2026/05/top-co-phieu-dang-chu-y-dau-phien-1405-830-1442191.htm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
+          <t>14/05: Đọc gì trước giờ giao dịch chứng khoán?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
+          <t>Cùng điểm lại những tin tức tài chính - kinh tế trong nước và quốc tế đáng chú ý trong 24h qua trước giờ giao dịch hôm nay.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:35:03 +0700</t>
+          <t>Thu, 14 May 2026 06:02:00 +0700</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
+          <t>http://vietstock.vn/2026/05/1405-doc-gi-truoc-gio-giao-dich-chung-khoan-830-1442326.htm</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3678,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
+          <t>Hà Nội có thể thí điểm cho thuê một phần lòng đường, vỉa hè cao nhất 45.000 đồng một m2 mỗi tháng để phát triển kinh tế đô thị, kinh tế đêm.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:00:00 +0700</t>
+          <t>Thu, 14 May 2026 05:00:00 +0700</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
+          <t>Dù gây thiệt hại ngắn hạn, xung đột Trung Đông được giới phân tích xem là cú hích buộc thế giới định hình lại chuỗi cung ứng năng lượng dài hạn.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 15:47:20 +0700</t>
+          <t>Thu, 14 May 2026 00:05:00 +0700</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
     </row>
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
+          <t>Thị trường vẫn đang tìm điểm cân bằng mới và giao dịch khá lỏng lẻo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 14/5/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:54 GMT</t>
+          <t>Wed, 13 May 2026 14:24:07 GMT</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
+          <t>https://vneconomy.vn/thi-truong-van-dang-tim-diem-can-bang-moi-va-giao-dich-kha-long-leo.htm</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
+          <t>Gia Lai đề xuất xây trung tâm đấu giá cá ngừ đầu tiên Đông Nam Á</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
+          <t>UBND tỉnh Gia Lai đề xuất đầu tư cảng cá thông minh Tam Quan, hướng tới hình thành trung tâm logistics thủy sản và trung tâm đấu giá cá ngừ đại dương đầu tiên ở Đông Nam Á.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:35:54 +0700</t>
+          <t>Wed, 13 May 2026 18:30:33 +0700</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
+          <t>https://vnexpress.net/gia-lai-de-xuat-xay-trung-tam-dau-gia-ca-ngu-dau-tien-dong-nam-a-5073426.html</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
+          <t>Đơn vị vận hành HoSE và HNX lên kế hoạch lãi kỷ lục</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
+          <t>Sở Giao dịch chứng khoán Việt Nam dự kiến có lãi kỷ lục 2.987 tỷ đồng năm nay với nhiều kế hoạch như ETF vàng, sàn carbon và startup.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:00:00 +0700</t>
+          <t>Wed, 13 May 2026 16:35:03 +0700</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
+          <t>https://vnexpress.net/don-vi-van-hanh-hose-va-hnx-len-ke-hoach-lai-ky-luc-5073472.html</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
+          <t>​Chuyên gia quốc tế: Việt Nam có cơ hội thành 'tọa độ vàng' siêu sự kiện</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
+          <t>Chính sách mở đường và làn sóng đầu tư hạ tầng quy mô lớn đang tạo đà cho nền công nghiệp văn hóa Việt Nam bứt phá, vươn tầm thành điểm đến mới của kinh tế trải nghiệm toàn cầu.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 10:46:42 +0700</t>
+          <t>Wed, 13 May 2026 16:00:00 +0700</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
+          <t>https://vnexpress.net/chuyen-gia-quoc-te-viet-nam-co-co-hoi-thanh-toa-do-vang-sieu-su-kien-5073499.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
+          <t>Ngân hàng tiếp tục rao bán nhà máy nông sản hơn 1.200 tỷ liên quan bà Trương Mỹ Lan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
+          <t>VietinBank phát mãi lần hai nhà máy Tanifood Tây Ninh liên quan vụ án Vạn Thịnh Phát với giá khởi điểm 1.200 tỷ đồng, thấp hơn 10% so với lần rao bán trước.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:40:31 GMT</t>
+          <t>Wed, 13 May 2026 15:47:20 +0700</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3876,29 +3876,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
+          <t>https://vnexpress.net/ngan-hang-tiep-tuc-rao-ban-nha-may-nong-san-hon-1-200-ty-lien-quan-ba-truong-my-lan-5073438.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
+          <t>Dòng tiền mạnh lên, thị trường phân hóa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
+          <t>Thanh khoản khớp lệnh hai s#224;n chiều nay tăng 67% so với buổi s#225;ng, trong đ#243; HoSE tăng gần 69% l#234;n mức cao nhất 7 tuần. Độ rộng cho thấy cổ phiếu c#243; sự phục hồi kh#225; tốt, mặc d#249; ảnh hưởng của trụ khiến VN-Index kh#244;ng thể vượt qua tham chiếu.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:08:00 +0700</t>
+          <t>Wed, 13 May 2026 08:33:54 GMT</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
+          <t>https://vneconomy.vn/dong-tien-manh-len-thi-truong-phan-hoa.htm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Thị trường đang tìm điểm cân bằng mới</t>
+          <t>Phát hiện giá Bitcoin tương quan với thị trường cá cược thể thao</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
+          <t>Diễn biến giá của Bitcoin và quỹ ETF lớn nhất thế giới về cá cược thể thao có mối liên hệ về mặt thống kê tới hơn 80%.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 15:36:11 GMT</t>
+          <t>Wed, 13 May 2026 14:35:54 +0700</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3936,29 +3936,29 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
+          <t>https://vnexpress.net/phat-hien-gia-bitcoin-tuong-quan-voi-thi-truong-ca-cuoc-the-thao-5073356.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
+          <t>Agribank thúc đẩy giải pháp ngân hàng số khu vực Tây Nam Bộ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
+          <t>Agribank đẩy mạnh các giải pháp thanh toán không tiền mặt, mở rộng hạ tầng giao dịch, thúc đẩy tài chính số khu vực nông thôn Tây Nam Bộ.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:02:19 GMT</t>
+          <t>Wed, 13 May 2026 14:00:00 +0700</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
+          <t>https://vnexpress.net/agribank-thuc-day-giai-phap-ngan-hang-so-khu-vuc-tay-nam-bo-5073401.html</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Trung Quốc thâu tóm 'ông lớn' thuốc kháng sinh Imexpharm</t>
+          <t>VinFast sẽ tách mảng sản xuất tại Việt Nam</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lian SGP Holding thuộc tập đoàn Livzon Pharmaceutical (Trung Quốc) vừa mua 68% vốn và trở thành cổ đông lớn nhất của doanh nghiệp đứng đầu mảng thuốc kháng sinh Imexpharm.</t>
+          <t>VinFast dự kiến chuyển giao mảng sản xuất cho nhóm nhà đầu tư mới với giá khoảng 530 triệu USD và ông Phạm Nhật Vượng vẫn tham gia pháp nhân mới nhưng giảm tỷ lệ sở hữu.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 16:21:11 +0700</t>
+          <t>Wed, 13 May 2026 10:46:42 +0700</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-trung-quoc-thau-tom-ong-lon-thuoc-khang-sinh-imexpharm-5073089.html</t>
+          <t>https://vnexpress.net/vinfast-se-tach-mang-san-xuat-tai-viet-nam-5073349.html</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
+          <t>Mở tài khoản chứng khoán qua VNeID: Tiện ích hiện đại cho nhà đầu tư</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
+          <t>Hiện nay, b#234;n cạnh c#225;c giao dịch h#224;nh ch#237;nh v#224; ng#226;n h#224;ng, người d#226;n đ#227; c#243; thể thực hiện mở t#224;i khoản chứng kho#225;n trực tiếp th#244;ng qua ứng dụng VNeID của Bộ C#244;ng an. Đ#226;y l#224; bước tiến mới trong việc tận dụng dữ liệu d#226;n cư quốc gia để đơn giản h#243;a thủ tục t#224;i ch#237;nh cho c#244;ng d#226;n.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:25:30 GMT</t>
+          <t>Wed, 13 May 2026 02:40:31 GMT</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
+          <t>https://vneconomy.vn/mo-tai-khoan-chung-khoan-qua-vneid-tien-ich-hien-dai-cho-nha-dau-tu.htm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
+          <t>Giới đầu tư kỳ vọng gì vào thượng đỉnh Mỹ - Trung?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
+          <t>Giới đầu tư dự báo khó có thỏa thuận kinh tế đột phá, dồn chú ý vào diễn biến lĩnh vực AI tại cuộc gặp lãnh đạo Mỹ - Trung.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:09:47 GMT</t>
+          <t>Wed, 13 May 2026 00:08:00 +0700</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
+          <t>https://vnexpress.net/gioi-dau-tu-ky-vong-gi-vao-thuong-dinh-my-trung-5073144.html</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
+          <t>Thị trường đang tìm điểm cân bằng mới</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 13/5/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:54:12 GMT</t>
+          <t>Tue, 12 May 2026 15:36:11 GMT</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-tim-diem-can-bang-moi.htm</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
+          <t>136 tỷ USD đầu tư cho các dự án điện giai đoạn 2026-2030, cổ phiếu nào hưởng lợi?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
+          <t>Quyết định số 1509/QĐ-BCT của Bộ C#244;ng Thương đưa ra kế hoạch đầu tư lớn cho giai đoạn 2026- 2030, bao gồm 118 tỷ USD (23,6 tỷ USD/năm) cho sản xuất năng lượng v#224; 18 tỷ USD (3,6 tỷ USD/năm) cho lưới điện.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 06:46:27 GMT</t>
+          <t>Tue, 12 May 2026 12:02:19 GMT</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
+          <t>https://vneconomy.vn/136-ty-usd-dau-tu-cho-cac-du-an-dien-giai-doan-2026-2030-co-phieu-nao-huong-loi.htm</t>
         </is>
       </c>
     </row>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
+          <t>Cổ phiếu tầm trung tăng tốt, VN-Index có “đổi trụ” thành công?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
+          <t>Những nỗ lực phục hồi về cuối phi#234;n vẫn kh#244;ng đủ để đổi m#224;u gi#225; nh#243;m cổ phiếu vốn h#243;a lớn nhất. Tuy nhi#234;n kh#225; nhiều blue-chips tầm trung cũng như cổ phiếu vừa v#224; nhỏ tăng gi#225; đ#227; b#249; lại phần n#224;o, duy tr#236; sắc xanh cho VN-Index.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:08:37 GMT</t>
+          <t>Tue, 12 May 2026 08:25:30 GMT</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -4146,29 +4146,29 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
+          <t>https://vneconomy.vn/co-phieu-tam-trung-tang-tot-vn-index-co-doi-tru-thanh-cong.htm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EU rót hơn 230 tỷ USD vào pin, xe điện để giảm phụ thuộc Trung Quốc</t>
+          <t>Có thể chính thức khởi động thị trường tài sản mã hóa vào quý 3/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Châu Âu và Thụy Sĩ đầu tư 235 tỷ USD vào chuỗi cung ứng pin, xe điện và trạm sạc, nhằm định hình hệ sinh thái và giảm phụ thuộc vào Trung Quốc.</t>
+          <t>“Ch#250;ng t#244;i tin rằng sớm nhất trong qu#253; 3 sẽ c#243; những hoạt động ch#237;nh thức đầu ti#234;n của thị trường t#224;i sản m#227; h#243;a tại Việt Nam với c#225;c tổ chức cung cấp dịch vụ dưới cơ chế quản l#253; an to#224;n, minh bạch”...</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 12:05:00 +0700</t>
+          <t>Tue, 12 May 2026 07:09:47 GMT</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/eu-rot-hon-230-ty-usd-vao-pin-xe-dien-de-giam-phu-thuoc-trung-quoc-5072856.html</t>
+          <t>https://vneconomy.vn/co-the-chinh-thuc-khoi-dong-thi-truong-tai-san-ma-hoa-vao-quy-32026.htm</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
+          <t>Nghiên cứu lập sàn giao dịch chứng khoán cho các startup</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
+          <t>Trong nỗ lực ho#224;n thiện hệ sinh th#225;i đổi mới s#225;ng tạo, Bộ T#224;i ch#237;nh đang nghi#234;n cứu cơ chế thiết lập một thị trường chứng kho#225;n ri#234;ng biệt d#224;nh cho c#225;c doanh nghiệp khởi nghiệp (startup) huy động vốn….</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 03:21:22 GMT</t>
+          <t>Tue, 12 May 2026 06:54:12 GMT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
+          <t>https://vneconomy.vn/nghien-cuu-lap-san-giao-dich-chung-khoan-cho-cac-startup.htm</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4218,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
+          <t>Một công ty chứng khoán hạ dự báo tăng trưởng VN-Index do rủi ro bên ngoài</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
+          <t>Dự b#225;o VN-Index đ#243;ng cửa tại 1.967 điểm, tăng 10,2% so với năm 2025 thấp hơn mức dự b#225;o 2.100 điểm được đưa ra đầu năm do phản #225;nh rủi ro bất định từ b#234;n ngo#224;i.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:52:20 GMT</t>
+          <t>Tue, 12 May 2026 06:46:27 GMT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/mot-cong-ty-chung-khoan-ha-du-bao-tang-truong-vn-index-do-rui-ro-ben-ngoai.htm</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
+          <t>Thanh khoản hụt hơi, cổ phiếu trụ tiếp tục giảm mạnh</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
+          <t>Mặc d#249; độ rộng chỉ số s#225;ng nay kh#244;ng qu#225; k#233;m nhưng ảnh hưởng từ c#225;c cổ phiếu trụ lại khiến VN-Index tổn thất nặng. Chỉ số giảm th#234;m 0,83% (-15,68 điểm), x#225;c nhận nỗ lực vượt đỉnh thất bại.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:00:59 GMT</t>
+          <t>Tue, 12 May 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
+          <t>https://vneconomy.vn/thanh-khoan-hut-hoi-co-phieu-tru-tiep-tuc-giam-manh.htm</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
+          <t>Thị trường hiện tại là “mỏ vàng” cho nhà đầu tư kiên nhẫn, nhiều cổ phiếu tốt và giá rất thấp</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
+          <t>Lời khuy#234;n cho nh#224; đầu tư đ#243; l#224; đừng qu#225; lo lắng về việc gi#225; chưa tăng ngay. Trong đầu tư, gi#225; cả sớm muộn cũng sẽ đồng quy với gi#225; trị nội tại. Việc mua được “h#224;ng tốt” ở “mức gi#225; thấp” l#224; lợi thế lớn nhất để c#243; bi#234;n lợi nhuận vượt trội trong tương lai.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:26:44 GMT</t>
+          <t>Tue, 12 May 2026 03:21:22 GMT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -4296,29 +4296,29 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
+          <t>https://vneconomy.vn/thi-truong-hien-tai-la-mo-vang-cho-nha-dau-tu-kien-nhan-nhieu-co-phieu-tot-va-gia-rat-thap.htm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'Cá voi' Bitcoin trị giá 40 triệu USD thức giấc</t>
+          <t>Các ETF ngoại tiếp tục rút ròng trên thị trường Việt Nam</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sau hơn 10 năm nắm giữ, một nhà đầu tư đã chuyển lượng Bitcoin trị giá 40 triệu USD sang ví mới trong bối cảnh tiền số phục hồi.</t>
+          <t>C#225;c quỹ ETF ngoại ghi nhận d#242;ng tiền r#250;t r#242;ng hơn 121 tỷ đồng, tập trung hầu hết ở quỹ Fubon FTSE Vietnam ETF -226,6 tỷ đồng.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:19:05 +0700</t>
+          <t>Tue, 12 May 2026 02:52:20 GMT</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ca-voi-bitcoin-tri-gia-40-trieu-usd-thuc-giac-5072749.html</t>
+          <t>https://vneconomy.vn/cac-etf-ngoai-tiep-tuc-rut-rong-tren-thi-truong-viet-nam.htm</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
+          <t>Top 3 nhóm ngành mạnh nhất so với thị trường chung</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
+          <t>Trong bối cảnh d#242;ng tiền t#236;m kiếm đến c#225;c cổ phiếu mạnh nhất, ABS lọc ra c#225;c nh#243;m ng#224;nh v#224; cổ phiếu mạnh nhất so với thị trường chung.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:46:58 GMT</t>
+          <t>Tue, 12 May 2026 00:00:59 GMT</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
+          <t>https://vneconomy.vn/top-3-nhom-nganh-manh-nhat-so-voi-thi-truong-chung.htm</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
+          <t>VN-Index mất mốc 1900 điểm, nhà đầu tư cẩn trọng trước điều chỉnh</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
+          <t>VnEconomy giới thiệu nhận định v#224; khuyến nghị đầu tư của một số c#244;ng ty chứng kho#225;n về diễn biến thị trường ng#224;y 12/5/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 10:58:53 GMT</t>
+          <t>Mon, 11 May 2026 15:26:44 GMT</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
+          <t>https://vneconomy.vn/vn-index-mat-moc-1900-diem-nha-dau-tu-can-trong-truoc-dieu-chinh.htm</t>
         </is>
       </c>
     </row>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
+          <t>Cá nhân tiếp tục mua ròng mạnh khi VN-Index rớt khỏi mốc 1.900 điểm</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
+          <t>Nh#224; đầu tư c#225; nh#226;n h#244;m nay mua r#242;ng 744,7 tỷ đồng trong đ#243; nh#224; đầu tư trong nước mua r#242;ng khớp lệnh 607 tỷ đồng. T#237;nh ri#234;ng khớp lệnh, nh#224; đầu tư c#225; nh#226;n mua r#242;ng chủ yếu l#224; ng#224;nh Bất động sản.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:28:46 GMT</t>
+          <t>Mon, 11 May 2026 12:46:58 GMT</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
+          <t>https://vneconomy.vn/ca-nhan-tiep-tuc-mua-rong-manh-khi-vn-index-rot-khoi-moc-1900-diem.htm</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Chỉ số “méo mó”, thị trường cần sự đồng thuận của dòng tiền</t>
+          <t>“Trùm” bán khống Michael Burry: Thị trường bây giờ giống những tháng cuối của bong bóng dotcom</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>T#236;nh trạng lệch pha giữa chỉ số v#224; mặt bằng chung n#224;y đang l#224; chủ đề được giới đầu tư theo d#245;i chặt. Nhiều #253; kiến cho rằng, nếu độ rộng v#224; thanh khoản kh#244;ng sớm cải thiện, rủi ro điều chỉnh kỹ thuật quanh v#249;ng đỉnh sẽ tăng l#234;n.</t>
+          <t>quot;C#243; cảm gi#225;c b#226;y giờ đang giống như những th#225;ng cuối c#249;ng của bong b#243;ng v#224;o năm 1999-2000quot;, nh#224; b#225;n khống nổi tiếng Michael Burry nhận định...</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:08:33 GMT</t>
+          <t>Mon, 11 May 2026 10:58:53 GMT</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chi-so-meo-mo-thi-truong-can-su-dong-thuan-cua-dong-tien.htm</t>
+          <t>https://vneconomy.vn/trum-ban-khong-michael-burry-thi-truong-bay-gio-giong-nhung-thang-cuoi-cua-bong-bong-dotcom.htm</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VN-Index vượt mốc 1920 điểm, cổ phiếu chứng khoán khởi sắc trở lại</t>
+          <t>Blog chứng khoán: Bữa tiệc vắng khách</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tuy độ rộng thị trường s#225;ng nay vẫn nghi#234;ng hẳn về ph#237;a giảm gi#225; nhưng sức mạnh từ nh#243;m trụ vẫn đủ sức “gồng g#225;nh” VN-Index v#224; đẩy chỉ số l#234;n mức 1921,29 điểm. Như vậy VN-Index đ#227; ho#224;n to#224;n vượt l#234;n tr#234;n v#249;ng đỉnh lịch sử, nhưng thị trường chung kh#244;ng c#243; qu#225;n t#237;nh b#249;ng nổ.</t>
+          <t>C#225;c cổ phiếu trụ dẫn dắt quay đầu giảm h#244;m nay tạo hiệu ứng ti#234;u cực tr#234;n diện rộng khi nh#224; đầu tư đ#227; chịu đựng qu#225; đủ t#236;nh trạng “xanh vỏ đỏ l#242;ng” những phi#234;n gần đ#226;y.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:10:22 GMT</t>
+          <t>Mon, 11 May 2026 09:28:46 GMT</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4476,67 +4476,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/vn-index-vuot-moc-1920-diem-co-phieu-chung-khoan-khoi-sac-tro-lai.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Tổ chức trong nước bán ròng gần 2.000 tỷ tuần qua</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Nh#224; đầu tư tổ chức trong nước b#225;n r#242;ng 1875.3 tỷ đồng, t#237;nh ri#234;ng khớp lệnh th#236; họ b#225;n r#242;ng 0.6 tỷ đồng.</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 03:23:29 GMT</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/to-chuc-trong-nuoc-ban-rong-gan-2000-ty-tuan-qua.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>VNeconomy</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Cơn sốt hợp đồng tài chính khoai tây ở châu Âu giữa chiến tranh Mỹ - Iran</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Một cơn sốt đầu cơ khoai t#226;y đang diễn ra ở ch#226;u #194;u d#249; hiện tại, khu vực n#224;y đang đối mặt với t#236;nh trạng dư thừa nguồn cung n#244;ng sản n#224;y...</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 02:33:57 GMT</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/con-sot-hop-dong-tai-chinh-khoai-tay-o-chau-au-giua-chien-tranh-my-iran.htm</t>
+          <t>https://vneconomy.vn/blog-chung-khoan-bua-tiec-vang-khach.htm</t>
         </is>
       </c>
     </row>

--- a/NEWS/market_news.xlsx
+++ b/NEWS/market_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ giảm điểm mạnh vì cổ phiếu công nghệ bị bán, giá dầu leo thang</t>
+          <t>Lợi suất trái phiếu chính phủ Nhật Bản tăng vọt, nhà đầu tư Nhật có thể ồ ạt rút vốn về nước</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lợi suất tr#225;i phiếu tăng mạnh cũng l#224; một nguy#234;n nh#226;n quan trọng khiến cổ phiếu bị b#225;n th#225;o...</t>
+          <t>Lợi suất tr#225;i phiếu ch#237;nh phủ Nhật Bản (JGB) tăng l#234;n mức cao nhất trong nhiều thập kỷ, dẫn tới lo ngại về khả năng c#225;c nh#224; đầu tư nước n#224;y sẽ r#250;t vốn khỏi thị trường nước ngo#224;i v#224; quay trở lại đầu tư trong nước...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 16 May 2026 01:44:28 GMT</t>
+          <t>Mon, 18 May 2026 00:57:23 GMT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,29 +486,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-giam-diem-manh-vi-co-phieu-cong-nghe-bi-ban-gia-dau-leo-thang.htm</t>
+          <t>https://vneconomy.vn/loi-suat-trai-phieu-chinh-phu-nhat-ban-tang-vot-nha-dau-tu-nhat-co-the-o-at-rut-von-ve-nuoc.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giá vàng thế giới xuống thấp nhất gần 2 tuần</t>
+          <t>Nỗi lo lãi suất tăng đè nặng lên giá vàng</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Đôla Mỹ đắt lên và lợi suất trái phiếu chính phủ Mỹ tăng cao khiến giá vàng thế giới mất hơn 100 USD phiên cuối tuần.</t>
+          <t>Giới chuy#234;n gia cho rằng thị trường kim loại qu#253; đang đối mặt với nhiều trở ngại lớn trong ngắn hạn, đặc biệt l#224; chi ph#237; cơ hội...</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sat, 16 May 2026 07:13:12 +0700</t>
+          <t>Mon, 18 May 2026 00:22:10 GMT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -516,29 +516,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-the-gioi-xuong-thap-nhat-gan-2-tuan-5074551.html</t>
+          <t>https://vneconomy.vn/noi-lo-lai-suat-tang-de-nang-len-gia-vang.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
+          <t>Thị trường trái phiếu chính phủ toàn cầu bán tháo vì mối lo lạm phát</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ngân hàng Nhà nước vừa nới cách tính tỷ lệ dư nợ cho vay trên tổng tiền gửi (LDR), qua đó hỗ trợ thanh khoản cho nhóm ngân hàng quốc doanh.</t>
+          <t>Thị trường tr#225;i phiếu to#224;n cầu đang trải qua một đợt b#225;n th#225;o mạnh mẽ khi nỗi lo về lạm ph#225;t k#233;o d#224;i. Động th#225;i n#224;y do t#225;c động từ cuộc chiến tranh Mỹ - Iran g#226;y #225;p lực lớn l#234;n chi ph#237; vay nợ của c#225;c ch#237;nh phủ...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 19:15:20 +0700</t>
+          <t>Sat, 16 May 2026 09:00:45 GMT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
+          <t>https://vneconomy.vn/thi-truong-trai-phieu-chinh-phu-toan-cau-ban-thao-vi-moi-lo-lam-phat.htm</t>
         </is>
       </c>
     </row>
@@ -558,17 +558,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ba cổ phiếu ngân hàng tiềm năng tăng giá tốt nhất trong bối cảnh lãi suất cao đe dọa NIM, nợ xấu tăng</t>
+          <t>Chứng khoán Mỹ giảm điểm mạnh vì cổ phiếu công nghệ bị bán, giá dầu leo thang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VnDirect kỳ vọng NIM to#224;n ng#224;nh sẽ dần cải thiện v#224;o cuối năm khi mặt bằng l#227;i suất c#243; xu hướng hạ nhiệt v#224; hoạt động thu hồi nợ thường t#237;ch cực hơn trong nửa cuối năm. Theo đ#243;, kỳ vọng NIM to#224;n ng#224;nh năm 2026 sẽ duy tr#236; quanh mức 3,1%.</t>
+          <t>Lợi suất tr#225;i phiếu tăng mạnh cũng l#224; một nguy#234;n nh#226;n quan trọng khiến cổ phiếu bị b#225;n th#225;o...</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 04:42:52 GMT</t>
+          <t>Sat, 16 May 2026 01:44:28 GMT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -576,29 +576,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ba-co-phieu-ngan-hang-tiem-nang-tang-gia-tot-nhat-trong-boi-canh-lai-suat-cao-de-doa-nim-no-xau-tang.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-giam-diem-manh-vi-co-phieu-cong-nghe-bi-ban-gia-dau-leo-thang.htm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
+          <t>Giá vàng thế giới xuống thấp nhất gần 2 tuần</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
+          <t>Đôla Mỹ đắt lên và lợi suất trái phiếu chính phủ Mỹ tăng cao khiến giá vàng thế giới mất hơn 100 USD phiên cuối tuần.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 00:40:12 GMT</t>
+          <t>Sat, 16 May 2026 07:13:12 +0700</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,29 +606,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
+          <t>https://vnexpress.net/gia-vang-the-gioi-xuong-thap-nhat-gan-2-tuan-5074551.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vietstock</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
+          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
+          <t>Ngân hàng Nhà nước vừa nới cách tính tỷ lệ dư nợ cho vay trên tổng tiền gửi (LDR), qua đó hỗ trợ thanh khoản cho nhóm ngân hàng quốc doanh.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 16:37:00 +0700</t>
+          <t>Fri, 15 May 2026 19:15:20 +0700</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -636,29 +636,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
+          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Giá xăng, dầu cùng giảm</t>
+          <t>Ba cổ phiếu ngân hàng tiềm năng tăng giá tốt nhất trong bối cảnh lãi suất cao đe dọa NIM, nợ xấu tăng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
+          <t>VnDirect kỳ vọng NIM to#224;n ng#224;nh sẽ dần cải thiện v#224;o cuối năm khi mặt bằng l#227;i suất c#243; xu hướng hạ nhiệt v#224; hoạt động thu hồi nợ thường t#237;ch cực hơn trong nửa cuối năm. Theo đ#243;, kỳ vọng NIM to#224;n ng#224;nh năm 2026 sẽ duy tr#236; quanh mức 3,1%.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 14:34:59 +0700</t>
+          <t>Fri, 15 May 2026 04:42:52 GMT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
+          <t>https://vneconomy.vn/ba-co-phieu-ngan-hang-tiem-nang-tang-gia-tot-nhat-trong-boi-canh-lai-suat-cao-de-doa-nim-no-xau-tang.htm</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
+          <t>Chứng khoán Mỹ liên tục lập đỉnh dù giá dầu neo cao</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
+          <t>Động lực cho phi#234;n tăng n#224;y l#224; xu hướng mua mạnh cổ phiếu c#244;ng nghệ v#224; t#226;m l#253; lạc quan thận trọng của nh#224; đầu tư về cuộc gặp thượng đỉnh Mỹ - Trung, bất chấp gi#225; dầu duy tr#236; tr#234;n ngưỡng 3 con số...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:50:35 GMT</t>
+          <t>Fri, 15 May 2026 00:40:12 GMT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lien-tuc-lap-dinh-du-gia-dau-neo-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>Vietstock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
+          <t>Nhịp đập Thị trường 14/05: VN-Index đóng cửa tại 1,925 điểm, khối ngoại mua ròng trở lại</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
+          <t>Sau phiên sáng ngập tràn điểm nhấn, thị trường phiên chiều lại thiên về giằng co trong biên độ hẹp.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 06:47:13 GMT</t>
+          <t>Thu, 14 May 2026 16:37:00 +0700</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -726,29 +726,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
+          <t>http://vietstock.vn/2026/05/nhip-dap-thi-truong-1405-vn-index-dong-cua-tai-1925-diem-khoi-ngoai-mua-rong-tro-lai-1636-1442403.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
+          <t>Từ 15h ngày 14/5, giá xăng, dầu cùng giảm theo đà biến động của thị trường năng lượng thế giới.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 01:18:51 GMT</t>
+          <t>Thu, 14 May 2026 14:34:59 +0700</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
+          <t>Rủi ro nào cho công ty chứng khoán khi mặt bằng lãi suất tăng cao?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
+          <t>C#225;c t#224;i sản Tr#225;i phiếu doanh nghiệp c#243; thể phải ghi nhận lỗ chưa thực hiện khi l#227;i suất tăng, tuy kh#244;ng phải ghi nhận v#224;o b#225;o c#225;o kết quả kinh doanh, điều n#224;y c#243; thể l#224;m b#224;o m#242;n vốn chủ sở hữu.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 00:26:34 GMT</t>
+          <t>Thu, 14 May 2026 06:50:35 GMT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -786,29 +786,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
+          <t>https://vneconomy.vn/rui-ro-nao-cho-cong-ty-chung-khoan-khi-mat-bang-lai-suat-tang-cao.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
+          <t>Khối ngoại bán ròng 2 tỷ USD từ đầu năm, vượt con số kỳ vọng 1,3 tỷ USD ETF đổ vào sau nâng hạng</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
+          <t>Gi#225; trị b#225;n r#242;ng lũy kế của nh#224; đầu tư nước ngo#224;i kể từ đầu năm 2026 đến nay l#234;n gần 53.000 tỷ đồng tr#234;n to#224;n bộ thị trường chứng kho#225;n Việt Nam.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:00:10 +0700</t>
+          <t>Thu, 14 May 2026 06:47:13 GMT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -816,29 +816,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-2-ty-usd-tu-dau-nam-vuot-con-so-ky-vong-13-ty-usd-etf-do-vao-sau-nang-hang.htm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VnExpress Business</t>
+          <t>VNeconomy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Doanh nghiệp Mỹ hưởng lợi gì khi cùng ông Trump tới Trung Quốc?</t>
+          <t>Chứng khoán Mỹ lập kỷ lục nhờ cổ phiếu công nghệ, giá dầu giảm vì mối lo lãi suất cao hơn lâu hơn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trong khi Boeing và Cargill có thể đạt thỏa thuận mua hàng, Nvidia, Meta và Tesla lại đến Trung Quốc để giải quyết các rào cản chính sách tại đây.</t>
+          <t>Thị trường chứng kho#225;n Mỹ tăng điểm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), khi cổ phiếu c#244;ng nghệ được mua mạnh, đưa hai chỉ số Samp;P 500 v#224; Nasdaq lập kỷ lục mới...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:18:27 +0700</t>
+          <t>Thu, 14 May 2026 01:18:51 GMT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-my-huong-loi-gi-khi-cung-ong-trump-toi-trung-quoc-5073296.html</t>
+          <t>https://vneconomy.vn/chung-khoan-my-lap-ky-luc-nho-co-phieu-cong-nghe-gia-dau-giam-vi-moi-lo-lai-suat-cao-hon-lau-hon.htm</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
+          <t>Áp lực lạm phát đè nặng giá vàng, SPDR Gold Trust mua ròng liên tục</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
+          <t>Gi#225; v#224;ng thế giới giảm trong phi#234;n giao dịch ng#224;y thứ Tư (13/5), trượt khỏi mốc 4.700 USD/oz, khi #225;p lực lạm ph#225;t gia tăng ở Mỹ đẩy cao mối lo l#227;i suất cao hơn l#226;u hơn...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 03:47:17 GMT</t>
+          <t>Thu, 14 May 2026 00:26:34 GMT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/ap-luc-lam-phat-de-nang-gia-vang-spdr-gold-trust-mua-rong-lien-tuc.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VNeconomy</t>
+          <t>VnExpress Business</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
+          <t>Phó thủ tướng: FDI thế hệ mới phải tạo giá trị cho Việt Nam</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
+          <t>Việt Nam không thu hút vốn FDI bằng mọi giá, mà ưu tiên các dự án công nghệ có khả năng kết nối doanh nghiệp nội.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:04:51 GMT</t>
+          <t>Wed, 13 May 2026 19:00:10 +0700</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
+          <t>https://vnexpress.net/pho-thu-tuong-fdi-the-he-moi-phai-tao-gia-tri-cho-viet-nam-5073553.html</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
+          <t>Tỷ giá đồng yên biến động mạnh trong lúc Bộ trưởng Bessent thăm Nhật Bản</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
+          <t>Giới chức Nhật Bản vốn tin rằng một sự ủng hộ từ #244;ng Bessent sẽ gi#250;p củng cố t#225;c dụng của việc họ can thiệp v#224;o thị trường tiền tệ, theo đ#243; cản lại #225;p lực mất gi#225; đồng y#234;n...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:57:58 GMT</t>
+          <t>Wed, 13 May 2026 03:47:17 GMT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
+          <t>https://vneconomy.vn/ty-gia-dong-yen-bien-dong-manh-trong-luc-bo-truong-bessent-tham-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
+          <t>Lạm phát ở Mỹ cao nhất gần 3 năm do giá xăng dầu tăng mạnh, Fed gặp khó</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
+          <t>Giới chuy#234;n gia cảnh b#225;o rằng gi#225; cả ở nền kinh tế lớn nhất thế giới sẽ tiếp tục leo thang tr#234;n phạm vi ng#224;y c#224;ng rộng hơn trong những th#225;ng sắp tới, khiến Fed kh#243; hạ l#227;i suất...</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:18:43 GMT</t>
+          <t>Wed, 13 May 2026 02:04:51 GMT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
+          <t>https://vneconomy.vn/lam-phat-o-my-cao-nhat-gan-3-nam-do-gia-xang-dau-tang-manh-fed-gap-kho.htm</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
+          <t>Dự báo MSCI đưa thị trường Việt Nam vào danh sách theo dõi trong năm 2026-2027</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
+          <t>Trong kịch bản cơ sở, BSC Research dự b#225;o thị trường chứng kho#225;n Việt Nam c#243; thể được MSCI th#244;ng b#225;o đưa v#224;o danh s#225;ch theo d#245;i (Watch-list) trong giai đoạn 2026-2027.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 14:06:05 GMT</t>
+          <t>Wed, 13 May 2026 01:57:58 GMT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
+          <t>https://vneconomy.vn/du-bao-msci-dua-thi-truong-viet-nam-vao-danh-sach-theo-doi-trong-nam-2026-2027.htm</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
+          <t>Chứng khoán Mỹ trượt khỏi kỷ lục sau báo cáo lạm phát, giá dầu tiếp tục leo thang</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
+          <t>Mối lo về lạm ph#225;t phủ b#243;ng l#234;n t#226;m tr#237; nh#224; đầu tư ở Phố Wall trong phi#234;n n#224;y...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 01:19:45 GMT</t>
+          <t>Wed, 13 May 2026 01:18:43 GMT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-truot-khoi-ky-luc-sau-bao-cao-lam-phat-gia-dau-tiep-tuc-leo-thang.htm</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
+          <t>Khối ngoại bán ròng hơn 800 tỷ, chủ yếu xả cổ phiếu ngân hàng</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
+          <t>Khối ngoại tiếp tục b#225;n r#242;ng 836.0 tỷ đồng, t#237;nh ri#234;ng giao dịch khớp lệnh th#236; họ b#225;n r#242;ng 685.3 tỷ đồng.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:02:03 GMT</t>
+          <t>Tue, 12 May 2026 14:06:05 GMT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
+          <t>https://vneconomy.vn/khoi-ngoai-ban-rong-hon-800-ty-chu-yeu-xa-co-phieu-ngan-hang.htm</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
+          <t>Chứng khoán Mỹ vẫn lập đỉnh mới dù đàm phán hòa bình bế tắc, giá dầu tăng 3%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
+          <t>“Với sự b#249;ng nổ của c#244;ng nghệ, thị trường n#224;y kh#244;ng muốn giảm”, một nh#224; quản l#253; quỹ n#243;i...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 00:01:27 GMT</t>
+          <t>Tue, 12 May 2026 01:19:45 GMT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/fiingroup-ap-luc-bien-loi-nhuan-khien-cac-ngan-hang-kho-giam-lai-suat-ngay-trong-ngan-han.htm</t>
+          <t>https://vneconomy.vn/chung-khoan-my-van-lap-dinh-moi-du-dam-phan-hoa-binh-be-tac-gia-dau-tang-3.htm</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tháng 4, HNX huy động 45.455 tỷ đồng qua đấu thầu trái phiếu Chính phủ</t>
+          <t>Thị trường đang thử thách quyết tâm bảo vệ tỷ giá đồng yên của Nhật Bản</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T#237;nh lũy kế từ đầu năm, Kho bạc Nh#224; nước đ#227; huy động được 125.556 tỷ đồng, ho#224;n th#224;nh 41% kế hoạch ph#225;t h#224;nh qu#253; 2 v#224; đạt 25% kế hoạch ph#225;t h#224;nh của năm 2026.</t>
+          <t>Bởi vậy, nếu BOJ tiếp tục giữ nguy#234;n thay v#236; tăng l#227;i suất, xu hướng mất gi#225; của đồng y#234;n c#243; thể c#242;n tiếp tục...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 12:47:52 GMT</t>
+          <t>Tue, 12 May 2026 00:02:03 GMT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/thang-4-hnx-huy-dong-45455-ty-dong-qua-dau-thau-trai-phieu-chinh-phu.htm</t>
+          <t>https://vneconomy.vn/thi-truong-dang-thu-thach-quyet-tam-bao-ve-ty-gia-dong-yen-cua-nhat-ban.htm</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Australia khởi xướng điều tra đối với thép mạ kẽm nhập khẩu từ Việt Nam</t>
+          <t>FiinGroup: Áp lực biên lợi nhuận khiến các ngân hàng khó giảm lãi suất ngay trong ngắn hạn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia vừa ch#237;nh thức khởi xướng điều tra đối với sản phẩm th#233;p mạ kẽm nhập khẩu từ Việt Nam. D#249; đối mặt với c#225;o buộc bi#234;n độ ph#225; gi#225; ở mức cao, c#225;c doanh nghiệp trong nước vẫn tự tin v#224;o khả năng bảo vệ lợi #237;ch hợp ph#225;p dựa tr#234;n số liệu thực tế v#224; kinh nghiệm d#224;y dạn...</t>
+          <t>Theo Fiingroup l#227;i suất cho vay được dự b#225;o sẽ kh#243; giảm ngay trong ngắn hạn khi bi#234;n lợi nhuận của c#225;c ng#226;n h#224;ng đang chịu #225;p lực thu hẹp r#245; rệt.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:53:09 GMT</t>
+          <t>Tue, 12 May 2026 00:01:27 GMT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ 